--- a/artfynd/A 30467-2025 artfynd.xlsx
+++ b/artfynd/A 30467-2025 artfynd.xlsx
@@ -675,45 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126919968</v>
+        <v>126909580</v>
       </c>
       <c r="B2" t="n">
-        <v>79987</v>
+        <v>98436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rislidstjärnarna, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>690349</v>
+        <v>690493</v>
       </c>
       <c r="R2" t="n">
-        <v>7097128</v>
+        <v>7097055</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,9 +747,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,12 +774,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
+          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -776,49 +790,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126909580</v>
+        <v>126919968</v>
       </c>
       <c r="B3" t="n">
-        <v>98361</v>
+        <v>80018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Rislidstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>690493</v>
+        <v>690349</v>
       </c>
       <c r="R3" t="n">
-        <v>7097055</v>
+        <v>7097128</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,19 +858,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,12 +875,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
+          <t>Emil Lindgren, Hedda Bring, Lotta Ihse, Eleonor Johansson, Fredrik Wilde, Nicklas Gustavsson, Isac Enetjärn, Malin Löfgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1005,32 +1005,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126917550</v>
+        <v>126917563</v>
       </c>
       <c r="B5" t="n">
-        <v>80119</v>
+        <v>79011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>690515</v>
+        <v>690509</v>
       </c>
       <c r="R5" t="n">
-        <v>7097014</v>
+        <v>7097052</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,32 +1106,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126917563</v>
+        <v>126917550</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>80150</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>690509</v>
+        <v>690515</v>
       </c>
       <c r="R6" t="n">
-        <v>7097052</v>
+        <v>7097014</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1210,7 @@
         <v>126919976</v>
       </c>
       <c r="B7" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
+          <t>Emil Lindgren, Hedda Bring, Lotta Ihse, Eleonor Johansson, Fredrik Wilde, Nicklas Gustavsson, Isac Enetjärn, Malin Löfgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1311,7 +1311,7 @@
         <v>126917539</v>
       </c>
       <c r="B8" t="n">
-        <v>91256</v>
+        <v>91330</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>126919966</v>
       </c>
       <c r="B9" t="n">
-        <v>91256</v>
+        <v>91330</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
+          <t>Emil Lindgren, Hedda Bring, Lotta Ihse, Eleonor Johansson, Fredrik Wilde, Nicklas Gustavsson, Isac Enetjärn, Malin Löfgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1517,7 +1517,7 @@
         <v>126917545</v>
       </c>
       <c r="B10" t="n">
-        <v>79987</v>
+        <v>80018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>126909288</v>
       </c>
       <c r="B11" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1726,10 +1726,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126909538</v>
+        <v>126909413</v>
       </c>
       <c r="B12" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>690484</v>
+        <v>690516</v>
       </c>
       <c r="R12" t="n">
-        <v>7097073</v>
+        <v>7097033</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126909413</v>
+        <v>126909538</v>
       </c>
       <c r="B13" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>690516</v>
+        <v>690484</v>
       </c>
       <c r="R13" t="n">
-        <v>7097033</v>
+        <v>7097073</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,7 +1959,7 @@
         <v>126918516</v>
       </c>
       <c r="B14" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,10 +2070,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126918507</v>
+        <v>126917549</v>
       </c>
       <c r="B15" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2099,19 +2099,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>N Johannesbomyran, Ång</t>
+          <t>Rislidtjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>690488</v>
+        <v>690509</v>
       </c>
       <c r="R15" t="n">
-        <v>7097027</v>
+        <v>7097031</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2152,19 +2149,18 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2175,10 +2171,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126917549</v>
+        <v>126918507</v>
       </c>
       <c r="B16" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2204,16 +2200,19 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rislidtjärnarna, Ång</t>
+          <t>N Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>690509</v>
+        <v>690488</v>
       </c>
       <c r="R16" t="n">
-        <v>7097031</v>
+        <v>7097027</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2254,18 +2253,19 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2393,7 +2393,7 @@
         <v>126909505</v>
       </c>
       <c r="B18" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>126927367</v>
       </c>
       <c r="B19" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2598,45 +2598,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126926856</v>
+        <v>126936912</v>
       </c>
       <c r="B20" t="n">
-        <v>78739</v>
+        <v>92609</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>N Johannesbomyran, N Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>690563</v>
+        <v>690392</v>
       </c>
       <c r="R20" t="n">
-        <v>7096856</v>
+        <v>7097038</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2683,60 +2683,64 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126936912</v>
+        <v>126927356</v>
       </c>
       <c r="B21" t="n">
-        <v>92535</v>
+        <v>79011</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>690392</v>
+        <v>690516</v>
       </c>
       <c r="R21" t="n">
-        <v>7097038</v>
+        <v>7096990</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2780,64 +2784,60 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126927356</v>
+        <v>126931573</v>
       </c>
       <c r="B22" t="n">
-        <v>78980</v>
+        <v>98436</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>690516</v>
+        <v>690578</v>
       </c>
       <c r="R22" t="n">
-        <v>7096990</v>
+        <v>7096991</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2881,57 +2881,61 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126931573</v>
+        <v>126926856</v>
       </c>
       <c r="B23" t="n">
-        <v>98361</v>
+        <v>78770</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>N Johannesbomyran, N Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>690578</v>
+        <v>690563</v>
       </c>
       <c r="R23" t="n">
-        <v>7096991</v>
+        <v>7096856</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2978,26 +2982,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126937624</v>
+        <v>126927661</v>
       </c>
       <c r="B24" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3025,14 +3025,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>690656</v>
+        <v>690574</v>
       </c>
       <c r="R24" t="n">
-        <v>7096868</v>
+        <v>7096978</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3079,26 +3079,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126927661</v>
+        <v>126937624</v>
       </c>
       <c r="B25" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3126,14 +3122,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>690574</v>
+        <v>690656</v>
       </c>
       <c r="R25" t="n">
-        <v>7096978</v>
+        <v>7096868</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3180,72 +3176,64 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126936890</v>
+        <v>126927842</v>
       </c>
       <c r="B26" t="n">
-        <v>98361</v>
+        <v>79011</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>690564</v>
+        <v>690605</v>
       </c>
       <c r="R26" t="n">
-        <v>7096907</v>
+        <v>7096920</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3283,71 +3271,82 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126927842</v>
+        <v>126936886</v>
       </c>
       <c r="B27" t="n">
-        <v>78980</v>
+        <v>98436</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>690605</v>
+        <v>690607</v>
       </c>
       <c r="R27" t="n">
-        <v>7096920</v>
+        <v>7097014</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3385,28 +3384,33 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>126936889</v>
       </c>
       <c r="B28" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3521,45 +3525,57 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126931565</v>
+        <v>126936890</v>
       </c>
       <c r="B29" t="n">
-        <v>78739</v>
+        <v>98436</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>690620</v>
+        <v>690564</v>
       </c>
       <c r="R29" t="n">
-        <v>7096859</v>
+        <v>7096907</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3600,18 +3616,19 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3622,61 +3639,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126936886</v>
+        <v>126931565</v>
       </c>
       <c r="B30" t="n">
-        <v>98361</v>
+        <v>78770</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>690607</v>
+        <v>690620</v>
       </c>
       <c r="R30" t="n">
-        <v>7097014</v>
+        <v>7096859</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3717,19 +3718,18 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3740,45 +3740,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126937621</v>
+        <v>126927550</v>
       </c>
       <c r="B31" t="n">
-        <v>98361</v>
+        <v>79011</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>690635</v>
+        <v>690574</v>
       </c>
       <c r="R31" t="n">
-        <v>7096944</v>
+        <v>7096994</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3813,11 +3813,6 @@
           <t>2025-07-26</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ca 40 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3830,77 +3825,57 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126936883</v>
+        <v>126936897</v>
       </c>
       <c r="B32" t="n">
-        <v>98361</v>
+        <v>79011</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>690668</v>
+        <v>690544</v>
       </c>
       <c r="R32" t="n">
-        <v>7096918</v>
+        <v>7096906</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3941,7 +3916,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3964,45 +3938,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126927550</v>
+        <v>126937621</v>
       </c>
       <c r="B33" t="n">
-        <v>78980</v>
+        <v>98436</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>690574</v>
+        <v>690635</v>
       </c>
       <c r="R33" t="n">
-        <v>7096994</v>
+        <v>7096944</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4037,6 +4011,11 @@
           <t>2025-07-26</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ca 40 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4049,57 +4028,77 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126936897</v>
+        <v>126936883</v>
       </c>
       <c r="B34" t="n">
-        <v>78980</v>
+        <v>98436</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>690544</v>
+        <v>690668</v>
       </c>
       <c r="R34" t="n">
-        <v>7096906</v>
+        <v>7096918</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4140,6 +4139,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4162,10 +4162,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126931567</v>
+        <v>126936888</v>
       </c>
       <c r="B35" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4192,12 +4192,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -4205,14 +4205,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>690686</v>
+        <v>690639</v>
       </c>
       <c r="R35" t="n">
-        <v>7096928</v>
+        <v>7096927</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4260,12 +4260,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4276,10 +4276,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126936888</v>
+        <v>126931567</v>
       </c>
       <c r="B36" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4306,12 +4306,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -4319,14 +4319,14 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>690639</v>
+        <v>690686</v>
       </c>
       <c r="R36" t="n">
-        <v>7096927</v>
+        <v>7096928</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4374,12 +4374,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4393,7 +4393,7 @@
         <v>126937620</v>
       </c>
       <c r="B37" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4501,10 +4501,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126936900</v>
+        <v>126926531</v>
       </c>
       <c r="B38" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4532,14 +4532,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>690663</v>
+        <v>690376</v>
       </c>
       <c r="R38" t="n">
-        <v>7096854</v>
+        <v>7097225</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4586,26 +4586,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126936910</v>
+        <v>126936900</v>
       </c>
       <c r="B39" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4637,10 +4633,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>690572</v>
+        <v>690663</v>
       </c>
       <c r="R39" t="n">
-        <v>7096932</v>
+        <v>7096854</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4703,10 +4699,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126926531</v>
+        <v>126936910</v>
       </c>
       <c r="B40" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4734,14 +4730,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>690376</v>
+        <v>690572</v>
       </c>
       <c r="R40" t="n">
-        <v>7097225</v>
+        <v>7096932</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4788,22 +4784,26 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
         <v>126936887</v>
       </c>
       <c r="B41" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4914,48 +4914,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126936894</v>
+        <v>126926789</v>
       </c>
       <c r="B42" t="n">
-        <v>98361</v>
+        <v>91339</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>690497</v>
+        <v>690438</v>
       </c>
       <c r="R42" t="n">
-        <v>7097017</v>
+        <v>7097141</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4999,64 +4999,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126926789</v>
+        <v>126936894</v>
       </c>
       <c r="B43" t="n">
-        <v>91265</v>
+        <v>98436</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>690438</v>
+        <v>690497</v>
       </c>
       <c r="R43" t="n">
-        <v>7097141</v>
+        <v>7097017</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5100,72 +5096,64 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126931570</v>
+        <v>126926859</v>
       </c>
       <c r="B44" t="n">
-        <v>98361</v>
+        <v>79011</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>690658</v>
+        <v>690483</v>
       </c>
       <c r="R44" t="n">
-        <v>7096895</v>
+        <v>7097114</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5203,68 +5191,75 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126936882</v>
+        <v>126931570</v>
       </c>
       <c r="B45" t="n">
-        <v>78739</v>
+        <v>98436</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>690560</v>
+        <v>690658</v>
       </c>
       <c r="R45" t="n">
-        <v>7096959</v>
+        <v>7096895</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5305,18 +5300,19 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5327,10 +5323,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126926859</v>
+        <v>126936882</v>
       </c>
       <c r="B46" t="n">
-        <v>78980</v>
+        <v>78770</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5338,37 +5334,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>690483</v>
+        <v>690560</v>
       </c>
       <c r="R46" t="n">
-        <v>7097114</v>
+        <v>7096959</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5412,22 +5408,26 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126936911</v>
+        <v>126928173</v>
       </c>
       <c r="B47" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5455,17 +5455,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>690481</v>
+        <v>690547</v>
       </c>
       <c r="R47" t="n">
-        <v>7097028</v>
+        <v>7096876</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5509,26 +5509,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
         <v>126937632</v>
       </c>
       <c r="B48" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5626,57 +5622,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126936885</v>
+        <v>126936911</v>
       </c>
       <c r="B49" t="n">
-        <v>98361</v>
+        <v>79011</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>690596</v>
+        <v>690481</v>
       </c>
       <c r="R49" t="n">
-        <v>7097007</v>
+        <v>7097028</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5717,7 +5701,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5740,10 +5723,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126928173</v>
+        <v>126937623</v>
       </c>
       <c r="B50" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5771,14 +5754,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>690547</v>
+        <v>690707</v>
       </c>
       <c r="R50" t="n">
-        <v>7096876</v>
+        <v>7096903</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5825,22 +5808,26 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126937623</v>
+        <v>126936877</v>
       </c>
       <c r="B51" t="n">
-        <v>78980</v>
+        <v>79629</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5848,37 +5835,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>690707</v>
+        <v>690378</v>
       </c>
       <c r="R51" t="n">
-        <v>7096903</v>
+        <v>7096984</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5922,12 +5909,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5938,45 +5925,57 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126936877</v>
+        <v>126936885</v>
       </c>
       <c r="B52" t="n">
-        <v>79598</v>
+        <v>98436</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>690378</v>
+        <v>690596</v>
       </c>
       <c r="R52" t="n">
-        <v>7096984</v>
+        <v>7097007</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6017,6 +6016,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6042,7 +6042,7 @@
         <v>126927000</v>
       </c>
       <c r="B53" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6136,10 +6136,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126936878</v>
+        <v>126928117</v>
       </c>
       <c r="B54" t="n">
-        <v>79598</v>
+        <v>79011</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6147,37 +6147,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>690509</v>
+        <v>690540</v>
       </c>
       <c r="R54" t="n">
-        <v>7096927</v>
+        <v>7096888</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6221,76 +6221,60 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126931571</v>
+        <v>126927086</v>
       </c>
       <c r="B55" t="n">
-        <v>98361</v>
+        <v>80114</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>690644</v>
+        <v>690545</v>
       </c>
       <c r="R55" t="n">
-        <v>7096948</v>
+        <v>7097033</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6328,33 +6312,28 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126927086</v>
+        <v>126936878</v>
       </c>
       <c r="B56" t="n">
-        <v>80083</v>
+        <v>79629</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6362,37 +6341,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>690545</v>
+        <v>690509</v>
       </c>
       <c r="R56" t="n">
-        <v>7097033</v>
+        <v>7096927</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6436,60 +6415,76 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126928117</v>
+        <v>126931571</v>
       </c>
       <c r="B57" t="n">
-        <v>78980</v>
+        <v>98436</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>690540</v>
+        <v>690644</v>
       </c>
       <c r="R57" t="n">
-        <v>7096888</v>
+        <v>7096948</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6527,28 +6522,33 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126927108</v>
+        <v>126926624</v>
       </c>
       <c r="B58" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6580,10 +6580,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>690542</v>
+        <v>690399</v>
       </c>
       <c r="R58" t="n">
-        <v>7097030</v>
+        <v>7097170</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6642,10 +6642,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126937630</v>
+        <v>126926566</v>
       </c>
       <c r="B59" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6673,14 +6673,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>690480</v>
+        <v>690362</v>
       </c>
       <c r="R59" t="n">
-        <v>7096994</v>
+        <v>7097210</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6727,26 +6727,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126927426</v>
+        <v>126937630</v>
       </c>
       <c r="B60" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6774,14 +6770,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>690560</v>
+        <v>690480</v>
       </c>
       <c r="R60" t="n">
-        <v>7097019</v>
+        <v>7096994</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6828,22 +6824,26 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126926624</v>
+        <v>126927108</v>
       </c>
       <c r="B61" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6875,10 +6875,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>690399</v>
+        <v>690542</v>
       </c>
       <c r="R61" t="n">
-        <v>7097170</v>
+        <v>7097030</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6937,10 +6937,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126926566</v>
+        <v>126927426</v>
       </c>
       <c r="B62" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6972,10 +6972,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>690362</v>
+        <v>690560</v>
       </c>
       <c r="R62" t="n">
-        <v>7097210</v>
+        <v>7097019</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7037,7 +7037,7 @@
         <v>126936881</v>
       </c>
       <c r="B63" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7135,45 +7135,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126936893</v>
+        <v>126927067</v>
       </c>
       <c r="B64" t="n">
-        <v>98361</v>
+        <v>79011</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>690658</v>
+        <v>690536</v>
       </c>
       <c r="R64" t="n">
-        <v>7096938</v>
+        <v>7097045</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7220,48 +7220,44 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126927409</v>
+        <v>126926457</v>
       </c>
       <c r="B65" t="n">
-        <v>98361</v>
+        <v>79011</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7271,10 +7267,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>690545</v>
+        <v>690374</v>
       </c>
       <c r="R65" t="n">
-        <v>7097003</v>
+        <v>7097232</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7333,10 +7329,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126927067</v>
+        <v>126931576</v>
       </c>
       <c r="B66" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7364,14 +7360,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>690536</v>
+        <v>690565</v>
       </c>
       <c r="R66" t="n">
-        <v>7097045</v>
+        <v>7096992</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7418,57 +7414,61 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126931576</v>
+        <v>126936893</v>
       </c>
       <c r="B67" t="n">
-        <v>78980</v>
+        <v>98436</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>690565</v>
+        <v>690658</v>
       </c>
       <c r="R67" t="n">
-        <v>7096992</v>
+        <v>7096938</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7515,12 +7515,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7531,32 +7531,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126926457</v>
+        <v>126927409</v>
       </c>
       <c r="B68" t="n">
-        <v>78980</v>
+        <v>98436</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7566,10 +7566,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>690374</v>
+        <v>690545</v>
       </c>
       <c r="R68" t="n">
-        <v>7097232</v>
+        <v>7097003</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7628,10 +7628,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126927324</v>
+        <v>126926526</v>
       </c>
       <c r="B69" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7659,17 +7659,17 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>N Johannesbomyran, N Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>690542</v>
+        <v>690490</v>
       </c>
       <c r="R69" t="n">
-        <v>7097025</v>
+        <v>7096997</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7713,12 +7713,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -7728,7 +7728,7 @@
         <v>126936908</v>
       </c>
       <c r="B70" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7826,10 +7826,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126926526</v>
+        <v>126927324</v>
       </c>
       <c r="B71" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7857,17 +7857,17 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>N Johannesbomyran, N Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>690490</v>
+        <v>690542</v>
       </c>
       <c r="R71" t="n">
-        <v>7096997</v>
+        <v>7097025</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7911,54 +7911,66 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126936896</v>
+        <v>126936891</v>
       </c>
       <c r="B72" t="n">
-        <v>78980</v>
+        <v>98436</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>690482</v>
+        <v>690644</v>
       </c>
       <c r="R72" t="n">
         <v>7096931</v>
@@ -8002,6 +8014,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8024,48 +8037,48 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126927191</v>
+        <v>126936879</v>
       </c>
       <c r="B73" t="n">
-        <v>78980</v>
+        <v>97320</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>690524</v>
+        <v>690490</v>
       </c>
       <c r="R73" t="n">
-        <v>7097009</v>
+        <v>7096937</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8109,72 +8122,64 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126936891</v>
+        <v>126927191</v>
       </c>
       <c r="B74" t="n">
-        <v>98361</v>
+        <v>79011</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>690644</v>
+        <v>690524</v>
       </c>
       <c r="R74" t="n">
-        <v>7096931</v>
+        <v>7097009</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8212,55 +8217,50 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126936879</v>
+        <v>126936896</v>
       </c>
       <c r="B75" t="n">
-        <v>97245</v>
+        <v>79011</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8270,10 +8270,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>690490</v>
+        <v>690482</v>
       </c>
       <c r="R75" t="n">
-        <v>7096937</v>
+        <v>7096931</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8336,10 +8336,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126927024</v>
+        <v>126927943</v>
       </c>
       <c r="B76" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8367,14 +8367,14 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>690503</v>
+        <v>690585</v>
       </c>
       <c r="R76" t="n">
-        <v>7097060</v>
+        <v>7096888</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8433,10 +8433,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126927395</v>
+        <v>126937629</v>
       </c>
       <c r="B77" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8464,14 +8464,14 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>690542</v>
+        <v>690504</v>
       </c>
       <c r="R77" t="n">
-        <v>7096989</v>
+        <v>7096980</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8518,22 +8518,26 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126937629</v>
+        <v>126927024</v>
       </c>
       <c r="B78" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8561,14 +8565,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>690504</v>
+        <v>690503</v>
       </c>
       <c r="R78" t="n">
-        <v>7096980</v>
+        <v>7097060</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8615,26 +8619,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126927943</v>
+        <v>126927395</v>
       </c>
       <c r="B79" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8662,14 +8662,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>690585</v>
+        <v>690542</v>
       </c>
       <c r="R79" t="n">
-        <v>7096888</v>
+        <v>7096989</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8728,10 +8728,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126927691</v>
+        <v>126936909</v>
       </c>
       <c r="B80" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8759,17 +8759,17 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>690577</v>
+        <v>690590</v>
       </c>
       <c r="R80" t="n">
-        <v>7096975</v>
+        <v>7096893</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8813,22 +8813,26 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126931564</v>
+        <v>126937622</v>
       </c>
       <c r="B81" t="n">
-        <v>79012</v>
+        <v>79011</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8836,37 +8840,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>690624</v>
+        <v>690620</v>
       </c>
       <c r="R81" t="n">
-        <v>7096879</v>
+        <v>7096858</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8910,12 +8914,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -8926,10 +8930,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126937622</v>
+        <v>126927691</v>
       </c>
       <c r="B82" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8957,14 +8961,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>690620</v>
+        <v>690577</v>
       </c>
       <c r="R82" t="n">
-        <v>7096858</v>
+        <v>7096975</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9011,26 +9015,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
         <v>126926723</v>
       </c>
       <c r="B83" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9124,48 +9124,48 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126927343</v>
+        <v>126931564</v>
       </c>
       <c r="B84" t="n">
-        <v>98361</v>
+        <v>79043</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>690544</v>
+        <v>690624</v>
       </c>
       <c r="R84" t="n">
-        <v>7097007</v>
+        <v>7096879</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9209,60 +9209,64 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126936909</v>
+        <v>126927343</v>
       </c>
       <c r="B85" t="n">
-        <v>78980</v>
+        <v>98436</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>690590</v>
+        <v>690544</v>
       </c>
       <c r="R85" t="n">
-        <v>7096893</v>
+        <v>7097007</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9306,26 +9310,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126936901</v>
+        <v>126936899</v>
       </c>
       <c r="B86" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>690623</v>
+        <v>690607</v>
       </c>
       <c r="R86" t="n">
-        <v>7096862</v>
+        <v>7097019</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9426,7 +9426,7 @@
         <v>126927737</v>
       </c>
       <c r="B87" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9520,10 +9520,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126936899</v>
+        <v>126936901</v>
       </c>
       <c r="B88" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9555,10 +9555,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>690607</v>
+        <v>690623</v>
       </c>
       <c r="R88" t="n">
-        <v>7097019</v>
+        <v>7096862</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9621,57 +9621,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126936892</v>
+        <v>126936913</v>
       </c>
       <c r="B89" t="n">
-        <v>98361</v>
+        <v>92609</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>690619</v>
+        <v>690466</v>
       </c>
       <c r="R89" t="n">
-        <v>7096955</v>
+        <v>7096945</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9712,7 +9700,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9738,7 +9725,7 @@
         <v>126936895</v>
       </c>
       <c r="B90" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9836,10 +9823,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126937616</v>
+        <v>126926697</v>
       </c>
       <c r="B91" t="n">
-        <v>79598</v>
+        <v>79011</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9847,34 +9834,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>690516</v>
+        <v>690438</v>
       </c>
       <c r="R91" t="n">
-        <v>7096946</v>
+        <v>7097148</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -9921,64 +9908,60 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126936913</v>
+        <v>126937616</v>
       </c>
       <c r="B92" t="n">
-        <v>92535</v>
+        <v>79629</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>690466</v>
+        <v>690516</v>
       </c>
       <c r="R92" t="n">
-        <v>7096945</v>
+        <v>7096946</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10022,12 +10005,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10038,48 +10021,60 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126926697</v>
+        <v>126936892</v>
       </c>
       <c r="B93" t="n">
-        <v>78980</v>
+        <v>98436</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>690438</v>
+        <v>690619</v>
       </c>
       <c r="R93" t="n">
-        <v>7097148</v>
+        <v>7096955</v>
       </c>
       <c r="S93" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10117,28 +10112,33 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126936884</v>
+        <v>126931572</v>
       </c>
       <c r="B94" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10165,31 +10165,27 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>690609</v>
+        <v>690665</v>
       </c>
       <c r="R94" t="n">
-        <v>7096953</v>
+        <v>7096920</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10237,12 +10233,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10253,10 +10249,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126937619</v>
+        <v>126936884</v>
       </c>
       <c r="B95" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10281,20 +10277,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>690621</v>
+        <v>690609</v>
       </c>
       <c r="R95" t="n">
-        <v>7096899</v>
+        <v>7096953</v>
       </c>
       <c r="S95" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10332,18 +10344,19 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10354,10 +10367,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126931572</v>
+        <v>126937619</v>
       </c>
       <c r="B96" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10382,32 +10395,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>690665</v>
+        <v>690621</v>
       </c>
       <c r="R96" t="n">
-        <v>7096920</v>
+        <v>7096899</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10445,19 +10446,18 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10468,45 +10468,61 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126936898</v>
+        <v>126931569</v>
       </c>
       <c r="B97" t="n">
-        <v>78980</v>
+        <v>98436</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>690576</v>
+        <v>690550</v>
       </c>
       <c r="R97" t="n">
-        <v>7096919</v>
+        <v>7097011</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10547,18 +10563,19 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10569,61 +10586,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126931569</v>
+        <v>126936880</v>
       </c>
       <c r="B98" t="n">
-        <v>98361</v>
+        <v>78770</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>690550</v>
+        <v>690619</v>
       </c>
       <c r="R98" t="n">
-        <v>7097011</v>
+        <v>7097003</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10664,19 +10665,18 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10687,10 +10687,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126927128</v>
+        <v>126936898</v>
       </c>
       <c r="B99" t="n">
-        <v>80083</v>
+        <v>79011</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10698,37 +10698,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>690517</v>
+        <v>690576</v>
       </c>
       <c r="R99" t="n">
-        <v>7097014</v>
+        <v>7096919</v>
       </c>
       <c r="S99" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10772,22 +10772,26 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY99" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126936880</v>
+        <v>126937627</v>
       </c>
       <c r="B100" t="n">
-        <v>78739</v>
+        <v>79011</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10795,37 +10799,37 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>690619</v>
+        <v>690522</v>
       </c>
       <c r="R100" t="n">
-        <v>7097003</v>
+        <v>7096919</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10869,12 +10873,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10885,10 +10889,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126937627</v>
+        <v>126927128</v>
       </c>
       <c r="B101" t="n">
-        <v>78980</v>
+        <v>80114</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10896,34 +10900,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>690522</v>
+        <v>690517</v>
       </c>
       <c r="R101" t="n">
-        <v>7096919</v>
+        <v>7097014</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -10970,48 +10974,44 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY101" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126927292</v>
+        <v>126927465</v>
       </c>
       <c r="B102" t="n">
-        <v>98361</v>
+        <v>79011</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11021,10 +11021,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>690530</v>
+        <v>690596</v>
       </c>
       <c r="R102" t="n">
-        <v>7097014</v>
+        <v>7097023</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -11083,48 +11083,48 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126927178</v>
+        <v>126931566</v>
       </c>
       <c r="B103" t="n">
-        <v>80112</v>
+        <v>78769</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>690520</v>
+        <v>690621</v>
       </c>
       <c r="R103" t="n">
-        <v>7097024</v>
+        <v>7096855</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11168,22 +11168,26 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY103" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126927139</v>
+        <v>126931577</v>
       </c>
       <c r="B104" t="n">
-        <v>80112</v>
+        <v>80049</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11191,37 +11195,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6462</v>
+        <v>6457</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>690515</v>
+        <v>690656</v>
       </c>
       <c r="R104" t="n">
-        <v>7097011</v>
+        <v>7096927</v>
       </c>
       <c r="S104" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11265,44 +11269,48 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY104" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126927465</v>
+        <v>126927178</v>
       </c>
       <c r="B105" t="n">
-        <v>78980</v>
+        <v>80143</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11312,10 +11320,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>690596</v>
+        <v>690520</v>
       </c>
       <c r="R105" t="n">
-        <v>7097023</v>
+        <v>7097024</v>
       </c>
       <c r="S105" t="n">
         <v>15</v>
@@ -11377,7 +11385,7 @@
         <v>126927184</v>
       </c>
       <c r="B106" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11471,10 +11479,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126931577</v>
+        <v>126927139</v>
       </c>
       <c r="B107" t="n">
-        <v>80018</v>
+        <v>80143</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11482,37 +11490,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6457</v>
+        <v>6462</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>690656</v>
+        <v>690515</v>
       </c>
       <c r="R107" t="n">
-        <v>7096927</v>
+        <v>7097011</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11556,64 +11564,60 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY107" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126931566</v>
+        <v>126927292</v>
       </c>
       <c r="B108" t="n">
-        <v>78738</v>
+        <v>98436</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>690621</v>
+        <v>690530</v>
       </c>
       <c r="R108" t="n">
-        <v>7096855</v>
+        <v>7097014</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11657,19 +11661,15 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY108" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30467-2025 artfynd.xlsx
+++ b/artfynd/A 30467-2025 artfynd.xlsx
@@ -675,49 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126909580</v>
+        <v>126919968</v>
       </c>
       <c r="B2" t="n">
-        <v>98436</v>
+        <v>80021</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Rislidstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>690493</v>
+        <v>690349</v>
       </c>
       <c r="R2" t="n">
-        <v>7097055</v>
+        <v>7097128</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -747,19 +743,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
+          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -790,45 +776,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126919968</v>
+        <v>126909580</v>
       </c>
       <c r="B3" t="n">
-        <v>80018</v>
+        <v>98442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rislidstjärnarna, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>690349</v>
+        <v>690493</v>
       </c>
       <c r="R3" t="n">
-        <v>7097128</v>
+        <v>7097055</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,9 +848,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,12 +875,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emil Lindgren, Hedda Bring, Lotta Ihse, Eleonor Johansson, Fredrik Wilde, Nicklas Gustavsson, Isac Enetjärn, Malin Löfgren</t>
+          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1008,7 +1008,7 @@
         <v>126917563</v>
       </c>
       <c r="B5" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>126917550</v>
       </c>
       <c r="B6" t="n">
-        <v>80150</v>
+        <v>80153</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>126919976</v>
       </c>
       <c r="B7" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emil Lindgren, Hedda Bring, Lotta Ihse, Eleonor Johansson, Fredrik Wilde, Nicklas Gustavsson, Isac Enetjärn, Malin Löfgren</t>
+          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1311,7 +1311,7 @@
         <v>126917539</v>
       </c>
       <c r="B8" t="n">
-        <v>91330</v>
+        <v>91336</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126919966</v>
+        <v>126917545</v>
       </c>
       <c r="B9" t="n">
-        <v>91330</v>
+        <v>80021</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1420,38 +1420,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1205</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rislidstjärnarna, Ång</t>
+          <t>Rislidtjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>690349</v>
+        <v>690344</v>
       </c>
       <c r="R9" t="n">
-        <v>7097128</v>
+        <v>7097126</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1498,12 +1494,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Emil Lindgren, Hedda Bring, Lotta Ihse, Eleonor Johansson, Fredrik Wilde, Nicklas Gustavsson, Isac Enetjärn, Malin Löfgren</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1514,10 +1510,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126917545</v>
+        <v>126919966</v>
       </c>
       <c r="B10" t="n">
-        <v>80018</v>
+        <v>91336</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1525,34 +1521,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>1205</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rislidtjärnarna, Ång</t>
+          <t>Rislidstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>690344</v>
+        <v>690349</v>
       </c>
       <c r="R10" t="n">
-        <v>7097126</v>
+        <v>7097128</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1599,12 +1599,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1618,7 +1618,7 @@
         <v>126909288</v>
       </c>
       <c r="B11" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>126909413</v>
       </c>
       <c r="B12" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>126909538</v>
       </c>
       <c r="B13" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>126918516</v>
       </c>
       <c r="B14" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>126917549</v>
       </c>
       <c r="B15" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>126918507</v>
       </c>
       <c r="B16" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>126909505</v>
       </c>
       <c r="B18" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>126927367</v>
       </c>
       <c r="B19" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2598,45 +2598,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126936912</v>
+        <v>126926856</v>
       </c>
       <c r="B20" t="n">
-        <v>92609</v>
+        <v>78773</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>N Johannesbomyran, N Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>690392</v>
+        <v>690563</v>
       </c>
       <c r="R20" t="n">
-        <v>7097038</v>
+        <v>7096856</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2683,26 +2683,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>126927356</v>
       </c>
       <c r="B21" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2796,45 +2792,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126931573</v>
+        <v>126936912</v>
       </c>
       <c r="B22" t="n">
-        <v>98436</v>
+        <v>92615</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>690578</v>
+        <v>690392</v>
       </c>
       <c r="R22" t="n">
-        <v>7096991</v>
+        <v>7097038</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2881,12 +2877,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2897,45 +2893,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126926856</v>
+        <v>126931573</v>
       </c>
       <c r="B23" t="n">
-        <v>78770</v>
+        <v>98442</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>N Johannesbomyran, N Johannesbomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>690563</v>
+        <v>690578</v>
       </c>
       <c r="R23" t="n">
-        <v>7096856</v>
+        <v>7096991</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2982,22 +2978,26 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>126927661</v>
       </c>
       <c r="B24" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>126937624</v>
       </c>
       <c r="B25" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>126927842</v>
       </c>
       <c r="B26" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>126936886</v>
       </c>
       <c r="B27" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3407,10 +3407,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126936889</v>
+        <v>126936890</v>
       </c>
       <c r="B28" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3445,11 +3445,7 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3458,10 +3454,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>690595</v>
+        <v>690564</v>
       </c>
       <c r="R28" t="n">
-        <v>7096886</v>
+        <v>7096907</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3525,10 +3521,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126936890</v>
+        <v>126936889</v>
       </c>
       <c r="B29" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3555,7 +3551,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3563,7 +3559,11 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
@@ -3572,10 +3572,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>690564</v>
+        <v>690595</v>
       </c>
       <c r="R29" t="n">
-        <v>7096907</v>
+        <v>7096886</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3642,7 +3642,7 @@
         <v>126931565</v>
       </c>
       <c r="B30" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>126927550</v>
       </c>
       <c r="B31" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3837,45 +3837,61 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126936897</v>
+        <v>126936883</v>
       </c>
       <c r="B32" t="n">
-        <v>79011</v>
+        <v>98442</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>690544</v>
+        <v>690668</v>
       </c>
       <c r="R32" t="n">
-        <v>7096906</v>
+        <v>7096918</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3916,6 +3932,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3938,48 +3955,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126937621</v>
+        <v>126936897</v>
       </c>
       <c r="B33" t="n">
-        <v>98436</v>
+        <v>79014</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>690635</v>
+        <v>690544</v>
       </c>
       <c r="R33" t="n">
-        <v>7096944</v>
+        <v>7096906</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4009,11 +4026,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ca 40 bladrosetter</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4028,12 +4040,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4044,10 +4056,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126936883</v>
+        <v>126937621</v>
       </c>
       <c r="B34" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4072,36 +4084,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>690668</v>
+        <v>690635</v>
       </c>
       <c r="R34" t="n">
-        <v>7096918</v>
+        <v>7096944</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4133,25 +4129,29 @@
           <t>2025-07-26</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ca 40 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4165,7 +4165,7 @@
         <v>126936888</v>
       </c>
       <c r="B35" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4276,10 +4276,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126931567</v>
+        <v>126937620</v>
       </c>
       <c r="B36" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4304,32 +4304,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>690686</v>
+        <v>690612</v>
       </c>
       <c r="R36" t="n">
-        <v>7096928</v>
+        <v>7096930</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4359,6 +4351,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Cirka 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4374,12 +4371,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4390,10 +4387,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126937620</v>
+        <v>126931567</v>
       </c>
       <c r="B37" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4418,24 +4415,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>690612</v>
+        <v>690686</v>
       </c>
       <c r="R37" t="n">
-        <v>7096930</v>
+        <v>7096928</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4465,11 +4470,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Cirka 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4485,12 +4485,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4501,10 +4501,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126926531</v>
+        <v>126936910</v>
       </c>
       <c r="B38" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4532,14 +4532,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>690376</v>
+        <v>690572</v>
       </c>
       <c r="R38" t="n">
-        <v>7097225</v>
+        <v>7096932</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4586,57 +4586,73 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126936900</v>
+        <v>126936887</v>
       </c>
       <c r="B39" t="n">
-        <v>79011</v>
+        <v>98442</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>690663</v>
+        <v>690632</v>
       </c>
       <c r="R39" t="n">
-        <v>7096854</v>
+        <v>7096922</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4677,6 +4693,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4699,10 +4716,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126936910</v>
+        <v>126926531</v>
       </c>
       <c r="B40" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4730,14 +4747,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>690572</v>
+        <v>690376</v>
       </c>
       <c r="R40" t="n">
-        <v>7096932</v>
+        <v>7097225</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4784,73 +4801,57 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126936887</v>
+        <v>126936900</v>
       </c>
       <c r="B41" t="n">
-        <v>98436</v>
+        <v>79014</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>690632</v>
+        <v>690663</v>
       </c>
       <c r="R41" t="n">
-        <v>7096922</v>
+        <v>7096854</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4891,7 +4892,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4917,7 +4917,7 @@
         <v>126926789</v>
       </c>
       <c r="B42" t="n">
-        <v>91339</v>
+        <v>91345</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>126936894</v>
       </c>
       <c r="B43" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>126926859</v>
       </c>
       <c r="B44" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>126931570</v>
       </c>
       <c r="B45" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
         <v>126936882</v>
       </c>
       <c r="B46" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5424,10 +5424,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126928173</v>
+        <v>126936877</v>
       </c>
       <c r="B47" t="n">
-        <v>79011</v>
+        <v>79632</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5435,37 +5435,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>690547</v>
+        <v>690378</v>
       </c>
       <c r="R47" t="n">
-        <v>7096876</v>
+        <v>7096984</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5509,60 +5509,76 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126937632</v>
+        <v>126936885</v>
       </c>
       <c r="B48" t="n">
-        <v>79011</v>
+        <v>98442</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>690454</v>
+        <v>690596</v>
       </c>
       <c r="R48" t="n">
-        <v>7097036</v>
+        <v>7097007</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5600,18 +5616,19 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5622,10 +5639,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126936911</v>
+        <v>126928173</v>
       </c>
       <c r="B49" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5653,17 +5670,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>690481</v>
+        <v>690547</v>
       </c>
       <c r="R49" t="n">
-        <v>7097028</v>
+        <v>7096876</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5707,26 +5724,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126937623</v>
+        <v>126937632</v>
       </c>
       <c r="B50" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5758,10 +5771,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>690707</v>
+        <v>690454</v>
       </c>
       <c r="R50" t="n">
-        <v>7096903</v>
+        <v>7097036</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5824,10 +5837,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126936877</v>
+        <v>126936911</v>
       </c>
       <c r="B51" t="n">
-        <v>79629</v>
+        <v>79014</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5835,21 +5848,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5859,10 +5872,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>690378</v>
+        <v>690481</v>
       </c>
       <c r="R51" t="n">
-        <v>7096984</v>
+        <v>7097028</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5925,60 +5938,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126936885</v>
+        <v>126937623</v>
       </c>
       <c r="B52" t="n">
-        <v>98436</v>
+        <v>79014</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>690596</v>
+        <v>690707</v>
       </c>
       <c r="R52" t="n">
-        <v>7097007</v>
+        <v>7096903</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6016,19 +6017,18 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6042,7 +6042,7 @@
         <v>126927000</v>
       </c>
       <c r="B53" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>126928117</v>
       </c>
       <c r="B54" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>126927086</v>
       </c>
       <c r="B55" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>126936878</v>
       </c>
       <c r="B56" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         <v>126931571</v>
       </c>
       <c r="B57" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6545,10 +6545,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126926624</v>
+        <v>126936881</v>
       </c>
       <c r="B58" t="n">
-        <v>79011</v>
+        <v>78773</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6556,37 +6556,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>690399</v>
+        <v>690617</v>
       </c>
       <c r="R58" t="n">
-        <v>7097170</v>
+        <v>7096851</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6630,22 +6630,26 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126926566</v>
+        <v>126926624</v>
       </c>
       <c r="B59" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6677,10 +6681,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>690362</v>
+        <v>690399</v>
       </c>
       <c r="R59" t="n">
-        <v>7097210</v>
+        <v>7097170</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6739,10 +6743,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126937630</v>
+        <v>126926566</v>
       </c>
       <c r="B60" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6770,14 +6774,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>690480</v>
+        <v>690362</v>
       </c>
       <c r="R60" t="n">
-        <v>7096994</v>
+        <v>7097210</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6824,26 +6828,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126927108</v>
+        <v>126937630</v>
       </c>
       <c r="B61" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6871,14 +6871,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>690542</v>
+        <v>690480</v>
       </c>
       <c r="R61" t="n">
-        <v>7097030</v>
+        <v>7096994</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6925,22 +6925,26 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126927426</v>
+        <v>126927108</v>
       </c>
       <c r="B62" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6972,10 +6976,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>690560</v>
+        <v>690542</v>
       </c>
       <c r="R62" t="n">
-        <v>7097019</v>
+        <v>7097030</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7034,10 +7038,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126936881</v>
+        <v>126927426</v>
       </c>
       <c r="B63" t="n">
-        <v>78770</v>
+        <v>79014</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7045,37 +7049,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>690617</v>
+        <v>690560</v>
       </c>
       <c r="R63" t="n">
-        <v>7096851</v>
+        <v>7097019</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7119,48 +7123,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126927067</v>
+        <v>126927409</v>
       </c>
       <c r="B64" t="n">
-        <v>79011</v>
+        <v>98442</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7170,13 +7170,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>690536</v>
+        <v>690545</v>
       </c>
       <c r="R64" t="n">
-        <v>7097045</v>
+        <v>7097003</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7232,10 +7232,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126926457</v>
+        <v>126927067</v>
       </c>
       <c r="B65" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7267,13 +7267,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>690374</v>
+        <v>690536</v>
       </c>
       <c r="R65" t="n">
-        <v>7097232</v>
+        <v>7097045</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7329,10 +7329,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126931576</v>
+        <v>126926457</v>
       </c>
       <c r="B66" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7360,17 +7360,17 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>690565</v>
+        <v>690374</v>
       </c>
       <c r="R66" t="n">
-        <v>7096992</v>
+        <v>7097232</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7414,61 +7414,57 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126936893</v>
+        <v>126931576</v>
       </c>
       <c r="B67" t="n">
-        <v>98436</v>
+        <v>79014</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>690658</v>
+        <v>690565</v>
       </c>
       <c r="R67" t="n">
-        <v>7096938</v>
+        <v>7096992</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7515,12 +7511,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7531,10 +7527,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126927409</v>
+        <v>126936893</v>
       </c>
       <c r="B68" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7562,17 +7558,17 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>690545</v>
+        <v>690658</v>
       </c>
       <c r="R68" t="n">
-        <v>7097003</v>
+        <v>7096938</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7616,22 +7612,26 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
         <v>126926526</v>
       </c>
       <c r="B69" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>126936908</v>
       </c>
       <c r="B70" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>126927324</v>
       </c>
       <c r="B71" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7923,60 +7923,48 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126936891</v>
+        <v>126927191</v>
       </c>
       <c r="B72" t="n">
-        <v>98436</v>
+        <v>79014</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>690644</v>
+        <v>690524</v>
       </c>
       <c r="R72" t="n">
-        <v>7096931</v>
+        <v>7097009</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8014,55 +8002,50 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126936879</v>
+        <v>126936896</v>
       </c>
       <c r="B73" t="n">
-        <v>97320</v>
+        <v>79014</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8072,10 +8055,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>690490</v>
+        <v>690482</v>
       </c>
       <c r="R73" t="n">
-        <v>7096937</v>
+        <v>7096931</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8138,48 +8121,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126927191</v>
+        <v>126936879</v>
       </c>
       <c r="B74" t="n">
-        <v>79011</v>
+        <v>97326</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>690524</v>
+        <v>690490</v>
       </c>
       <c r="R74" t="n">
-        <v>7097009</v>
+        <v>7096937</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8223,54 +8206,70 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126936896</v>
+        <v>126936891</v>
       </c>
       <c r="B75" t="n">
-        <v>79011</v>
+        <v>98442</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>690482</v>
+        <v>690644</v>
       </c>
       <c r="R75" t="n">
         <v>7096931</v>
@@ -8314,6 +8313,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8339,7 +8339,7 @@
         <v>126927943</v>
       </c>
       <c r="B76" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>126937629</v>
       </c>
       <c r="B77" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>126927024</v>
       </c>
       <c r="B78" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>126927395</v>
       </c>
       <c r="B79" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>126936909</v>
       </c>
       <c r="B80" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8832,7 +8832,7 @@
         <v>126937622</v>
       </c>
       <c r="B81" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>126927691</v>
       </c>
       <c r="B82" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9027,10 +9027,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126926723</v>
+        <v>126931564</v>
       </c>
       <c r="B83" t="n">
-        <v>78770</v>
+        <v>79046</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9038,37 +9038,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>690433</v>
+        <v>690624</v>
       </c>
       <c r="R83" t="n">
-        <v>7097136</v>
+        <v>7096879</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9112,60 +9112,64 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126931564</v>
+        <v>126927343</v>
       </c>
       <c r="B84" t="n">
-        <v>79043</v>
+        <v>98442</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>690624</v>
+        <v>690544</v>
       </c>
       <c r="R84" t="n">
-        <v>7096879</v>
+        <v>7097007</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9209,48 +9213,44 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126927343</v>
+        <v>126926723</v>
       </c>
       <c r="B85" t="n">
-        <v>98436</v>
+        <v>78773</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9260,10 +9260,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>690544</v>
+        <v>690433</v>
       </c>
       <c r="R85" t="n">
-        <v>7097007</v>
+        <v>7097136</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9322,10 +9322,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126936899</v>
+        <v>126927737</v>
       </c>
       <c r="B86" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9353,17 +9353,17 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>690607</v>
+        <v>690623</v>
       </c>
       <c r="R86" t="n">
-        <v>7097019</v>
+        <v>7096931</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9407,26 +9407,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126927737</v>
+        <v>126936899</v>
       </c>
       <c r="B87" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9454,17 +9450,17 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>690623</v>
+        <v>690607</v>
       </c>
       <c r="R87" t="n">
-        <v>7096931</v>
+        <v>7097019</v>
       </c>
       <c r="S87" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9508,22 +9504,26 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
         <v>126936901</v>
       </c>
       <c r="B88" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9621,32 +9621,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126936913</v>
+        <v>126936895</v>
       </c>
       <c r="B89" t="n">
-        <v>92609</v>
+        <v>79014</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9656,7 +9656,7 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>690466</v>
+        <v>690445</v>
       </c>
       <c r="R89" t="n">
         <v>7096945</v>
@@ -9722,10 +9722,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126936895</v>
+        <v>126926697</v>
       </c>
       <c r="B90" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9753,17 +9753,17 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>690445</v>
+        <v>690438</v>
       </c>
       <c r="R90" t="n">
-        <v>7096945</v>
+        <v>7097148</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9807,64 +9807,60 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126926697</v>
+        <v>126936913</v>
       </c>
       <c r="B91" t="n">
-        <v>79011</v>
+        <v>92615</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>690438</v>
+        <v>690466</v>
       </c>
       <c r="R91" t="n">
-        <v>7097148</v>
+        <v>7096945</v>
       </c>
       <c r="S91" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9908,22 +9904,26 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
         <v>126937616</v>
       </c>
       <c r="B92" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>126936892</v>
       </c>
       <c r="B93" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10135,60 +10135,48 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126931572</v>
+        <v>126927128</v>
       </c>
       <c r="B94" t="n">
-        <v>98436</v>
+        <v>80117</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>690665</v>
+        <v>690517</v>
       </c>
       <c r="R94" t="n">
-        <v>7096920</v>
+        <v>7097014</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10226,33 +10214,28 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126936884</v>
+        <v>126937619</v>
       </c>
       <c r="B95" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10277,36 +10260,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>690609</v>
+        <v>690621</v>
       </c>
       <c r="R95" t="n">
-        <v>7096953</v>
+        <v>7096899</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10344,19 +10311,18 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10367,10 +10333,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126937619</v>
+        <v>126931572</v>
       </c>
       <c r="B96" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10395,20 +10361,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>690621</v>
+        <v>690665</v>
       </c>
       <c r="R96" t="n">
-        <v>7096899</v>
+        <v>7096920</v>
       </c>
       <c r="S96" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10446,18 +10424,19 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10471,7 +10450,7 @@
         <v>126931569</v>
       </c>
       <c r="B97" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10586,45 +10565,61 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126936880</v>
+        <v>126936884</v>
       </c>
       <c r="B98" t="n">
-        <v>78770</v>
+        <v>98442</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>690619</v>
+        <v>690609</v>
       </c>
       <c r="R98" t="n">
-        <v>7097003</v>
+        <v>7096953</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10665,6 +10660,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10687,10 +10683,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126936898</v>
+        <v>126936880</v>
       </c>
       <c r="B99" t="n">
-        <v>79011</v>
+        <v>78773</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10698,21 +10694,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10722,10 +10718,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>690576</v>
+        <v>690619</v>
       </c>
       <c r="R99" t="n">
-        <v>7096919</v>
+        <v>7097003</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10788,10 +10784,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126937627</v>
+        <v>126936898</v>
       </c>
       <c r="B100" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10819,17 +10815,17 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>690522</v>
+        <v>690576</v>
       </c>
       <c r="R100" t="n">
         <v>7096919</v>
       </c>
       <c r="S100" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10873,12 +10869,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10889,10 +10885,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126927128</v>
+        <v>126937627</v>
       </c>
       <c r="B101" t="n">
-        <v>80114</v>
+        <v>79014</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10900,34 +10896,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>690517</v>
+        <v>690522</v>
       </c>
       <c r="R101" t="n">
-        <v>7097014</v>
+        <v>7096919</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -10974,60 +10970,64 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY101" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126927465</v>
+        <v>126931577</v>
       </c>
       <c r="B102" t="n">
-        <v>79011</v>
+        <v>80052</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6457</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>690596</v>
+        <v>690656</v>
       </c>
       <c r="R102" t="n">
-        <v>7097023</v>
+        <v>7096927</v>
       </c>
       <c r="S102" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11071,60 +11071,64 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY102" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126931566</v>
+        <v>126927178</v>
       </c>
       <c r="B103" t="n">
-        <v>78769</v>
+        <v>80146</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>690621</v>
+        <v>690520</v>
       </c>
       <c r="R103" t="n">
-        <v>7096855</v>
+        <v>7097024</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11168,64 +11172,60 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY103" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126931577</v>
+        <v>126927184</v>
       </c>
       <c r="B104" t="n">
-        <v>80049</v>
+        <v>80117</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6457</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>690656</v>
+        <v>690520</v>
       </c>
       <c r="R104" t="n">
-        <v>7096927</v>
+        <v>7097024</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11269,26 +11269,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY104" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126927178</v>
+        <v>126927139</v>
       </c>
       <c r="B105" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11320,10 +11316,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>690520</v>
+        <v>690515</v>
       </c>
       <c r="R105" t="n">
-        <v>7097024</v>
+        <v>7097011</v>
       </c>
       <c r="S105" t="n">
         <v>15</v>
@@ -11382,10 +11378,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126927184</v>
+        <v>126931566</v>
       </c>
       <c r="B106" t="n">
-        <v>80114</v>
+        <v>78772</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11393,37 +11389,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>690520</v>
+        <v>690621</v>
       </c>
       <c r="R106" t="n">
-        <v>7097024</v>
+        <v>7096855</v>
       </c>
       <c r="S106" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11467,44 +11463,48 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY106" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126927139</v>
+        <v>126927292</v>
       </c>
       <c r="B107" t="n">
-        <v>80143</v>
+        <v>98442</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11514,10 +11514,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>690515</v>
+        <v>690530</v>
       </c>
       <c r="R107" t="n">
-        <v>7097011</v>
+        <v>7097014</v>
       </c>
       <c r="S107" t="n">
         <v>15</v>
@@ -11576,32 +11576,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126927292</v>
+        <v>126927465</v>
       </c>
       <c r="B108" t="n">
-        <v>98436</v>
+        <v>79014</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11611,10 +11611,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>690530</v>
+        <v>690596</v>
       </c>
       <c r="R108" t="n">
-        <v>7097014</v>
+        <v>7097023</v>
       </c>
       <c r="S108" t="n">
         <v>15</v>

--- a/artfynd/A 30467-2025 artfynd.xlsx
+++ b/artfynd/A 30467-2025 artfynd.xlsx
@@ -1005,32 +1005,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126917563</v>
+        <v>126917550</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>80153</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>690509</v>
+        <v>690515</v>
       </c>
       <c r="R5" t="n">
-        <v>7097052</v>
+        <v>7097014</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,32 +1106,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126917550</v>
+        <v>126917563</v>
       </c>
       <c r="B6" t="n">
-        <v>80153</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>690515</v>
+        <v>690509</v>
       </c>
       <c r="R6" t="n">
-        <v>7097014</v>
+        <v>7097052</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126917545</v>
+        <v>126919966</v>
       </c>
       <c r="B9" t="n">
-        <v>80021</v>
+        <v>91336</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1420,34 +1420,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>1205</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rislidtjärnarna, Ång</t>
+          <t>Rislidstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>690344</v>
+        <v>690349</v>
       </c>
       <c r="R9" t="n">
-        <v>7097126</v>
+        <v>7097128</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,12 +1498,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1510,10 +1514,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126919966</v>
+        <v>126917545</v>
       </c>
       <c r="B10" t="n">
-        <v>91336</v>
+        <v>80021</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1521,38 +1525,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1205</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rislidstjärnarna, Ång</t>
+          <t>Rislidtjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>690349</v>
+        <v>690344</v>
       </c>
       <c r="R10" t="n">
-        <v>7097128</v>
+        <v>7097126</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1599,12 +1599,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -2598,10 +2598,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126926856</v>
+        <v>126927356</v>
       </c>
       <c r="B20" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2609,37 +2609,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>N Johannesbomyran, N Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>690563</v>
+        <v>690516</v>
       </c>
       <c r="R20" t="n">
-        <v>7096856</v>
+        <v>7096990</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2683,60 +2683,60 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126927356</v>
+        <v>126936912</v>
       </c>
       <c r="B21" t="n">
-        <v>79014</v>
+        <v>92615</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>690516</v>
+        <v>690392</v>
       </c>
       <c r="R21" t="n">
-        <v>7096990</v>
+        <v>7097038</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2780,57 +2780,61 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126936912</v>
+        <v>126931573</v>
       </c>
       <c r="B22" t="n">
-        <v>92615</v>
+        <v>98442</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>690392</v>
+        <v>690578</v>
       </c>
       <c r="R22" t="n">
-        <v>7097038</v>
+        <v>7096991</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2877,12 +2881,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2893,45 +2897,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126931573</v>
+        <v>126926856</v>
       </c>
       <c r="B23" t="n">
-        <v>98442</v>
+        <v>78773</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>N Johannesbomyran, N Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>690578</v>
+        <v>690563</v>
       </c>
       <c r="R23" t="n">
-        <v>7096991</v>
+        <v>7096856</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2978,23 +2982,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126927661</v>
+        <v>126937624</v>
       </c>
       <c r="B24" t="n">
         <v>79014</v>
@@ -3025,14 +3025,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>690574</v>
+        <v>690656</v>
       </c>
       <c r="R24" t="n">
-        <v>7096978</v>
+        <v>7096868</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3079,19 +3079,23 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126937624</v>
+        <v>126927661</v>
       </c>
       <c r="B25" t="n">
         <v>79014</v>
@@ -3122,14 +3126,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>690656</v>
+        <v>690574</v>
       </c>
       <c r="R25" t="n">
-        <v>7096868</v>
+        <v>7096978</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3176,19 +3180,15 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3289,61 +3289,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126936886</v>
+        <v>126931565</v>
       </c>
       <c r="B27" t="n">
-        <v>98442</v>
+        <v>78773</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>690607</v>
+        <v>690620</v>
       </c>
       <c r="R27" t="n">
-        <v>7097014</v>
+        <v>7096859</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3384,19 +3368,18 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3407,7 +3390,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126936890</v>
+        <v>126936889</v>
       </c>
       <c r="B28" t="n">
         <v>98442</v>
@@ -3437,7 +3420,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3445,7 +3428,11 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3454,10 +3441,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>690564</v>
+        <v>690595</v>
       </c>
       <c r="R28" t="n">
-        <v>7096907</v>
+        <v>7096886</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3521,7 +3508,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126936889</v>
+        <v>126936890</v>
       </c>
       <c r="B29" t="n">
         <v>98442</v>
@@ -3551,7 +3538,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3559,11 +3546,7 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
@@ -3572,10 +3555,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>690595</v>
+        <v>690564</v>
       </c>
       <c r="R29" t="n">
-        <v>7096886</v>
+        <v>7096907</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3639,45 +3622,61 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126931565</v>
+        <v>126936886</v>
       </c>
       <c r="B30" t="n">
-        <v>78773</v>
+        <v>98442</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>690620</v>
+        <v>690607</v>
       </c>
       <c r="R30" t="n">
-        <v>7096859</v>
+        <v>7097014</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3718,18 +3717,19 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3740,7 +3740,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126927550</v>
+        <v>126936897</v>
       </c>
       <c r="B31" t="n">
         <v>79014</v>
@@ -3771,17 +3771,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>690574</v>
+        <v>690544</v>
       </c>
       <c r="R31" t="n">
-        <v>7096994</v>
+        <v>7096906</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3825,76 +3825,64 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126936883</v>
+        <v>126927550</v>
       </c>
       <c r="B32" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>690668</v>
+        <v>690574</v>
       </c>
       <c r="R32" t="n">
-        <v>7096918</v>
+        <v>7096994</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3932,71 +3920,66 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126936897</v>
+        <v>126937621</v>
       </c>
       <c r="B33" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>690544</v>
+        <v>690635</v>
       </c>
       <c r="R33" t="n">
-        <v>7096906</v>
+        <v>7096944</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4026,6 +4009,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ca 40 bladrosetter</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4040,12 +4028,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4056,7 +4044,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126937621</v>
+        <v>126936883</v>
       </c>
       <c r="B34" t="n">
         <v>98442</v>
@@ -4084,20 +4072,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>690635</v>
+        <v>690668</v>
       </c>
       <c r="R34" t="n">
-        <v>7096944</v>
+        <v>7096918</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4129,29 +4133,25 @@
           <t>2025-07-26</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ca 40 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4162,7 +4162,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126936888</v>
+        <v>126931567</v>
       </c>
       <c r="B35" t="n">
         <v>98442</v>
@@ -4192,12 +4192,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -4205,14 +4205,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>690639</v>
+        <v>690686</v>
       </c>
       <c r="R35" t="n">
-        <v>7096927</v>
+        <v>7096928</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4260,12 +4260,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4276,7 +4276,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126937620</v>
+        <v>126936888</v>
       </c>
       <c r="B36" t="n">
         <v>98442</v>
@@ -4304,24 +4304,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>690612</v>
+        <v>690639</v>
       </c>
       <c r="R36" t="n">
-        <v>7096930</v>
+        <v>7096927</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4351,11 +4359,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Cirka 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4371,12 +4374,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4387,7 +4390,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126931567</v>
+        <v>126937620</v>
       </c>
       <c r="B37" t="n">
         <v>98442</v>
@@ -4415,32 +4418,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>690686</v>
+        <v>690612</v>
       </c>
       <c r="R37" t="n">
-        <v>7096928</v>
+        <v>7096930</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4470,6 +4465,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Cirka 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4485,12 +4485,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4914,48 +4914,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126926789</v>
+        <v>126936894</v>
       </c>
       <c r="B42" t="n">
-        <v>91345</v>
+        <v>98442</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>690438</v>
+        <v>690497</v>
       </c>
       <c r="R42" t="n">
-        <v>7097141</v>
+        <v>7097017</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4999,60 +4999,64 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126936894</v>
+        <v>126926789</v>
       </c>
       <c r="B43" t="n">
-        <v>98442</v>
+        <v>91345</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>690497</v>
+        <v>690438</v>
       </c>
       <c r="R43" t="n">
-        <v>7097017</v>
+        <v>7097141</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5096,19 +5100,15 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5209,57 +5209,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126931570</v>
+        <v>126936882</v>
       </c>
       <c r="B45" t="n">
-        <v>98442</v>
+        <v>78773</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>690658</v>
+        <v>690560</v>
       </c>
       <c r="R45" t="n">
-        <v>7096895</v>
+        <v>7096959</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5300,19 +5288,18 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5323,45 +5310,57 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126936882</v>
+        <v>126931570</v>
       </c>
       <c r="B46" t="n">
-        <v>78773</v>
+        <v>98442</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>690560</v>
+        <v>690658</v>
       </c>
       <c r="R46" t="n">
-        <v>7096959</v>
+        <v>7096895</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5402,18 +5401,19 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5424,10 +5424,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126936877</v>
+        <v>126928173</v>
       </c>
       <c r="B47" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5435,37 +5435,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>690378</v>
+        <v>690547</v>
       </c>
       <c r="R47" t="n">
-        <v>7096984</v>
+        <v>7096876</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5509,73 +5509,57 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126936885</v>
+        <v>126936877</v>
       </c>
       <c r="B48" t="n">
-        <v>98442</v>
+        <v>79632</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>690596</v>
+        <v>690378</v>
       </c>
       <c r="R48" t="n">
-        <v>7097007</v>
+        <v>7096984</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5616,7 +5600,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5639,7 +5622,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126928173</v>
+        <v>126937632</v>
       </c>
       <c r="B49" t="n">
         <v>79014</v>
@@ -5670,14 +5653,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>690547</v>
+        <v>690454</v>
       </c>
       <c r="R49" t="n">
-        <v>7096876</v>
+        <v>7097036</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5724,19 +5707,23 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126937632</v>
+        <v>126936911</v>
       </c>
       <c r="B50" t="n">
         <v>79014</v>
@@ -5767,17 +5754,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>690454</v>
+        <v>690481</v>
       </c>
       <c r="R50" t="n">
-        <v>7097036</v>
+        <v>7097028</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5821,12 +5808,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5837,7 +5824,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126936911</v>
+        <v>126937623</v>
       </c>
       <c r="B51" t="n">
         <v>79014</v>
@@ -5868,17 +5855,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>690481</v>
+        <v>690707</v>
       </c>
       <c r="R51" t="n">
-        <v>7097028</v>
+        <v>7096903</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5922,12 +5909,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5938,48 +5925,60 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126937623</v>
+        <v>126936885</v>
       </c>
       <c r="B52" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>690707</v>
+        <v>690596</v>
       </c>
       <c r="R52" t="n">
-        <v>7096903</v>
+        <v>7097007</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6017,18 +6016,19 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6039,48 +6039,60 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126927000</v>
+        <v>126931571</v>
       </c>
       <c r="B53" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>690487</v>
+        <v>690644</v>
       </c>
       <c r="R53" t="n">
-        <v>7097101</v>
+        <v>7096948</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6118,28 +6130,33 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126928117</v>
+        <v>126936878</v>
       </c>
       <c r="B54" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6147,37 +6164,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>690540</v>
+        <v>690509</v>
       </c>
       <c r="R54" t="n">
-        <v>7096888</v>
+        <v>7096927</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6221,22 +6238,26 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126927086</v>
+        <v>126928117</v>
       </c>
       <c r="B55" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6244,34 +6265,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>690545</v>
+        <v>690540</v>
       </c>
       <c r="R55" t="n">
-        <v>7097033</v>
+        <v>7096888</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6330,10 +6351,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126936878</v>
+        <v>126927000</v>
       </c>
       <c r="B56" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6341,37 +6362,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>690509</v>
+        <v>690487</v>
       </c>
       <c r="R56" t="n">
-        <v>7096927</v>
+        <v>7097101</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6415,76 +6436,60 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126931571</v>
+        <v>126927086</v>
       </c>
       <c r="B57" t="n">
-        <v>98442</v>
+        <v>80117</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>690644</v>
+        <v>690545</v>
       </c>
       <c r="R57" t="n">
-        <v>7096948</v>
+        <v>7097033</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6522,33 +6527,28 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126936881</v>
+        <v>126937630</v>
       </c>
       <c r="B58" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6556,37 +6556,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>690617</v>
+        <v>690480</v>
       </c>
       <c r="R58" t="n">
-        <v>7096851</v>
+        <v>7096994</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6630,12 +6630,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6646,7 +6646,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126926624</v>
+        <v>126927108</v>
       </c>
       <c r="B59" t="n">
         <v>79014</v>
@@ -6681,10 +6681,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>690399</v>
+        <v>690542</v>
       </c>
       <c r="R59" t="n">
-        <v>7097170</v>
+        <v>7097030</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6743,7 +6743,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126926566</v>
+        <v>126927426</v>
       </c>
       <c r="B60" t="n">
         <v>79014</v>
@@ -6778,10 +6778,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>690362</v>
+        <v>690560</v>
       </c>
       <c r="R60" t="n">
-        <v>7097210</v>
+        <v>7097019</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6840,7 +6840,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126937630</v>
+        <v>126926624</v>
       </c>
       <c r="B61" t="n">
         <v>79014</v>
@@ -6871,14 +6871,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>690480</v>
+        <v>690399</v>
       </c>
       <c r="R61" t="n">
-        <v>7096994</v>
+        <v>7097170</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6925,23 +6925,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126927108</v>
+        <v>126926566</v>
       </c>
       <c r="B62" t="n">
         <v>79014</v>
@@ -6976,10 +6972,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>690542</v>
+        <v>690362</v>
       </c>
       <c r="R62" t="n">
-        <v>7097030</v>
+        <v>7097210</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7038,10 +7034,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126927426</v>
+        <v>126936881</v>
       </c>
       <c r="B63" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7049,37 +7045,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>690560</v>
+        <v>690617</v>
       </c>
       <c r="R63" t="n">
-        <v>7097019</v>
+        <v>7096851</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7123,44 +7119,48 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126927409</v>
+        <v>126927067</v>
       </c>
       <c r="B64" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7170,13 +7170,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>690545</v>
+        <v>690536</v>
       </c>
       <c r="R64" t="n">
-        <v>7097003</v>
+        <v>7097045</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126927067</v>
+        <v>126926457</v>
       </c>
       <c r="B65" t="n">
         <v>79014</v>
@@ -7267,13 +7267,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>690536</v>
+        <v>690374</v>
       </c>
       <c r="R65" t="n">
-        <v>7097045</v>
+        <v>7097232</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126926457</v>
+        <v>126931576</v>
       </c>
       <c r="B66" t="n">
         <v>79014</v>
@@ -7360,17 +7360,17 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>690374</v>
+        <v>690565</v>
       </c>
       <c r="R66" t="n">
-        <v>7097232</v>
+        <v>7096992</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7414,60 +7414,64 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126931576</v>
+        <v>126927409</v>
       </c>
       <c r="B67" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>690565</v>
+        <v>690545</v>
       </c>
       <c r="R67" t="n">
-        <v>7096992</v>
+        <v>7097003</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7511,19 +7515,15 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7628,7 +7628,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126926526</v>
+        <v>126927324</v>
       </c>
       <c r="B69" t="n">
         <v>79014</v>
@@ -7659,17 +7659,17 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>N Johannesbomyran, N Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>690490</v>
+        <v>690542</v>
       </c>
       <c r="R69" t="n">
-        <v>7096997</v>
+        <v>7097025</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7713,19 +7713,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126936908</v>
+        <v>126926526</v>
       </c>
       <c r="B70" t="n">
         <v>79014</v>
@@ -7756,14 +7756,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>N Johannesbomyran, N Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>690598</v>
+        <v>690490</v>
       </c>
       <c r="R70" t="n">
-        <v>7096855</v>
+        <v>7096997</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7810,23 +7810,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126927324</v>
+        <v>126936908</v>
       </c>
       <c r="B71" t="n">
         <v>79014</v>
@@ -7857,17 +7853,17 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>690542</v>
+        <v>690598</v>
       </c>
       <c r="R71" t="n">
-        <v>7097025</v>
+        <v>7096855</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7911,19 +7907,23 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126927191</v>
+        <v>126936896</v>
       </c>
       <c r="B72" t="n">
         <v>79014</v>
@@ -7954,17 +7954,17 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>690524</v>
+        <v>690482</v>
       </c>
       <c r="R72" t="n">
-        <v>7097009</v>
+        <v>7096931</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8008,19 +8008,23 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126936896</v>
+        <v>126927191</v>
       </c>
       <c r="B73" t="n">
         <v>79014</v>
@@ -8051,17 +8055,17 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>690482</v>
+        <v>690524</v>
       </c>
       <c r="R73" t="n">
-        <v>7096931</v>
+        <v>7097009</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8105,19 +8109,15 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8433,7 +8433,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126937629</v>
+        <v>126927024</v>
       </c>
       <c r="B77" t="n">
         <v>79014</v>
@@ -8464,14 +8464,14 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>690504</v>
+        <v>690503</v>
       </c>
       <c r="R77" t="n">
-        <v>7096980</v>
+        <v>7097060</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8518,23 +8518,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126927024</v>
+        <v>126927395</v>
       </c>
       <c r="B78" t="n">
         <v>79014</v>
@@ -8569,10 +8565,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>690503</v>
+        <v>690542</v>
       </c>
       <c r="R78" t="n">
-        <v>7097060</v>
+        <v>7096989</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8631,7 +8627,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126927395</v>
+        <v>126937629</v>
       </c>
       <c r="B79" t="n">
         <v>79014</v>
@@ -8662,14 +8658,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>690542</v>
+        <v>690504</v>
       </c>
       <c r="R79" t="n">
-        <v>7096989</v>
+        <v>7096980</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8716,22 +8712,26 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126936909</v>
+        <v>126931564</v>
       </c>
       <c r="B80" t="n">
-        <v>79014</v>
+        <v>79046</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8739,34 +8739,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>690590</v>
+        <v>690624</v>
       </c>
       <c r="R80" t="n">
-        <v>7096893</v>
+        <v>7096879</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8813,12 +8813,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8829,7 +8829,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126937622</v>
+        <v>126936909</v>
       </c>
       <c r="B81" t="n">
         <v>79014</v>
@@ -8860,17 +8860,17 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>690620</v>
+        <v>690590</v>
       </c>
       <c r="R81" t="n">
-        <v>7096858</v>
+        <v>7096893</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8914,12 +8914,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -8930,7 +8930,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126927691</v>
+        <v>126937622</v>
       </c>
       <c r="B82" t="n">
         <v>79014</v>
@@ -8961,14 +8961,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>690577</v>
+        <v>690620</v>
       </c>
       <c r="R82" t="n">
-        <v>7096975</v>
+        <v>7096858</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9015,22 +9015,26 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126931564</v>
+        <v>126927691</v>
       </c>
       <c r="B83" t="n">
-        <v>79046</v>
+        <v>79014</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9038,37 +9042,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>690624</v>
+        <v>690577</v>
       </c>
       <c r="R83" t="n">
-        <v>7096879</v>
+        <v>7096975</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9112,48 +9116,44 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126927343</v>
+        <v>126926723</v>
       </c>
       <c r="B84" t="n">
-        <v>98442</v>
+        <v>78773</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9163,10 +9163,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>690544</v>
+        <v>690433</v>
       </c>
       <c r="R84" t="n">
-        <v>7097007</v>
+        <v>7097136</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9225,32 +9225,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126926723</v>
+        <v>126927343</v>
       </c>
       <c r="B85" t="n">
-        <v>78773</v>
+        <v>98442</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9260,10 +9260,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>690433</v>
+        <v>690544</v>
       </c>
       <c r="R85" t="n">
-        <v>7097136</v>
+        <v>7097007</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9322,7 +9322,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126927737</v>
+        <v>126936899</v>
       </c>
       <c r="B86" t="n">
         <v>79014</v>
@@ -9353,17 +9353,17 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>690623</v>
+        <v>690607</v>
       </c>
       <c r="R86" t="n">
-        <v>7096931</v>
+        <v>7097019</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9407,19 +9407,23 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126936899</v>
+        <v>126927737</v>
       </c>
       <c r="B87" t="n">
         <v>79014</v>
@@ -9450,17 +9454,17 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>690607</v>
+        <v>690623</v>
       </c>
       <c r="R87" t="n">
-        <v>7097019</v>
+        <v>7096931</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9504,19 +9508,15 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9621,45 +9621,57 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126936895</v>
+        <v>126936892</v>
       </c>
       <c r="B89" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>690445</v>
+        <v>690619</v>
       </c>
       <c r="R89" t="n">
-        <v>7096945</v>
+        <v>7096955</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9700,6 +9712,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9722,48 +9735,48 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126926697</v>
+        <v>126936913</v>
       </c>
       <c r="B90" t="n">
-        <v>79014</v>
+        <v>92615</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>690438</v>
+        <v>690466</v>
       </c>
       <c r="R90" t="n">
-        <v>7097148</v>
+        <v>7096945</v>
       </c>
       <c r="S90" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9807,60 +9820,64 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126936913</v>
+        <v>126937616</v>
       </c>
       <c r="B91" t="n">
-        <v>92615</v>
+        <v>79632</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>690466</v>
+        <v>690516</v>
       </c>
       <c r="R91" t="n">
-        <v>7096945</v>
+        <v>7096946</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9904,12 +9921,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -9920,10 +9937,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126937616</v>
+        <v>126936895</v>
       </c>
       <c r="B92" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9931,37 +9948,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>690516</v>
+        <v>690445</v>
       </c>
       <c r="R92" t="n">
-        <v>7096946</v>
+        <v>7096945</v>
       </c>
       <c r="S92" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10005,12 +10022,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10021,60 +10038,48 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126936892</v>
+        <v>126926697</v>
       </c>
       <c r="B93" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>690619</v>
+        <v>690438</v>
       </c>
       <c r="R93" t="n">
-        <v>7096955</v>
+        <v>7097148</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10112,26 +10117,21 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10232,48 +10232,48 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126937619</v>
+        <v>126936898</v>
       </c>
       <c r="B95" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>690621</v>
+        <v>690576</v>
       </c>
       <c r="R95" t="n">
-        <v>7096899</v>
+        <v>7096919</v>
       </c>
       <c r="S95" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10317,12 +10317,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10333,60 +10333,48 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126931572</v>
+        <v>126937627</v>
       </c>
       <c r="B96" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>690665</v>
+        <v>690522</v>
       </c>
       <c r="R96" t="n">
-        <v>7096920</v>
+        <v>7096919</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10424,19 +10412,18 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10447,61 +10434,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126931569</v>
+        <v>126936880</v>
       </c>
       <c r="B97" t="n">
-        <v>98442</v>
+        <v>78773</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>690550</v>
+        <v>690619</v>
       </c>
       <c r="R97" t="n">
-        <v>7097011</v>
+        <v>7097003</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10542,19 +10513,18 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10683,48 +10653,48 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126936880</v>
+        <v>126937619</v>
       </c>
       <c r="B99" t="n">
-        <v>78773</v>
+        <v>98442</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>690619</v>
+        <v>690621</v>
       </c>
       <c r="R99" t="n">
-        <v>7097003</v>
+        <v>7096899</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10768,12 +10738,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10784,45 +10754,61 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126936898</v>
+        <v>126931569</v>
       </c>
       <c r="B100" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>690576</v>
+        <v>690550</v>
       </c>
       <c r="R100" t="n">
-        <v>7096919</v>
+        <v>7097011</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10863,18 +10849,19 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10885,48 +10872,60 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126937627</v>
+        <v>126931572</v>
       </c>
       <c r="B101" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>690522</v>
+        <v>690665</v>
       </c>
       <c r="R101" t="n">
-        <v>7096919</v>
+        <v>7096920</v>
       </c>
       <c r="S101" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10964,18 +10963,19 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -10986,48 +10986,48 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126931577</v>
+        <v>126927465</v>
       </c>
       <c r="B102" t="n">
-        <v>80052</v>
+        <v>79014</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>690656</v>
+        <v>690596</v>
       </c>
       <c r="R102" t="n">
-        <v>7096927</v>
+        <v>7097023</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11071,26 +11071,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY102" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126927178</v>
+        <v>126931577</v>
       </c>
       <c r="B103" t="n">
-        <v>80146</v>
+        <v>80052</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11098,37 +11094,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6462</v>
+        <v>6457</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>690520</v>
+        <v>690656</v>
       </c>
       <c r="R103" t="n">
-        <v>7097024</v>
+        <v>7096927</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11172,44 +11168,48 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY103" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126927184</v>
+        <v>126927178</v>
       </c>
       <c r="B104" t="n">
-        <v>80117</v>
+        <v>80146</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11281,32 +11281,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126927139</v>
+        <v>126927184</v>
       </c>
       <c r="B105" t="n">
-        <v>80146</v>
+        <v>80117</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11316,10 +11316,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>690515</v>
+        <v>690520</v>
       </c>
       <c r="R105" t="n">
-        <v>7097011</v>
+        <v>7097024</v>
       </c>
       <c r="S105" t="n">
         <v>15</v>
@@ -11378,48 +11378,48 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126931566</v>
+        <v>126927139</v>
       </c>
       <c r="B106" t="n">
-        <v>78772</v>
+        <v>80146</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>690621</v>
+        <v>690515</v>
       </c>
       <c r="R106" t="n">
-        <v>7096855</v>
+        <v>7097011</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11463,19 +11463,15 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY106" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11576,10 +11572,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126927465</v>
+        <v>126931566</v>
       </c>
       <c r="B108" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11587,37 +11583,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>690596</v>
+        <v>690621</v>
       </c>
       <c r="R108" t="n">
-        <v>7097023</v>
+        <v>7096855</v>
       </c>
       <c r="S108" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11661,15 +11657,19 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY108" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30467-2025 artfynd.xlsx
+++ b/artfynd/A 30467-2025 artfynd.xlsx
@@ -4501,7 +4501,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126936910</v>
+        <v>126926531</v>
       </c>
       <c r="B38" t="n">
         <v>79014</v>
@@ -4532,14 +4532,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>690572</v>
+        <v>690376</v>
       </c>
       <c r="R38" t="n">
-        <v>7096932</v>
+        <v>7097225</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4586,73 +4586,57 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126936887</v>
+        <v>126936900</v>
       </c>
       <c r="B39" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>690632</v>
+        <v>690663</v>
       </c>
       <c r="R39" t="n">
-        <v>7096922</v>
+        <v>7096854</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4693,7 +4677,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4716,7 +4699,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126926531</v>
+        <v>126936910</v>
       </c>
       <c r="B40" t="n">
         <v>79014</v>
@@ -4747,14 +4730,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>690376</v>
+        <v>690572</v>
       </c>
       <c r="R40" t="n">
-        <v>7097225</v>
+        <v>7096932</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4801,57 +4784,73 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126936900</v>
+        <v>126936887</v>
       </c>
       <c r="B41" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>690663</v>
+        <v>690632</v>
       </c>
       <c r="R41" t="n">
-        <v>7096854</v>
+        <v>7096922</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4892,6 +4891,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5112,10 +5112,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126926859</v>
+        <v>126936882</v>
       </c>
       <c r="B44" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5123,37 +5123,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>690483</v>
+        <v>690560</v>
       </c>
       <c r="R44" t="n">
-        <v>7097114</v>
+        <v>7096959</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5197,22 +5197,26 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126936882</v>
+        <v>126926859</v>
       </c>
       <c r="B45" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5220,37 +5224,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>690560</v>
+        <v>690483</v>
       </c>
       <c r="R45" t="n">
-        <v>7096959</v>
+        <v>7097114</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5294,19 +5298,15 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6545,7 +6545,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126937630</v>
+        <v>126926624</v>
       </c>
       <c r="B58" t="n">
         <v>79014</v>
@@ -6576,14 +6576,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>690480</v>
+        <v>690399</v>
       </c>
       <c r="R58" t="n">
-        <v>7096994</v>
+        <v>7097170</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6630,23 +6630,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126927108</v>
+        <v>126926566</v>
       </c>
       <c r="B59" t="n">
         <v>79014</v>
@@ -6681,10 +6677,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>690542</v>
+        <v>690362</v>
       </c>
       <c r="R59" t="n">
-        <v>7097030</v>
+        <v>7097210</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6743,7 +6739,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126927426</v>
+        <v>126937630</v>
       </c>
       <c r="B60" t="n">
         <v>79014</v>
@@ -6774,14 +6770,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>690560</v>
+        <v>690480</v>
       </c>
       <c r="R60" t="n">
-        <v>7097019</v>
+        <v>7096994</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6828,19 +6824,23 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126926624</v>
+        <v>126927108</v>
       </c>
       <c r="B61" t="n">
         <v>79014</v>
@@ -6875,10 +6875,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>690399</v>
+        <v>690542</v>
       </c>
       <c r="R61" t="n">
-        <v>7097170</v>
+        <v>7097030</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6937,7 +6937,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126926566</v>
+        <v>126927426</v>
       </c>
       <c r="B62" t="n">
         <v>79014</v>
@@ -6972,10 +6972,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>690362</v>
+        <v>690560</v>
       </c>
       <c r="R62" t="n">
-        <v>7097210</v>
+        <v>7097019</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7628,7 +7628,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126927324</v>
+        <v>126926526</v>
       </c>
       <c r="B69" t="n">
         <v>79014</v>
@@ -7659,17 +7659,17 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>N Johannesbomyran, N Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>690542</v>
+        <v>690490</v>
       </c>
       <c r="R69" t="n">
-        <v>7097025</v>
+        <v>7096997</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7713,19 +7713,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126926526</v>
+        <v>126936908</v>
       </c>
       <c r="B70" t="n">
         <v>79014</v>
@@ -7756,14 +7756,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>N Johannesbomyran, N Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>690490</v>
+        <v>690598</v>
       </c>
       <c r="R70" t="n">
-        <v>7096997</v>
+        <v>7096855</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7810,19 +7810,23 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126936908</v>
+        <v>126927324</v>
       </c>
       <c r="B71" t="n">
         <v>79014</v>
@@ -7853,17 +7857,17 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>690598</v>
+        <v>690542</v>
       </c>
       <c r="R71" t="n">
-        <v>7096855</v>
+        <v>7097025</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7907,19 +7911,15 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8829,10 +8829,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126936909</v>
+        <v>126926723</v>
       </c>
       <c r="B81" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8840,37 +8840,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>690590</v>
+        <v>690433</v>
       </c>
       <c r="R81" t="n">
-        <v>7096893</v>
+        <v>7097136</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8914,61 +8914,57 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126937622</v>
+        <v>126927343</v>
       </c>
       <c r="B82" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>690620</v>
+        <v>690544</v>
       </c>
       <c r="R82" t="n">
-        <v>7096858</v>
+        <v>7097007</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9015,23 +9011,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126927691</v>
+        <v>126936909</v>
       </c>
       <c r="B83" t="n">
         <v>79014</v>
@@ -9062,17 +9054,17 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>690577</v>
+        <v>690590</v>
       </c>
       <c r="R83" t="n">
-        <v>7096975</v>
+        <v>7096893</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9116,22 +9108,26 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126926723</v>
+        <v>126937622</v>
       </c>
       <c r="B84" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9139,34 +9135,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>690433</v>
+        <v>690620</v>
       </c>
       <c r="R84" t="n">
-        <v>7097136</v>
+        <v>7096858</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9213,44 +9209,48 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126927343</v>
+        <v>126927691</v>
       </c>
       <c r="B85" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9260,10 +9260,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>690544</v>
+        <v>690577</v>
       </c>
       <c r="R85" t="n">
-        <v>7097007</v>
+        <v>7096975</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9621,57 +9621,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126936892</v>
+        <v>126936895</v>
       </c>
       <c r="B89" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>690619</v>
+        <v>690445</v>
       </c>
       <c r="R89" t="n">
-        <v>7096955</v>
+        <v>7096945</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9712,7 +9700,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9735,48 +9722,48 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126936913</v>
+        <v>126926697</v>
       </c>
       <c r="B90" t="n">
-        <v>92615</v>
+        <v>79014</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>690466</v>
+        <v>690438</v>
       </c>
       <c r="R90" t="n">
-        <v>7096945</v>
+        <v>7097148</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9820,64 +9807,60 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126937616</v>
+        <v>126936913</v>
       </c>
       <c r="B91" t="n">
-        <v>79632</v>
+        <v>92615</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>690516</v>
+        <v>690466</v>
       </c>
       <c r="R91" t="n">
-        <v>7096946</v>
+        <v>7096945</v>
       </c>
       <c r="S91" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9921,12 +9904,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -9937,10 +9920,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126936895</v>
+        <v>126937616</v>
       </c>
       <c r="B92" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9948,37 +9931,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>690445</v>
+        <v>690516</v>
       </c>
       <c r="R92" t="n">
-        <v>7096945</v>
+        <v>7096946</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10022,12 +10005,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10038,48 +10021,60 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126926697</v>
+        <v>126936892</v>
       </c>
       <c r="B93" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>690438</v>
+        <v>690619</v>
       </c>
       <c r="R93" t="n">
-        <v>7097148</v>
+        <v>7096955</v>
       </c>
       <c r="S93" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10117,21 +10112,26 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">

--- a/artfynd/A 30467-2025 artfynd.xlsx
+++ b/artfynd/A 30467-2025 artfynd.xlsx
@@ -675,45 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126919968</v>
+        <v>126909580</v>
       </c>
       <c r="B2" t="n">
-        <v>80021</v>
+        <v>98443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rislidstjärnarna, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>690349</v>
+        <v>690493</v>
       </c>
       <c r="R2" t="n">
-        <v>7097128</v>
+        <v>7097055</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,9 +747,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,12 +774,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
+          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -776,49 +790,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126909580</v>
+        <v>126919968</v>
       </c>
       <c r="B3" t="n">
-        <v>98442</v>
+        <v>80021</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Rislidstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>690493</v>
+        <v>690349</v>
       </c>
       <c r="R3" t="n">
-        <v>7097055</v>
+        <v>7097128</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,19 +858,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,12 +875,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
+          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1005,32 +1005,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126917550</v>
+        <v>126917563</v>
       </c>
       <c r="B5" t="n">
-        <v>80153</v>
+        <v>79014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>690515</v>
+        <v>690509</v>
       </c>
       <c r="R5" t="n">
-        <v>7097014</v>
+        <v>7097052</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,32 +1106,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126917563</v>
+        <v>126917550</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>80153</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>690509</v>
+        <v>690515</v>
       </c>
       <c r="R6" t="n">
-        <v>7097052</v>
+        <v>7097014</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1210,7 @@
         <v>126919976</v>
       </c>
       <c r="B7" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>126917539</v>
       </c>
       <c r="B8" t="n">
-        <v>91336</v>
+        <v>91337</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>126919966</v>
       </c>
       <c r="B9" t="n">
-        <v>91336</v>
+        <v>91337</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>126909413</v>
       </c>
       <c r="B12" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>126909538</v>
       </c>
       <c r="B13" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>126918516</v>
       </c>
       <c r="B14" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2598,48 +2598,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126927356</v>
+        <v>126936912</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>690516</v>
+        <v>690392</v>
       </c>
       <c r="R20" t="n">
-        <v>7096990</v>
+        <v>7097038</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2683,60 +2683,64 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126936912</v>
+        <v>126927356</v>
       </c>
       <c r="B21" t="n">
-        <v>92615</v>
+        <v>79014</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>690392</v>
+        <v>690516</v>
       </c>
       <c r="R21" t="n">
-        <v>7097038</v>
+        <v>7096990</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2780,26 +2784,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>126931573</v>
       </c>
       <c r="B22" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2994,48 +2994,64 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126937624</v>
+        <v>126936889</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>690656</v>
+        <v>690595</v>
       </c>
       <c r="R24" t="n">
-        <v>7096868</v>
+        <v>7096886</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3073,18 +3089,19 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3095,48 +3112,64 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126927661</v>
+        <v>126936886</v>
       </c>
       <c r="B25" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>690574</v>
+        <v>690607</v>
       </c>
       <c r="R25" t="n">
-        <v>7096978</v>
+        <v>7097014</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3174,28 +3207,33 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126927842</v>
+        <v>126931565</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3203,37 +3241,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>690605</v>
+        <v>690620</v>
       </c>
       <c r="R26" t="n">
-        <v>7096920</v>
+        <v>7096859</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3277,22 +3315,26 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126931565</v>
+        <v>126927661</v>
       </c>
       <c r="B27" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3300,37 +3342,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>690620</v>
+        <v>690574</v>
       </c>
       <c r="R27" t="n">
-        <v>7096859</v>
+        <v>7096978</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3374,80 +3416,60 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126936889</v>
+        <v>126937624</v>
       </c>
       <c r="B28" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>690595</v>
+        <v>690656</v>
       </c>
       <c r="R28" t="n">
-        <v>7096886</v>
+        <v>7096868</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3485,19 +3507,18 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3508,60 +3529,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126936890</v>
+        <v>126927842</v>
       </c>
       <c r="B29" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>690564</v>
+        <v>690605</v>
       </c>
       <c r="R29" t="n">
-        <v>7096907</v>
+        <v>7096920</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3599,33 +3608,28 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126936886</v>
+        <v>126936890</v>
       </c>
       <c r="B30" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3652,7 +3656,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3660,11 +3664,7 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>690607</v>
+        <v>690564</v>
       </c>
       <c r="R30" t="n">
-        <v>7097014</v>
+        <v>7096907</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3841,48 +3841,64 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126927550</v>
+        <v>126936883</v>
       </c>
       <c r="B32" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>690574</v>
+        <v>690668</v>
       </c>
       <c r="R32" t="n">
-        <v>7096994</v>
+        <v>7096918</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3920,63 +3936,68 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126937621</v>
+        <v>126927550</v>
       </c>
       <c r="B33" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>690635</v>
+        <v>690574</v>
       </c>
       <c r="R33" t="n">
-        <v>7096944</v>
+        <v>7096994</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4011,11 +4032,6 @@
           <t>2025-07-26</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ca 40 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4028,26 +4044,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126936883</v>
+        <v>126937621</v>
       </c>
       <c r="B34" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4072,36 +4084,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>690668</v>
+        <v>690635</v>
       </c>
       <c r="R34" t="n">
-        <v>7096918</v>
+        <v>7096944</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4133,25 +4129,29 @@
           <t>2025-07-26</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ca 40 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4165,7 +4165,7 @@
         <v>126931567</v>
       </c>
       <c r="B35" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4276,10 +4276,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126936888</v>
+        <v>126937620</v>
       </c>
       <c r="B36" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4304,32 +4304,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>690639</v>
+        <v>690612</v>
       </c>
       <c r="R36" t="n">
-        <v>7096927</v>
+        <v>7096930</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4359,6 +4351,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Cirka 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4374,12 +4371,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4390,10 +4387,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126937620</v>
+        <v>126936888</v>
       </c>
       <c r="B37" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4418,24 +4415,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>690612</v>
+        <v>690639</v>
       </c>
       <c r="R37" t="n">
-        <v>7096930</v>
+        <v>7096927</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4465,11 +4470,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Cirka 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4485,12 +4485,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4598,7 +4598,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126936900</v>
+        <v>126936910</v>
       </c>
       <c r="B39" t="n">
         <v>79014</v>
@@ -4633,10 +4633,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>690663</v>
+        <v>690572</v>
       </c>
       <c r="R39" t="n">
-        <v>7096854</v>
+        <v>7096932</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4699,7 +4699,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126936910</v>
+        <v>126936900</v>
       </c>
       <c r="B40" t="n">
         <v>79014</v>
@@ -4734,10 +4734,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>690572</v>
+        <v>690663</v>
       </c>
       <c r="R40" t="n">
-        <v>7096932</v>
+        <v>7096854</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4803,7 +4803,7 @@
         <v>126936887</v>
       </c>
       <c r="B41" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>126936894</v>
       </c>
       <c r="B42" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>126926789</v>
       </c>
       <c r="B43" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5112,10 +5112,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126936882</v>
+        <v>126926859</v>
       </c>
       <c r="B44" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5123,37 +5123,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>690560</v>
+        <v>690483</v>
       </c>
       <c r="R44" t="n">
-        <v>7096959</v>
+        <v>7097114</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5197,64 +5197,72 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126926859</v>
+        <v>126931570</v>
       </c>
       <c r="B45" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>690483</v>
+        <v>690658</v>
       </c>
       <c r="R45" t="n">
-        <v>7097114</v>
+        <v>7096895</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5292,75 +5300,68 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126931570</v>
+        <v>126936882</v>
       </c>
       <c r="B46" t="n">
-        <v>98442</v>
+        <v>78773</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>690658</v>
+        <v>690560</v>
       </c>
       <c r="R46" t="n">
-        <v>7096895</v>
+        <v>7096959</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5401,19 +5402,18 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5424,7 +5424,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126928173</v>
+        <v>126937623</v>
       </c>
       <c r="B47" t="n">
         <v>79014</v>
@@ -5455,14 +5455,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>690547</v>
+        <v>690707</v>
       </c>
       <c r="R47" t="n">
-        <v>7096876</v>
+        <v>7096903</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5509,22 +5509,26 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126936877</v>
+        <v>126936911</v>
       </c>
       <c r="B48" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5532,21 +5536,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5556,10 +5560,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>690378</v>
+        <v>690481</v>
       </c>
       <c r="R48" t="n">
-        <v>7096984</v>
+        <v>7097028</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5622,7 +5626,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126937632</v>
+        <v>126928173</v>
       </c>
       <c r="B49" t="n">
         <v>79014</v>
@@ -5653,14 +5657,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>690454</v>
+        <v>690547</v>
       </c>
       <c r="R49" t="n">
-        <v>7097036</v>
+        <v>7096876</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5707,23 +5711,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126936911</v>
+        <v>126937632</v>
       </c>
       <c r="B50" t="n">
         <v>79014</v>
@@ -5754,17 +5754,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>690481</v>
+        <v>690454</v>
       </c>
       <c r="R50" t="n">
-        <v>7097028</v>
+        <v>7097036</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5808,12 +5808,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5824,10 +5824,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126937623</v>
+        <v>126936877</v>
       </c>
       <c r="B51" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5835,37 +5835,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>690707</v>
+        <v>690378</v>
       </c>
       <c r="R51" t="n">
-        <v>7096903</v>
+        <v>7096984</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5909,12 +5909,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5928,7 +5928,7 @@
         <v>126936885</v>
       </c>
       <c r="B52" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6039,60 +6039,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126931571</v>
+        <v>126927000</v>
       </c>
       <c r="B53" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>690644</v>
+        <v>690487</v>
       </c>
       <c r="R53" t="n">
-        <v>7096948</v>
+        <v>7097101</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6130,33 +6118,28 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126936878</v>
+        <v>126928117</v>
       </c>
       <c r="B54" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6164,37 +6147,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>690509</v>
+        <v>690540</v>
       </c>
       <c r="R54" t="n">
-        <v>7096927</v>
+        <v>7096888</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6238,26 +6221,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126928117</v>
+        <v>126936878</v>
       </c>
       <c r="B55" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6265,37 +6244,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>690540</v>
+        <v>690509</v>
       </c>
       <c r="R55" t="n">
-        <v>7096888</v>
+        <v>7096927</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6339,22 +6318,26 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126927000</v>
+        <v>126927086</v>
       </c>
       <c r="B56" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6362,21 +6345,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6386,10 +6369,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>690487</v>
+        <v>690545</v>
       </c>
       <c r="R56" t="n">
-        <v>7097101</v>
+        <v>7097033</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6448,48 +6431,60 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126927086</v>
+        <v>126931571</v>
       </c>
       <c r="B57" t="n">
-        <v>80117</v>
+        <v>98443</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>690545</v>
+        <v>690644</v>
       </c>
       <c r="R57" t="n">
-        <v>7097033</v>
+        <v>7096948</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6527,21 +6522,26 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7135,7 +7135,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126927067</v>
+        <v>126926457</v>
       </c>
       <c r="B64" t="n">
         <v>79014</v>
@@ -7170,13 +7170,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>690536</v>
+        <v>690374</v>
       </c>
       <c r="R64" t="n">
-        <v>7097045</v>
+        <v>7097232</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126926457</v>
+        <v>126931576</v>
       </c>
       <c r="B65" t="n">
         <v>79014</v>
@@ -7263,17 +7263,17 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>690374</v>
+        <v>690565</v>
       </c>
       <c r="R65" t="n">
-        <v>7097232</v>
+        <v>7096992</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7317,60 +7317,64 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126931576</v>
+        <v>126927409</v>
       </c>
       <c r="B66" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>690565</v>
+        <v>690545</v>
       </c>
       <c r="R66" t="n">
-        <v>7096992</v>
+        <v>7097003</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7414,26 +7418,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126927409</v>
+        <v>126936893</v>
       </c>
       <c r="B67" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7461,17 +7461,17 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>690545</v>
+        <v>690658</v>
       </c>
       <c r="R67" t="n">
-        <v>7097003</v>
+        <v>7096938</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7515,57 +7515,61 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126936893</v>
+        <v>126927067</v>
       </c>
       <c r="B68" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>690658</v>
+        <v>690536</v>
       </c>
       <c r="R68" t="n">
-        <v>7096938</v>
+        <v>7097045</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7612,19 +7616,15 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7923,7 +7923,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126936896</v>
+        <v>126927191</v>
       </c>
       <c r="B72" t="n">
         <v>79014</v>
@@ -7954,17 +7954,17 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>690482</v>
+        <v>690524</v>
       </c>
       <c r="R72" t="n">
-        <v>7096931</v>
+        <v>7097009</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8008,23 +8008,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126927191</v>
+        <v>126936896</v>
       </c>
       <c r="B73" t="n">
         <v>79014</v>
@@ -8055,17 +8051,17 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>690524</v>
+        <v>690482</v>
       </c>
       <c r="R73" t="n">
-        <v>7097009</v>
+        <v>7096931</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8109,22 +8105,26 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
         <v>126936879</v>
       </c>
       <c r="B74" t="n">
-        <v>97326</v>
+        <v>97327</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         <v>126936891</v>
       </c>
       <c r="B75" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8433,7 +8433,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126927024</v>
+        <v>126937629</v>
       </c>
       <c r="B77" t="n">
         <v>79014</v>
@@ -8464,14 +8464,14 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>690503</v>
+        <v>690504</v>
       </c>
       <c r="R77" t="n">
-        <v>7097060</v>
+        <v>7096980</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8518,19 +8518,23 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126927395</v>
+        <v>126927024</v>
       </c>
       <c r="B78" t="n">
         <v>79014</v>
@@ -8565,10 +8569,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>690542</v>
+        <v>690503</v>
       </c>
       <c r="R78" t="n">
-        <v>7096989</v>
+        <v>7097060</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8627,7 +8631,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126937629</v>
+        <v>126927395</v>
       </c>
       <c r="B79" t="n">
         <v>79014</v>
@@ -8658,14 +8662,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>690504</v>
+        <v>690542</v>
       </c>
       <c r="R79" t="n">
-        <v>7096980</v>
+        <v>7096989</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8712,19 +8716,15 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8829,10 +8829,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126926723</v>
+        <v>126927691</v>
       </c>
       <c r="B81" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8840,21 +8840,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8864,10 +8864,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>690433</v>
+        <v>690577</v>
       </c>
       <c r="R81" t="n">
-        <v>7097136</v>
+        <v>7096975</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8929,7 +8929,7 @@
         <v>126927343</v>
       </c>
       <c r="B82" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9023,10 +9023,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126936909</v>
+        <v>126926723</v>
       </c>
       <c r="B83" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9034,37 +9034,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>690590</v>
+        <v>690433</v>
       </c>
       <c r="R83" t="n">
-        <v>7096893</v>
+        <v>7097136</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9108,23 +9108,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126937622</v>
+        <v>126936909</v>
       </c>
       <c r="B84" t="n">
         <v>79014</v>
@@ -9155,17 +9151,17 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>690620</v>
+        <v>690590</v>
       </c>
       <c r="R84" t="n">
-        <v>7096858</v>
+        <v>7096893</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9209,12 +9205,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9225,7 +9221,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126927691</v>
+        <v>126937622</v>
       </c>
       <c r="B85" t="n">
         <v>79014</v>
@@ -9256,14 +9252,14 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>690577</v>
+        <v>690620</v>
       </c>
       <c r="R85" t="n">
-        <v>7096975</v>
+        <v>7096858</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9310,19 +9306,23 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126936899</v>
+        <v>126927737</v>
       </c>
       <c r="B86" t="n">
         <v>79014</v>
@@ -9353,17 +9353,17 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>690607</v>
+        <v>690623</v>
       </c>
       <c r="R86" t="n">
-        <v>7097019</v>
+        <v>7096931</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9407,23 +9407,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126927737</v>
+        <v>126936899</v>
       </c>
       <c r="B87" t="n">
         <v>79014</v>
@@ -9454,17 +9450,17 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>690623</v>
+        <v>690607</v>
       </c>
       <c r="R87" t="n">
-        <v>7096931</v>
+        <v>7097019</v>
       </c>
       <c r="S87" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9508,15 +9504,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9621,7 +9621,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126936895</v>
+        <v>126926697</v>
       </c>
       <c r="B89" t="n">
         <v>79014</v>
@@ -9652,17 +9652,17 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>690445</v>
+        <v>690438</v>
       </c>
       <c r="R89" t="n">
-        <v>7096945</v>
+        <v>7097148</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9706,64 +9706,72 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126926697</v>
+        <v>126936892</v>
       </c>
       <c r="B90" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>690438</v>
+        <v>690619</v>
       </c>
       <c r="R90" t="n">
-        <v>7097148</v>
+        <v>7096955</v>
       </c>
       <c r="S90" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9801,28 +9809,33 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
         <v>126936913</v>
       </c>
       <c r="B91" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9920,10 +9933,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126937616</v>
+        <v>126936895</v>
       </c>
       <c r="B92" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9931,37 +9944,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>690516</v>
+        <v>690445</v>
       </c>
       <c r="R92" t="n">
-        <v>7096946</v>
+        <v>7096945</v>
       </c>
       <c r="S92" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10005,12 +10018,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10021,60 +10034,48 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126936892</v>
+        <v>126937616</v>
       </c>
       <c r="B93" t="n">
-        <v>98442</v>
+        <v>79632</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>690619</v>
+        <v>690516</v>
       </c>
       <c r="R93" t="n">
-        <v>7096955</v>
+        <v>7096946</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10112,19 +10113,18 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10135,10 +10135,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126927128</v>
+        <v>126936898</v>
       </c>
       <c r="B94" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10146,37 +10146,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>690517</v>
+        <v>690576</v>
       </c>
       <c r="R94" t="n">
-        <v>7097014</v>
+        <v>7096919</v>
       </c>
       <c r="S94" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10220,19 +10220,23 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126936898</v>
+        <v>126937627</v>
       </c>
       <c r="B95" t="n">
         <v>79014</v>
@@ -10263,17 +10267,17 @@
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>690576</v>
+        <v>690522</v>
       </c>
       <c r="R95" t="n">
         <v>7096919</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10317,12 +10321,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10333,10 +10337,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126937627</v>
+        <v>126927128</v>
       </c>
       <c r="B96" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10344,34 +10348,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>690522</v>
+        <v>690517</v>
       </c>
       <c r="R96" t="n">
-        <v>7096919</v>
+        <v>7097014</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -10418,61 +10422,73 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126936880</v>
+        <v>126936884</v>
       </c>
       <c r="B97" t="n">
-        <v>78773</v>
+        <v>98443</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>690619</v>
+        <v>690609</v>
       </c>
       <c r="R97" t="n">
-        <v>7097003</v>
+        <v>7096953</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10513,6 +10529,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10535,10 +10552,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126936884</v>
+        <v>126937619</v>
       </c>
       <c r="B98" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10563,36 +10580,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>690609</v>
+        <v>690621</v>
       </c>
       <c r="R98" t="n">
-        <v>7096953</v>
+        <v>7096899</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10630,19 +10631,18 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10653,10 +10653,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126937619</v>
+        <v>126931569</v>
       </c>
       <c r="B99" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10681,20 +10681,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>690621</v>
+        <v>690550</v>
       </c>
       <c r="R99" t="n">
-        <v>7096899</v>
+        <v>7097011</v>
       </c>
       <c r="S99" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10732,18 +10748,19 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10754,10 +10771,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126931569</v>
+        <v>126931572</v>
       </c>
       <c r="B100" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10784,7 +10801,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -10792,11 +10809,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
@@ -10805,10 +10818,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>690550</v>
+        <v>690665</v>
       </c>
       <c r="R100" t="n">
-        <v>7097011</v>
+        <v>7096920</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10872,57 +10885,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126931572</v>
+        <v>126936880</v>
       </c>
       <c r="B101" t="n">
-        <v>98442</v>
+        <v>78773</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>690665</v>
+        <v>690619</v>
       </c>
       <c r="R101" t="n">
-        <v>7096920</v>
+        <v>7097003</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10963,19 +10964,18 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -10986,10 +10986,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126927465</v>
+        <v>126931566</v>
       </c>
       <c r="B102" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10997,37 +10997,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>690596</v>
+        <v>690621</v>
       </c>
       <c r="R102" t="n">
-        <v>7097023</v>
+        <v>7096855</v>
       </c>
       <c r="S102" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11071,15 +11071,19 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY102" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11478,7 +11482,7 @@
         <v>126927292</v>
       </c>
       <c r="B107" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11572,10 +11576,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126931566</v>
+        <v>126927465</v>
       </c>
       <c r="B108" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11583,37 +11587,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>690621</v>
+        <v>690596</v>
       </c>
       <c r="R108" t="n">
-        <v>7096855</v>
+        <v>7097023</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11657,19 +11661,15 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY108" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30467-2025 artfynd.xlsx
+++ b/artfynd/A 30467-2025 artfynd.xlsx
@@ -675,49 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126909580</v>
+        <v>126919968</v>
       </c>
       <c r="B2" t="n">
-        <v>98443</v>
+        <v>80021</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Rislidstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>690493</v>
+        <v>690349</v>
       </c>
       <c r="R2" t="n">
-        <v>7097055</v>
+        <v>7097128</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -747,19 +743,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
+          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -790,45 +776,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126919968</v>
+        <v>126909580</v>
       </c>
       <c r="B3" t="n">
-        <v>80021</v>
+        <v>98443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rislidstjärnarna, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>690349</v>
+        <v>690493</v>
       </c>
       <c r="R3" t="n">
-        <v>7097128</v>
+        <v>7097055</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,9 +848,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,12 +875,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
+          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -2994,64 +2994,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126936889</v>
+        <v>126927661</v>
       </c>
       <c r="B24" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>690595</v>
+        <v>690574</v>
       </c>
       <c r="R24" t="n">
-        <v>7096886</v>
+        <v>7096978</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3089,87 +3073,66 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126936886</v>
+        <v>126937624</v>
       </c>
       <c r="B25" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>690607</v>
+        <v>690656</v>
       </c>
       <c r="R25" t="n">
-        <v>7097014</v>
+        <v>7096868</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3207,19 +3170,18 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3230,10 +3192,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126931565</v>
+        <v>126927842</v>
       </c>
       <c r="B26" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3241,37 +3203,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>690620</v>
+        <v>690605</v>
       </c>
       <c r="R26" t="n">
-        <v>7096859</v>
+        <v>7096920</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3315,64 +3277,72 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126927661</v>
+        <v>126936890</v>
       </c>
       <c r="B27" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>690574</v>
+        <v>690564</v>
       </c>
       <c r="R27" t="n">
-        <v>7096978</v>
+        <v>7096907</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3410,66 +3380,87 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126937624</v>
+        <v>126936889</v>
       </c>
       <c r="B28" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>690656</v>
+        <v>690595</v>
       </c>
       <c r="R28" t="n">
-        <v>7096868</v>
+        <v>7096886</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3507,18 +3498,19 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3529,48 +3521,64 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126927842</v>
+        <v>126936886</v>
       </c>
       <c r="B29" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>690605</v>
+        <v>690607</v>
       </c>
       <c r="R29" t="n">
-        <v>7096920</v>
+        <v>7097014</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3608,75 +3616,68 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126936890</v>
+        <v>126931565</v>
       </c>
       <c r="B30" t="n">
-        <v>98443</v>
+        <v>78773</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>690564</v>
+        <v>690620</v>
       </c>
       <c r="R30" t="n">
-        <v>7096907</v>
+        <v>7096859</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3717,19 +3718,18 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3740,7 +3740,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126936897</v>
+        <v>126927550</v>
       </c>
       <c r="B31" t="n">
         <v>79014</v>
@@ -3771,17 +3771,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>690544</v>
+        <v>690574</v>
       </c>
       <c r="R31" t="n">
-        <v>7096906</v>
+        <v>7096994</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3825,23 +3825,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126936883</v>
+        <v>126937621</v>
       </c>
       <c r="B32" t="n">
         <v>98443</v>
@@ -3869,36 +3865,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>690668</v>
+        <v>690635</v>
       </c>
       <c r="R32" t="n">
-        <v>7096918</v>
+        <v>7096944</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3930,25 +3910,29 @@
           <t>2025-07-26</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ca 40 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3959,7 +3943,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126927550</v>
+        <v>126936897</v>
       </c>
       <c r="B33" t="n">
         <v>79014</v>
@@ -3990,17 +3974,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>690574</v>
+        <v>690544</v>
       </c>
       <c r="R33" t="n">
-        <v>7096994</v>
+        <v>7096906</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4044,19 +4028,23 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126937621</v>
+        <v>126936883</v>
       </c>
       <c r="B34" t="n">
         <v>98443</v>
@@ -4084,20 +4072,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>690635</v>
+        <v>690668</v>
       </c>
       <c r="R34" t="n">
-        <v>7096944</v>
+        <v>7096918</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4129,29 +4133,25 @@
           <t>2025-07-26</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ca 40 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4501,45 +4501,57 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126926531</v>
+        <v>126936887</v>
       </c>
       <c r="B38" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>690376</v>
+        <v>690632</v>
       </c>
       <c r="R38" t="n">
-        <v>7097225</v>
+        <v>7096922</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4580,25 +4592,30 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126936910</v>
+        <v>126926531</v>
       </c>
       <c r="B39" t="n">
         <v>79014</v>
@@ -4629,14 +4646,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>690572</v>
+        <v>690376</v>
       </c>
       <c r="R39" t="n">
-        <v>7096932</v>
+        <v>7097225</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4683,23 +4700,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126936900</v>
+        <v>126936910</v>
       </c>
       <c r="B40" t="n">
         <v>79014</v>
@@ -4734,10 +4747,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>690663</v>
+        <v>690572</v>
       </c>
       <c r="R40" t="n">
-        <v>7096854</v>
+        <v>7096932</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4800,57 +4813,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126936887</v>
+        <v>126936900</v>
       </c>
       <c r="B41" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>690632</v>
+        <v>690663</v>
       </c>
       <c r="R41" t="n">
-        <v>7096922</v>
+        <v>7096854</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4891,7 +4892,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5424,7 +5424,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126937623</v>
+        <v>126936911</v>
       </c>
       <c r="B47" t="n">
         <v>79014</v>
@@ -5455,17 +5455,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>690707</v>
+        <v>690481</v>
       </c>
       <c r="R47" t="n">
-        <v>7096903</v>
+        <v>7097028</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5509,12 +5509,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5525,45 +5525,57 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126936911</v>
+        <v>126936885</v>
       </c>
       <c r="B48" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>690481</v>
+        <v>690596</v>
       </c>
       <c r="R48" t="n">
-        <v>7097028</v>
+        <v>7097007</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5604,6 +5616,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5824,10 +5837,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126936877</v>
+        <v>126937623</v>
       </c>
       <c r="B51" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5835,37 +5848,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>690378</v>
+        <v>690707</v>
       </c>
       <c r="R51" t="n">
-        <v>7096984</v>
+        <v>7096903</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5909,12 +5922,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5925,57 +5938,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126936885</v>
+        <v>126936877</v>
       </c>
       <c r="B52" t="n">
-        <v>98443</v>
+        <v>79632</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>690596</v>
+        <v>690378</v>
       </c>
       <c r="R52" t="n">
-        <v>7097007</v>
+        <v>7096984</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6016,7 +6017,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6039,10 +6039,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126927000</v>
+        <v>126936878</v>
       </c>
       <c r="B53" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6050,37 +6050,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>690487</v>
+        <v>690509</v>
       </c>
       <c r="R53" t="n">
-        <v>7097101</v>
+        <v>7096927</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6124,60 +6124,76 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126928117</v>
+        <v>126931571</v>
       </c>
       <c r="B54" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>690540</v>
+        <v>690644</v>
       </c>
       <c r="R54" t="n">
-        <v>7096888</v>
+        <v>7096948</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6215,28 +6231,33 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126936878</v>
+        <v>126927000</v>
       </c>
       <c r="B55" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6244,37 +6265,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>690509</v>
+        <v>690487</v>
       </c>
       <c r="R55" t="n">
-        <v>7096927</v>
+        <v>7097101</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6318,26 +6339,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126927086</v>
+        <v>126928117</v>
       </c>
       <c r="B56" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6345,34 +6362,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>690545</v>
+        <v>690540</v>
       </c>
       <c r="R56" t="n">
-        <v>7097033</v>
+        <v>7096888</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6431,60 +6448,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126931571</v>
+        <v>126927086</v>
       </c>
       <c r="B57" t="n">
-        <v>98443</v>
+        <v>80117</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>690644</v>
+        <v>690545</v>
       </c>
       <c r="R57" t="n">
-        <v>7096948</v>
+        <v>7097033</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6522,33 +6527,28 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126926624</v>
+        <v>126936881</v>
       </c>
       <c r="B58" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6556,37 +6556,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>690399</v>
+        <v>690617</v>
       </c>
       <c r="R58" t="n">
-        <v>7097170</v>
+        <v>7096851</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6630,19 +6630,23 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126926566</v>
+        <v>126926624</v>
       </c>
       <c r="B59" t="n">
         <v>79014</v>
@@ -6677,10 +6681,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>690362</v>
+        <v>690399</v>
       </c>
       <c r="R59" t="n">
-        <v>7097210</v>
+        <v>7097170</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6739,7 +6743,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126937630</v>
+        <v>126926566</v>
       </c>
       <c r="B60" t="n">
         <v>79014</v>
@@ -6770,14 +6774,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>690480</v>
+        <v>690362</v>
       </c>
       <c r="R60" t="n">
-        <v>7096994</v>
+        <v>7097210</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6824,23 +6828,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126927108</v>
+        <v>126937630</v>
       </c>
       <c r="B61" t="n">
         <v>79014</v>
@@ -6871,14 +6871,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>690542</v>
+        <v>690480</v>
       </c>
       <c r="R61" t="n">
-        <v>7097030</v>
+        <v>7096994</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6925,19 +6925,23 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126927426</v>
+        <v>126927108</v>
       </c>
       <c r="B62" t="n">
         <v>79014</v>
@@ -6972,10 +6976,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>690560</v>
+        <v>690542</v>
       </c>
       <c r="R62" t="n">
-        <v>7097019</v>
+        <v>7097030</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7034,10 +7038,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126936881</v>
+        <v>126927426</v>
       </c>
       <c r="B63" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7045,37 +7049,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>690617</v>
+        <v>690560</v>
       </c>
       <c r="R63" t="n">
-        <v>7096851</v>
+        <v>7097019</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7119,23 +7123,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126926457</v>
+        <v>126927067</v>
       </c>
       <c r="B64" t="n">
         <v>79014</v>
@@ -7170,13 +7170,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>690374</v>
+        <v>690536</v>
       </c>
       <c r="R64" t="n">
-        <v>7097232</v>
+        <v>7097045</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126931576</v>
+        <v>126926457</v>
       </c>
       <c r="B65" t="n">
         <v>79014</v>
@@ -7263,17 +7263,17 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>690565</v>
+        <v>690374</v>
       </c>
       <c r="R65" t="n">
-        <v>7096992</v>
+        <v>7097232</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7317,19 +7317,15 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7531,7 +7527,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126927067</v>
+        <v>126931576</v>
       </c>
       <c r="B68" t="n">
         <v>79014</v>
@@ -7562,14 +7558,14 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>690536</v>
+        <v>690565</v>
       </c>
       <c r="R68" t="n">
-        <v>7097045</v>
+        <v>7096992</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7616,15 +7612,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8728,10 +8728,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126931564</v>
+        <v>126927691</v>
       </c>
       <c r="B80" t="n">
-        <v>79046</v>
+        <v>79014</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8739,37 +8739,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>690624</v>
+        <v>690577</v>
       </c>
       <c r="R80" t="n">
-        <v>7096879</v>
+        <v>7096975</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8813,48 +8813,44 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126927691</v>
+        <v>126927343</v>
       </c>
       <c r="B81" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8864,10 +8860,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>690577</v>
+        <v>690544</v>
       </c>
       <c r="R81" t="n">
-        <v>7096975</v>
+        <v>7097007</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8926,32 +8922,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126927343</v>
+        <v>126926723</v>
       </c>
       <c r="B82" t="n">
-        <v>98443</v>
+        <v>78773</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8961,10 +8957,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>690544</v>
+        <v>690433</v>
       </c>
       <c r="R82" t="n">
-        <v>7097007</v>
+        <v>7097136</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9023,10 +9019,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126926723</v>
+        <v>126931564</v>
       </c>
       <c r="B83" t="n">
-        <v>78773</v>
+        <v>79046</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9034,37 +9030,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>690433</v>
+        <v>690624</v>
       </c>
       <c r="R83" t="n">
-        <v>7097136</v>
+        <v>7096879</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9108,15 +9104,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">

--- a/artfynd/A 30467-2025 artfynd.xlsx
+++ b/artfynd/A 30467-2025 artfynd.xlsx
@@ -1005,32 +1005,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126917563</v>
+        <v>126917550</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>80153</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>690509</v>
+        <v>690515</v>
       </c>
       <c r="R5" t="n">
-        <v>7097052</v>
+        <v>7097014</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,32 +1106,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126917550</v>
+        <v>126917563</v>
       </c>
       <c r="B6" t="n">
-        <v>80153</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>690515</v>
+        <v>690509</v>
       </c>
       <c r="R6" t="n">
-        <v>7097014</v>
+        <v>7097052</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1726,7 +1726,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126909413</v>
+        <v>126909538</v>
       </c>
       <c r="B12" t="n">
         <v>98443</v>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>690516</v>
+        <v>690484</v>
       </c>
       <c r="R12" t="n">
-        <v>7097033</v>
+        <v>7097073</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1841,7 +1841,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126909538</v>
+        <v>126909413</v>
       </c>
       <c r="B13" t="n">
         <v>98443</v>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>690484</v>
+        <v>690516</v>
       </c>
       <c r="R13" t="n">
-        <v>7097073</v>
+        <v>7097033</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2796,45 +2796,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126931573</v>
+        <v>126926856</v>
       </c>
       <c r="B22" t="n">
-        <v>98443</v>
+        <v>78773</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>N Johannesbomyran, N Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>690578</v>
+        <v>690563</v>
       </c>
       <c r="R22" t="n">
-        <v>7096991</v>
+        <v>7096856</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2881,61 +2881,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126926856</v>
+        <v>126931573</v>
       </c>
       <c r="B23" t="n">
-        <v>78773</v>
+        <v>98443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>N Johannesbomyran, N Johannesbomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>690563</v>
+        <v>690578</v>
       </c>
       <c r="R23" t="n">
-        <v>7096856</v>
+        <v>7096991</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2982,15 +2978,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3289,7 +3289,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126936890</v>
+        <v>126936886</v>
       </c>
       <c r="B27" t="n">
         <v>98443</v>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3327,7 +3327,11 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
@@ -3336,10 +3340,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>690564</v>
+        <v>690607</v>
       </c>
       <c r="R27" t="n">
-        <v>7096907</v>
+        <v>7097014</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3403,7 +3407,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126936889</v>
+        <v>126936890</v>
       </c>
       <c r="B28" t="n">
         <v>98443</v>
@@ -3433,7 +3437,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3441,11 +3445,7 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3454,10 +3454,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>690595</v>
+        <v>690564</v>
       </c>
       <c r="R28" t="n">
-        <v>7096886</v>
+        <v>7096907</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3521,7 +3521,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126936886</v>
+        <v>126936889</v>
       </c>
       <c r="B29" t="n">
         <v>98443</v>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3572,10 +3572,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>690607</v>
+        <v>690595</v>
       </c>
       <c r="R29" t="n">
-        <v>7097014</v>
+        <v>7096886</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3740,7 +3740,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126927550</v>
+        <v>126936897</v>
       </c>
       <c r="B31" t="n">
         <v>79014</v>
@@ -3771,17 +3771,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>690574</v>
+        <v>690544</v>
       </c>
       <c r="R31" t="n">
-        <v>7096994</v>
+        <v>7096906</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3825,57 +3825,61 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126937621</v>
+        <v>126927550</v>
       </c>
       <c r="B32" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>690635</v>
+        <v>690574</v>
       </c>
       <c r="R32" t="n">
-        <v>7096944</v>
+        <v>7096994</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3910,11 +3914,6 @@
           <t>2025-07-26</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ca 40 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -3927,61 +3926,73 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126936897</v>
+        <v>126936883</v>
       </c>
       <c r="B33" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>690544</v>
+        <v>690668</v>
       </c>
       <c r="R33" t="n">
-        <v>7096906</v>
+        <v>7096918</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4022,6 +4033,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4044,7 +4056,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126936883</v>
+        <v>126937621</v>
       </c>
       <c r="B34" t="n">
         <v>98443</v>
@@ -4072,36 +4084,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>690668</v>
+        <v>690635</v>
       </c>
       <c r="R34" t="n">
-        <v>7096918</v>
+        <v>7096944</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4133,25 +4129,29 @@
           <t>2025-07-26</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ca 40 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4162,7 +4162,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126931567</v>
+        <v>126937620</v>
       </c>
       <c r="B35" t="n">
         <v>98443</v>
@@ -4190,32 +4190,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>690686</v>
+        <v>690612</v>
       </c>
       <c r="R35" t="n">
-        <v>7096928</v>
+        <v>7096930</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4245,6 +4237,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Cirka 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4260,12 +4257,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4276,7 +4273,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126937620</v>
+        <v>126936888</v>
       </c>
       <c r="B36" t="n">
         <v>98443</v>
@@ -4304,24 +4301,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>690612</v>
+        <v>690639</v>
       </c>
       <c r="R36" t="n">
-        <v>7096930</v>
+        <v>7096927</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4351,11 +4356,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Cirka 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4371,12 +4371,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4387,7 +4387,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126936888</v>
+        <v>126931567</v>
       </c>
       <c r="B37" t="n">
         <v>98443</v>
@@ -4417,12 +4417,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -4430,14 +4430,14 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>690639</v>
+        <v>690686</v>
       </c>
       <c r="R37" t="n">
-        <v>7096927</v>
+        <v>7096928</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4485,12 +4485,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4501,57 +4501,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126936887</v>
+        <v>126936900</v>
       </c>
       <c r="B38" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>690632</v>
+        <v>690663</v>
       </c>
       <c r="R38" t="n">
-        <v>7096922</v>
+        <v>7096854</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4592,7 +4580,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4615,7 +4602,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126926531</v>
+        <v>126936910</v>
       </c>
       <c r="B39" t="n">
         <v>79014</v>
@@ -4646,14 +4633,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>690376</v>
+        <v>690572</v>
       </c>
       <c r="R39" t="n">
-        <v>7097225</v>
+        <v>7096932</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4700,19 +4687,23 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126936910</v>
+        <v>126926531</v>
       </c>
       <c r="B40" t="n">
         <v>79014</v>
@@ -4743,14 +4734,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>690572</v>
+        <v>690376</v>
       </c>
       <c r="R40" t="n">
-        <v>7096932</v>
+        <v>7097225</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4797,61 +4788,69 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126936900</v>
+        <v>126936887</v>
       </c>
       <c r="B41" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>690663</v>
+        <v>690632</v>
       </c>
       <c r="R41" t="n">
-        <v>7096854</v>
+        <v>7096922</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4892,6 +4891,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4914,48 +4914,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126936894</v>
+        <v>126926789</v>
       </c>
       <c r="B42" t="n">
-        <v>98443</v>
+        <v>91346</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>690497</v>
+        <v>690438</v>
       </c>
       <c r="R42" t="n">
-        <v>7097017</v>
+        <v>7097141</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4999,64 +4999,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126926789</v>
+        <v>126936894</v>
       </c>
       <c r="B43" t="n">
-        <v>91346</v>
+        <v>98443</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>690438</v>
+        <v>690497</v>
       </c>
       <c r="R43" t="n">
-        <v>7097141</v>
+        <v>7097017</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5100,22 +5096,26 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126926859</v>
+        <v>126936882</v>
       </c>
       <c r="B44" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5123,37 +5123,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>690483</v>
+        <v>690560</v>
       </c>
       <c r="R44" t="n">
-        <v>7097114</v>
+        <v>7096959</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5197,15 +5197,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5323,10 +5327,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126936882</v>
+        <v>126926859</v>
       </c>
       <c r="B46" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5334,37 +5338,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>690560</v>
+        <v>690483</v>
       </c>
       <c r="R46" t="n">
-        <v>7096959</v>
+        <v>7097114</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5408,23 +5412,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126936911</v>
+        <v>126937632</v>
       </c>
       <c r="B47" t="n">
         <v>79014</v>
@@ -5455,17 +5455,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>690481</v>
+        <v>690454</v>
       </c>
       <c r="R47" t="n">
-        <v>7097028</v>
+        <v>7097036</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5509,12 +5509,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5525,57 +5525,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126936885</v>
+        <v>126936911</v>
       </c>
       <c r="B48" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>690596</v>
+        <v>690481</v>
       </c>
       <c r="R48" t="n">
-        <v>7097007</v>
+        <v>7097028</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5616,7 +5604,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5639,7 +5626,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126928173</v>
+        <v>126937623</v>
       </c>
       <c r="B49" t="n">
         <v>79014</v>
@@ -5670,14 +5657,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>690547</v>
+        <v>690707</v>
       </c>
       <c r="R49" t="n">
-        <v>7096876</v>
+        <v>7096903</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5724,22 +5711,26 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126937632</v>
+        <v>126936877</v>
       </c>
       <c r="B50" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5747,37 +5738,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>690454</v>
+        <v>690378</v>
       </c>
       <c r="R50" t="n">
-        <v>7097036</v>
+        <v>7096984</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5821,12 +5812,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5837,7 +5828,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126937623</v>
+        <v>126928173</v>
       </c>
       <c r="B51" t="n">
         <v>79014</v>
@@ -5868,14 +5859,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>690707</v>
+        <v>690547</v>
       </c>
       <c r="R51" t="n">
-        <v>7096903</v>
+        <v>7096876</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5922,61 +5913,69 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126936877</v>
+        <v>126936885</v>
       </c>
       <c r="B52" t="n">
-        <v>79632</v>
+        <v>98443</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>690378</v>
+        <v>690596</v>
       </c>
       <c r="R52" t="n">
-        <v>7096984</v>
+        <v>7097007</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6017,6 +6016,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6039,10 +6039,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126936878</v>
+        <v>126927000</v>
       </c>
       <c r="B53" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6050,37 +6050,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>690509</v>
+        <v>690487</v>
       </c>
       <c r="R53" t="n">
-        <v>7096927</v>
+        <v>7097101</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6124,76 +6124,60 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126931571</v>
+        <v>126928117</v>
       </c>
       <c r="B54" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>690644</v>
+        <v>690540</v>
       </c>
       <c r="R54" t="n">
-        <v>7096948</v>
+        <v>7096888</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6231,33 +6215,28 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126927000</v>
+        <v>126927086</v>
       </c>
       <c r="B55" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6265,21 +6244,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6289,10 +6268,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>690487</v>
+        <v>690545</v>
       </c>
       <c r="R55" t="n">
-        <v>7097101</v>
+        <v>7097033</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6351,10 +6330,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126928117</v>
+        <v>126936878</v>
       </c>
       <c r="B56" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6362,37 +6341,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>690540</v>
+        <v>690509</v>
       </c>
       <c r="R56" t="n">
-        <v>7096888</v>
+        <v>7096927</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6436,60 +6415,76 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126927086</v>
+        <v>126931571</v>
       </c>
       <c r="B57" t="n">
-        <v>80117</v>
+        <v>98443</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>690545</v>
+        <v>690644</v>
       </c>
       <c r="R57" t="n">
-        <v>7097033</v>
+        <v>7096948</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6527,28 +6522,33 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126936881</v>
+        <v>126926624</v>
       </c>
       <c r="B58" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6556,37 +6556,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>690617</v>
+        <v>690399</v>
       </c>
       <c r="R58" t="n">
-        <v>7096851</v>
+        <v>7097170</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6630,23 +6630,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126926624</v>
+        <v>126926566</v>
       </c>
       <c r="B59" t="n">
         <v>79014</v>
@@ -6681,10 +6677,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>690399</v>
+        <v>690362</v>
       </c>
       <c r="R59" t="n">
-        <v>7097170</v>
+        <v>7097210</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6743,7 +6739,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126926566</v>
+        <v>126937630</v>
       </c>
       <c r="B60" t="n">
         <v>79014</v>
@@ -6774,14 +6770,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>690362</v>
+        <v>690480</v>
       </c>
       <c r="R60" t="n">
-        <v>7097210</v>
+        <v>7096994</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6828,19 +6824,23 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126937630</v>
+        <v>126927108</v>
       </c>
       <c r="B61" t="n">
         <v>79014</v>
@@ -6871,14 +6871,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>690480</v>
+        <v>690542</v>
       </c>
       <c r="R61" t="n">
-        <v>7096994</v>
+        <v>7097030</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6925,23 +6925,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126927108</v>
+        <v>126927426</v>
       </c>
       <c r="B62" t="n">
         <v>79014</v>
@@ -6976,10 +6972,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>690542</v>
+        <v>690560</v>
       </c>
       <c r="R62" t="n">
-        <v>7097030</v>
+        <v>7097019</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7038,10 +7034,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126927426</v>
+        <v>126936881</v>
       </c>
       <c r="B63" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7049,37 +7045,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>690560</v>
+        <v>690617</v>
       </c>
       <c r="R63" t="n">
-        <v>7097019</v>
+        <v>7096851</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7123,15 +7119,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7329,48 +7329,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126927409</v>
+        <v>126931576</v>
       </c>
       <c r="B66" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>690545</v>
+        <v>690565</v>
       </c>
       <c r="R66" t="n">
-        <v>7097003</v>
+        <v>7096992</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7414,19 +7414,23 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126936893</v>
+        <v>126927409</v>
       </c>
       <c r="B67" t="n">
         <v>98443</v>
@@ -7457,17 +7461,17 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>690658</v>
+        <v>690545</v>
       </c>
       <c r="R67" t="n">
-        <v>7096938</v>
+        <v>7097003</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7511,61 +7515,57 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126931576</v>
+        <v>126936893</v>
       </c>
       <c r="B68" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>690565</v>
+        <v>690658</v>
       </c>
       <c r="R68" t="n">
-        <v>7096992</v>
+        <v>7096938</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7612,12 +7612,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7923,48 +7923,60 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126927191</v>
+        <v>126936891</v>
       </c>
       <c r="B72" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>690524</v>
+        <v>690644</v>
       </c>
       <c r="R72" t="n">
-        <v>7097009</v>
+        <v>7096931</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8002,25 +8014,30 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126936896</v>
+        <v>126927191</v>
       </c>
       <c r="B73" t="n">
         <v>79014</v>
@@ -8051,17 +8068,17 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>690482</v>
+        <v>690524</v>
       </c>
       <c r="R73" t="n">
-        <v>7096931</v>
+        <v>7097009</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8105,48 +8122,44 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126936879</v>
+        <v>126936896</v>
       </c>
       <c r="B74" t="n">
-        <v>97327</v>
+        <v>79014</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8156,10 +8169,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>690490</v>
+        <v>690482</v>
       </c>
       <c r="R74" t="n">
-        <v>7096937</v>
+        <v>7096931</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8222,57 +8235,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126936891</v>
+        <v>126936879</v>
       </c>
       <c r="B75" t="n">
-        <v>98443</v>
+        <v>97327</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>690644</v>
+        <v>690490</v>
       </c>
       <c r="R75" t="n">
-        <v>7096931</v>
+        <v>7096937</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8313,7 +8314,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8728,7 +8728,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126927691</v>
+        <v>126936909</v>
       </c>
       <c r="B80" t="n">
         <v>79014</v>
@@ -8759,17 +8759,17 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>690577</v>
+        <v>690590</v>
       </c>
       <c r="R80" t="n">
-        <v>7096975</v>
+        <v>7096893</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8813,57 +8813,61 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126927343</v>
+        <v>126937622</v>
       </c>
       <c r="B81" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>690544</v>
+        <v>690620</v>
       </c>
       <c r="R81" t="n">
-        <v>7097007</v>
+        <v>7096858</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8910,22 +8914,26 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126926723</v>
+        <v>126927691</v>
       </c>
       <c r="B82" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8933,21 +8941,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8957,10 +8965,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>690433</v>
+        <v>690577</v>
       </c>
       <c r="R82" t="n">
-        <v>7097136</v>
+        <v>7096975</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9019,48 +9027,48 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126931564</v>
+        <v>126927343</v>
       </c>
       <c r="B83" t="n">
-        <v>79046</v>
+        <v>98443</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>690624</v>
+        <v>690544</v>
       </c>
       <c r="R83" t="n">
-        <v>7096879</v>
+        <v>7097007</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9104,26 +9112,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126936909</v>
+        <v>126931564</v>
       </c>
       <c r="B84" t="n">
-        <v>79014</v>
+        <v>79046</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9131,34 +9135,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>690590</v>
+        <v>690624</v>
       </c>
       <c r="R84" t="n">
-        <v>7096893</v>
+        <v>7096879</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9205,12 +9209,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9221,10 +9225,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126937622</v>
+        <v>126926723</v>
       </c>
       <c r="B85" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9232,34 +9236,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>690620</v>
+        <v>690433</v>
       </c>
       <c r="R85" t="n">
-        <v>7096858</v>
+        <v>7097136</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9306,23 +9310,19 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126927737</v>
+        <v>126936899</v>
       </c>
       <c r="B86" t="n">
         <v>79014</v>
@@ -9353,17 +9353,17 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>690623</v>
+        <v>690607</v>
       </c>
       <c r="R86" t="n">
-        <v>7096931</v>
+        <v>7097019</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9407,19 +9407,23 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126936899</v>
+        <v>126927737</v>
       </c>
       <c r="B87" t="n">
         <v>79014</v>
@@ -9450,17 +9454,17 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>690607</v>
+        <v>690623</v>
       </c>
       <c r="R87" t="n">
-        <v>7097019</v>
+        <v>7096931</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9504,19 +9508,15 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9621,48 +9621,48 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126926697</v>
+        <v>126936913</v>
       </c>
       <c r="B89" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>690438</v>
+        <v>690466</v>
       </c>
       <c r="R89" t="n">
-        <v>7097148</v>
+        <v>7096945</v>
       </c>
       <c r="S89" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9706,69 +9706,61 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126936892</v>
+        <v>126936895</v>
       </c>
       <c r="B90" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>690619</v>
+        <v>690445</v>
       </c>
       <c r="R90" t="n">
-        <v>7096955</v>
+        <v>7096945</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9809,7 +9801,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9832,48 +9823,48 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126936913</v>
+        <v>126926697</v>
       </c>
       <c r="B91" t="n">
-        <v>92616</v>
+        <v>79014</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>690466</v>
+        <v>690438</v>
       </c>
       <c r="R91" t="n">
-        <v>7096945</v>
+        <v>7097148</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9917,26 +9908,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126936895</v>
+        <v>126937616</v>
       </c>
       <c r="B92" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9944,37 +9931,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>690445</v>
+        <v>690516</v>
       </c>
       <c r="R92" t="n">
-        <v>7096945</v>
+        <v>7096946</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10018,12 +10005,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10034,48 +10021,60 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126937616</v>
+        <v>126936892</v>
       </c>
       <c r="B93" t="n">
-        <v>79632</v>
+        <v>98443</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>690516</v>
+        <v>690619</v>
       </c>
       <c r="R93" t="n">
-        <v>7096946</v>
+        <v>7096955</v>
       </c>
       <c r="S93" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10113,18 +10112,19 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10135,10 +10135,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126936898</v>
+        <v>126936880</v>
       </c>
       <c r="B94" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10146,21 +10146,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10170,10 +10170,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>690576</v>
+        <v>690619</v>
       </c>
       <c r="R94" t="n">
-        <v>7096919</v>
+        <v>7097003</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10236,48 +10236,60 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126937627</v>
+        <v>126931572</v>
       </c>
       <c r="B95" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>690522</v>
+        <v>690665</v>
       </c>
       <c r="R95" t="n">
-        <v>7096919</v>
+        <v>7096920</v>
       </c>
       <c r="S95" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10315,18 +10327,19 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10337,45 +10350,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126927128</v>
+        <v>126937619</v>
       </c>
       <c r="B96" t="n">
-        <v>80117</v>
+        <v>98443</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>690517</v>
+        <v>690621</v>
       </c>
       <c r="R96" t="n">
-        <v>7097014</v>
+        <v>7096899</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -10422,19 +10435,23 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126936884</v>
+        <v>126931569</v>
       </c>
       <c r="B97" t="n">
         <v>98443</v>
@@ -10464,12 +10481,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -10481,14 +10498,14 @@
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>690609</v>
+        <v>690550</v>
       </c>
       <c r="R97" t="n">
-        <v>7096953</v>
+        <v>7097011</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10536,12 +10553,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10552,7 +10569,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126937619</v>
+        <v>126936884</v>
       </c>
       <c r="B98" t="n">
         <v>98443</v>
@@ -10580,20 +10597,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>690621</v>
+        <v>690609</v>
       </c>
       <c r="R98" t="n">
-        <v>7096899</v>
+        <v>7096953</v>
       </c>
       <c r="S98" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10631,18 +10664,19 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10653,61 +10687,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126931569</v>
+        <v>126936898</v>
       </c>
       <c r="B99" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>690550</v>
+        <v>690576</v>
       </c>
       <c r="R99" t="n">
-        <v>7097011</v>
+        <v>7096919</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10748,19 +10766,18 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10771,60 +10788,48 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126931572</v>
+        <v>126937627</v>
       </c>
       <c r="B100" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>690665</v>
+        <v>690522</v>
       </c>
       <c r="R100" t="n">
-        <v>7096920</v>
+        <v>7096919</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10862,19 +10867,18 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10885,10 +10889,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126936880</v>
+        <v>126927128</v>
       </c>
       <c r="B101" t="n">
-        <v>78773</v>
+        <v>80117</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10896,37 +10900,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>690619</v>
+        <v>690517</v>
       </c>
       <c r="R101" t="n">
-        <v>7097003</v>
+        <v>7097014</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10970,64 +10974,60 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY101" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126931566</v>
+        <v>126927292</v>
       </c>
       <c r="B102" t="n">
-        <v>78772</v>
+        <v>98443</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>690621</v>
+        <v>690530</v>
       </c>
       <c r="R102" t="n">
-        <v>7096855</v>
+        <v>7097014</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11071,64 +11071,60 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY102" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126931577</v>
+        <v>126927465</v>
       </c>
       <c r="B103" t="n">
-        <v>80052</v>
+        <v>79014</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>690656</v>
+        <v>690596</v>
       </c>
       <c r="R103" t="n">
-        <v>7096927</v>
+        <v>7097023</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11172,26 +11168,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY103" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126927178</v>
+        <v>126931577</v>
       </c>
       <c r="B104" t="n">
-        <v>80146</v>
+        <v>80052</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11199,37 +11191,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6462</v>
+        <v>6457</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>690520</v>
+        <v>690656</v>
       </c>
       <c r="R104" t="n">
-        <v>7097024</v>
+        <v>7096927</v>
       </c>
       <c r="S104" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11273,44 +11265,48 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY104" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126927184</v>
+        <v>126927178</v>
       </c>
       <c r="B105" t="n">
-        <v>80117</v>
+        <v>80146</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11382,32 +11378,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126927139</v>
+        <v>126927184</v>
       </c>
       <c r="B106" t="n">
-        <v>80146</v>
+        <v>80117</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11417,10 +11413,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>690515</v>
+        <v>690520</v>
       </c>
       <c r="R106" t="n">
-        <v>7097011</v>
+        <v>7097024</v>
       </c>
       <c r="S106" t="n">
         <v>15</v>
@@ -11479,32 +11475,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126927292</v>
+        <v>126927139</v>
       </c>
       <c r="B107" t="n">
-        <v>98443</v>
+        <v>80146</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11514,10 +11510,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>690530</v>
+        <v>690515</v>
       </c>
       <c r="R107" t="n">
-        <v>7097014</v>
+        <v>7097011</v>
       </c>
       <c r="S107" t="n">
         <v>15</v>
@@ -11576,10 +11572,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126927465</v>
+        <v>126931566</v>
       </c>
       <c r="B108" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11587,37 +11583,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>690596</v>
+        <v>690621</v>
       </c>
       <c r="R108" t="n">
-        <v>7097023</v>
+        <v>7096855</v>
       </c>
       <c r="S108" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11661,15 +11657,19 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY108" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30467-2025 artfynd.xlsx
+++ b/artfynd/A 30467-2025 artfynd.xlsx
@@ -1409,49 +1409,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126919966</v>
+        <v>126909288</v>
       </c>
       <c r="B9" t="n">
-        <v>91337</v>
+        <v>78773</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1205</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rislidstjärnarna, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>690349</v>
+        <v>690438</v>
       </c>
       <c r="R9" t="n">
-        <v>7097128</v>
+        <v>7097136</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,9 +1477,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1498,12 +1504,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
+          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1514,10 +1520,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126917545</v>
+        <v>126919966</v>
       </c>
       <c r="B10" t="n">
-        <v>80021</v>
+        <v>91337</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1525,34 +1531,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>1205</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rislidtjärnarna, Ång</t>
+          <t>Rislidstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>690344</v>
+        <v>690349</v>
       </c>
       <c r="R10" t="n">
-        <v>7097126</v>
+        <v>7097128</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1599,12 +1609,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1615,45 +1625,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126909288</v>
+        <v>126917545</v>
       </c>
       <c r="B11" t="n">
-        <v>78773</v>
+        <v>80021</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Rislidtjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>690438</v>
+        <v>690344</v>
       </c>
       <c r="R11" t="n">
-        <v>7097136</v>
+        <v>7097126</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1683,19 +1693,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1710,12 +1710,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1726,7 +1726,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126909538</v>
+        <v>126909413</v>
       </c>
       <c r="B12" t="n">
         <v>98443</v>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>690484</v>
+        <v>690516</v>
       </c>
       <c r="R12" t="n">
-        <v>7097073</v>
+        <v>7097033</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1841,7 +1841,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126909413</v>
+        <v>126909538</v>
       </c>
       <c r="B13" t="n">
         <v>98443</v>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>690516</v>
+        <v>690484</v>
       </c>
       <c r="R13" t="n">
-        <v>7097033</v>
+        <v>7097073</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -3289,61 +3289,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126936886</v>
+        <v>126931565</v>
       </c>
       <c r="B27" t="n">
-        <v>98443</v>
+        <v>78773</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>690607</v>
+        <v>690620</v>
       </c>
       <c r="R27" t="n">
-        <v>7097014</v>
+        <v>7096859</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3384,19 +3368,18 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3407,7 +3390,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126936890</v>
+        <v>126936886</v>
       </c>
       <c r="B28" t="n">
         <v>98443</v>
@@ -3437,7 +3420,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3445,7 +3428,11 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3454,10 +3441,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>690564</v>
+        <v>690607</v>
       </c>
       <c r="R28" t="n">
-        <v>7096907</v>
+        <v>7097014</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3521,7 +3508,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126936889</v>
+        <v>126936890</v>
       </c>
       <c r="B29" t="n">
         <v>98443</v>
@@ -3551,7 +3538,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3559,11 +3546,7 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
@@ -3572,10 +3555,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>690595</v>
+        <v>690564</v>
       </c>
       <c r="R29" t="n">
-        <v>7096886</v>
+        <v>7096907</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3639,45 +3622,61 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126931565</v>
+        <v>126936889</v>
       </c>
       <c r="B30" t="n">
-        <v>78773</v>
+        <v>98443</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>690620</v>
+        <v>690595</v>
       </c>
       <c r="R30" t="n">
-        <v>7096859</v>
+        <v>7096886</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3718,18 +3717,19 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -5112,10 +5112,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126936882</v>
+        <v>126926859</v>
       </c>
       <c r="B44" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5123,37 +5123,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>690560</v>
+        <v>690483</v>
       </c>
       <c r="R44" t="n">
-        <v>7096959</v>
+        <v>7097114</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5197,19 +5197,15 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5327,10 +5323,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126926859</v>
+        <v>126936882</v>
       </c>
       <c r="B46" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5338,37 +5334,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>690483</v>
+        <v>690560</v>
       </c>
       <c r="R46" t="n">
-        <v>7097114</v>
+        <v>7096959</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5412,60 +5408,76 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126937632</v>
+        <v>126936885</v>
       </c>
       <c r="B47" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>690454</v>
+        <v>690596</v>
       </c>
       <c r="R47" t="n">
-        <v>7097036</v>
+        <v>7097007</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5503,18 +5515,19 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5525,7 +5538,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126936911</v>
+        <v>126937632</v>
       </c>
       <c r="B48" t="n">
         <v>79014</v>
@@ -5556,17 +5569,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>690481</v>
+        <v>690454</v>
       </c>
       <c r="R48" t="n">
-        <v>7097028</v>
+        <v>7097036</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5610,12 +5623,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5626,7 +5639,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126937623</v>
+        <v>126936911</v>
       </c>
       <c r="B49" t="n">
         <v>79014</v>
@@ -5657,17 +5670,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>690707</v>
+        <v>690481</v>
       </c>
       <c r="R49" t="n">
-        <v>7096903</v>
+        <v>7097028</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5711,12 +5724,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5727,10 +5740,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126936877</v>
+        <v>126937623</v>
       </c>
       <c r="B50" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5738,37 +5751,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>690378</v>
+        <v>690707</v>
       </c>
       <c r="R50" t="n">
-        <v>7096984</v>
+        <v>7096903</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5812,12 +5825,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5828,10 +5841,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126928173</v>
+        <v>126936877</v>
       </c>
       <c r="B51" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5839,37 +5852,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>690547</v>
+        <v>690378</v>
       </c>
       <c r="R51" t="n">
-        <v>7096876</v>
+        <v>7096984</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5913,72 +5926,64 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126936885</v>
+        <v>126928173</v>
       </c>
       <c r="B52" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>690596</v>
+        <v>690547</v>
       </c>
       <c r="R52" t="n">
-        <v>7097007</v>
+        <v>7096876</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6016,26 +6021,21 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7135,32 +7135,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126927067</v>
+        <v>126927409</v>
       </c>
       <c r="B64" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7170,13 +7170,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>690536</v>
+        <v>690545</v>
       </c>
       <c r="R64" t="n">
-        <v>7097045</v>
+        <v>7097003</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7232,48 +7232,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126926457</v>
+        <v>126936893</v>
       </c>
       <c r="B65" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>690374</v>
+        <v>690658</v>
       </c>
       <c r="R65" t="n">
-        <v>7097232</v>
+        <v>7096938</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7317,19 +7317,23 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126931576</v>
+        <v>126927067</v>
       </c>
       <c r="B66" t="n">
         <v>79014</v>
@@ -7360,14 +7364,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>690565</v>
+        <v>690536</v>
       </c>
       <c r="R66" t="n">
-        <v>7096992</v>
+        <v>7097045</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7414,48 +7418,44 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126927409</v>
+        <v>126926457</v>
       </c>
       <c r="B67" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7465,10 +7465,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>690545</v>
+        <v>690374</v>
       </c>
       <c r="R67" t="n">
-        <v>7097003</v>
+        <v>7097232</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7527,45 +7527,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126936893</v>
+        <v>126931576</v>
       </c>
       <c r="B68" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>690658</v>
+        <v>690565</v>
       </c>
       <c r="R68" t="n">
-        <v>7096938</v>
+        <v>7096992</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7612,12 +7612,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -8728,10 +8728,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126936909</v>
+        <v>126931564</v>
       </c>
       <c r="B80" t="n">
-        <v>79014</v>
+        <v>79046</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8739,34 +8739,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>690590</v>
+        <v>690624</v>
       </c>
       <c r="R80" t="n">
-        <v>7096893</v>
+        <v>7096879</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8813,12 +8813,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8829,7 +8829,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126937622</v>
+        <v>126936909</v>
       </c>
       <c r="B81" t="n">
         <v>79014</v>
@@ -8860,17 +8860,17 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>690620</v>
+        <v>690590</v>
       </c>
       <c r="R81" t="n">
-        <v>7096858</v>
+        <v>7096893</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8914,12 +8914,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -8930,7 +8930,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126927691</v>
+        <v>126937622</v>
       </c>
       <c r="B82" t="n">
         <v>79014</v>
@@ -8961,14 +8961,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>690577</v>
+        <v>690620</v>
       </c>
       <c r="R82" t="n">
-        <v>7096975</v>
+        <v>7096858</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9015,44 +9015,48 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126927343</v>
+        <v>126927691</v>
       </c>
       <c r="B83" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9062,10 +9066,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>690544</v>
+        <v>690577</v>
       </c>
       <c r="R83" t="n">
-        <v>7097007</v>
+        <v>7096975</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9124,10 +9128,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126931564</v>
+        <v>126926723</v>
       </c>
       <c r="B84" t="n">
-        <v>79046</v>
+        <v>78773</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9135,37 +9139,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>690624</v>
+        <v>690433</v>
       </c>
       <c r="R84" t="n">
-        <v>7096879</v>
+        <v>7097136</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9209,48 +9213,44 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126926723</v>
+        <v>126927343</v>
       </c>
       <c r="B85" t="n">
-        <v>78773</v>
+        <v>98443</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9260,10 +9260,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>690433</v>
+        <v>690544</v>
       </c>
       <c r="R85" t="n">
-        <v>7097136</v>
+        <v>7097007</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9621,45 +9621,57 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126936913</v>
+        <v>126936892</v>
       </c>
       <c r="B89" t="n">
-        <v>92616</v>
+        <v>98443</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>690466</v>
+        <v>690619</v>
       </c>
       <c r="R89" t="n">
-        <v>7096945</v>
+        <v>7096955</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9700,6 +9712,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9722,32 +9735,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126936895</v>
+        <v>126936913</v>
       </c>
       <c r="B90" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9757,7 +9770,7 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>690445</v>
+        <v>690466</v>
       </c>
       <c r="R90" t="n">
         <v>7096945</v>
@@ -9823,7 +9836,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126926697</v>
+        <v>126936895</v>
       </c>
       <c r="B91" t="n">
         <v>79014</v>
@@ -9854,17 +9867,17 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>690438</v>
+        <v>690445</v>
       </c>
       <c r="R91" t="n">
-        <v>7097148</v>
+        <v>7096945</v>
       </c>
       <c r="S91" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9908,22 +9921,26 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126937616</v>
+        <v>126926697</v>
       </c>
       <c r="B92" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9931,34 +9948,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>690516</v>
+        <v>690438</v>
       </c>
       <c r="R92" t="n">
-        <v>7096946</v>
+        <v>7097148</v>
       </c>
       <c r="S92" t="n">
         <v>15</v>
@@ -10005,76 +10022,60 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126936892</v>
+        <v>126937616</v>
       </c>
       <c r="B93" t="n">
-        <v>98443</v>
+        <v>79632</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>690619</v>
+        <v>690516</v>
       </c>
       <c r="R93" t="n">
-        <v>7096955</v>
+        <v>7096946</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10112,19 +10113,18 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">

--- a/artfynd/A 30467-2025 artfynd.xlsx
+++ b/artfynd/A 30467-2025 artfynd.xlsx
@@ -5424,60 +5424,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126936885</v>
+        <v>126937632</v>
       </c>
       <c r="B47" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>690596</v>
+        <v>690454</v>
       </c>
       <c r="R47" t="n">
-        <v>7097007</v>
+        <v>7097036</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5515,19 +5503,18 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5538,7 +5525,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126937632</v>
+        <v>126936911</v>
       </c>
       <c r="B48" t="n">
         <v>79014</v>
@@ -5569,17 +5556,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>690454</v>
+        <v>690481</v>
       </c>
       <c r="R48" t="n">
-        <v>7097036</v>
+        <v>7097028</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5623,12 +5610,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5639,7 +5626,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126936911</v>
+        <v>126937623</v>
       </c>
       <c r="B49" t="n">
         <v>79014</v>
@@ -5670,17 +5657,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>690481</v>
+        <v>690707</v>
       </c>
       <c r="R49" t="n">
-        <v>7097028</v>
+        <v>7096903</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5724,12 +5711,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5740,10 +5727,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126937623</v>
+        <v>126936877</v>
       </c>
       <c r="B50" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5751,37 +5738,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>690707</v>
+        <v>690378</v>
       </c>
       <c r="R50" t="n">
-        <v>7096903</v>
+        <v>7096984</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5825,12 +5812,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5841,10 +5828,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126936877</v>
+        <v>126928173</v>
       </c>
       <c r="B51" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5852,37 +5839,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>690378</v>
+        <v>690547</v>
       </c>
       <c r="R51" t="n">
-        <v>7096984</v>
+        <v>7096876</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5926,64 +5913,72 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126928173</v>
+        <v>126936885</v>
       </c>
       <c r="B52" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>690547</v>
+        <v>690596</v>
       </c>
       <c r="R52" t="n">
-        <v>7096876</v>
+        <v>7097007</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6021,21 +6016,26 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7923,60 +7923,48 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126936891</v>
+        <v>126927191</v>
       </c>
       <c r="B72" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>690644</v>
+        <v>690524</v>
       </c>
       <c r="R72" t="n">
-        <v>7096931</v>
+        <v>7097009</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8014,30 +8002,25 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126927191</v>
+        <v>126936896</v>
       </c>
       <c r="B73" t="n">
         <v>79014</v>
@@ -8068,17 +8051,17 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>690524</v>
+        <v>690482</v>
       </c>
       <c r="R73" t="n">
-        <v>7097009</v>
+        <v>7096931</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8122,44 +8105,48 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126936896</v>
+        <v>126936879</v>
       </c>
       <c r="B74" t="n">
-        <v>79014</v>
+        <v>97327</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8169,10 +8156,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>690482</v>
+        <v>690490</v>
       </c>
       <c r="R74" t="n">
-        <v>7096931</v>
+        <v>7096937</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8235,45 +8222,57 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126936879</v>
+        <v>126936891</v>
       </c>
       <c r="B75" t="n">
-        <v>97327</v>
+        <v>98443</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>690490</v>
+        <v>690644</v>
       </c>
       <c r="R75" t="n">
-        <v>7096937</v>
+        <v>7096931</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8314,6 +8313,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -9621,60 +9621,48 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126936892</v>
+        <v>126937616</v>
       </c>
       <c r="B89" t="n">
-        <v>98443</v>
+        <v>79632</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>690619</v>
+        <v>690516</v>
       </c>
       <c r="R89" t="n">
-        <v>7096955</v>
+        <v>7096946</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9712,19 +9700,18 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -10034,48 +10021,60 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126937616</v>
+        <v>126936892</v>
       </c>
       <c r="B93" t="n">
-        <v>79632</v>
+        <v>98443</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>690516</v>
+        <v>690619</v>
       </c>
       <c r="R93" t="n">
-        <v>7096946</v>
+        <v>7096955</v>
       </c>
       <c r="S93" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10113,18 +10112,19 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">

--- a/artfynd/A 30467-2025 artfynd.xlsx
+++ b/artfynd/A 30467-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126919968</v>
       </c>
       <c r="B2" t="n">
-        <v>80021</v>
+        <v>80025</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126909580</v>
       </c>
       <c r="B3" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>126917533</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,32 +1005,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126917550</v>
+        <v>126917563</v>
       </c>
       <c r="B5" t="n">
-        <v>80153</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>690515</v>
+        <v>690509</v>
       </c>
       <c r="R5" t="n">
-        <v>7097014</v>
+        <v>7097052</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,32 +1106,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126917563</v>
+        <v>126917550</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>80157</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>690509</v>
+        <v>690515</v>
       </c>
       <c r="R6" t="n">
-        <v>7097052</v>
+        <v>7097014</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1210,7 @@
         <v>126919976</v>
       </c>
       <c r="B7" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>126917539</v>
       </c>
       <c r="B8" t="n">
-        <v>91337</v>
+        <v>91341</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1409,45 +1409,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126909288</v>
+        <v>126919966</v>
       </c>
       <c r="B9" t="n">
-        <v>78773</v>
+        <v>91341</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>1205</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Rislidstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>690438</v>
+        <v>690349</v>
       </c>
       <c r="R9" t="n">
-        <v>7097136</v>
+        <v>7097128</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1477,19 +1481,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1504,12 +1498,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
+          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1520,49 +1514,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126919966</v>
+        <v>126909288</v>
       </c>
       <c r="B10" t="n">
-        <v>91337</v>
+        <v>78777</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1205</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rislidstjärnarna, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>690349</v>
+        <v>690438</v>
       </c>
       <c r="R10" t="n">
-        <v>7097128</v>
+        <v>7097136</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,9 +1582,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1609,12 +1609,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
+          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1628,7 +1628,7 @@
         <v>126917545</v>
       </c>
       <c r="B11" t="n">
-        <v>80021</v>
+        <v>80025</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>126909413</v>
       </c>
       <c r="B12" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>126909538</v>
       </c>
       <c r="B13" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>126918516</v>
       </c>
       <c r="B14" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>126917549</v>
       </c>
       <c r="B15" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>126918507</v>
       </c>
       <c r="B16" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>126917534</v>
       </c>
       <c r="B17" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>126909505</v>
       </c>
       <c r="B18" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>126927367</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2598,48 +2598,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126936912</v>
+        <v>126927356</v>
       </c>
       <c r="B20" t="n">
-        <v>92616</v>
+        <v>79018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>690392</v>
+        <v>690516</v>
       </c>
       <c r="R20" t="n">
-        <v>7097038</v>
+        <v>7096990</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2683,64 +2683,60 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126927356</v>
+        <v>126936912</v>
       </c>
       <c r="B21" t="n">
-        <v>79014</v>
+        <v>92620</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>690516</v>
+        <v>690392</v>
       </c>
       <c r="R21" t="n">
-        <v>7096990</v>
+        <v>7097038</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2784,57 +2780,61 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126926856</v>
+        <v>126931573</v>
       </c>
       <c r="B22" t="n">
-        <v>78773</v>
+        <v>98447</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>N Johannesbomyran, N Johannesbomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>690563</v>
+        <v>690578</v>
       </c>
       <c r="R22" t="n">
-        <v>7096856</v>
+        <v>7096991</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2881,57 +2881,61 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126931573</v>
+        <v>126926856</v>
       </c>
       <c r="B23" t="n">
-        <v>98443</v>
+        <v>78777</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>N Johannesbomyran, N Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>690578</v>
+        <v>690563</v>
       </c>
       <c r="R23" t="n">
-        <v>7096991</v>
+        <v>7096856</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2978,26 +2982,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>126927661</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3091,10 +3091,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126937624</v>
+        <v>126927842</v>
       </c>
       <c r="B25" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3122,14 +3122,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>690656</v>
+        <v>690605</v>
       </c>
       <c r="R25" t="n">
-        <v>7096868</v>
+        <v>7096920</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3176,26 +3176,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126927842</v>
+        <v>126937624</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3223,14 +3219,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>690605</v>
+        <v>690656</v>
       </c>
       <c r="R26" t="n">
-        <v>7096920</v>
+        <v>7096868</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3277,57 +3273,77 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126931565</v>
+        <v>126936889</v>
       </c>
       <c r="B27" t="n">
-        <v>78773</v>
+        <v>98447</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>690620</v>
+        <v>690595</v>
       </c>
       <c r="R27" t="n">
-        <v>7096859</v>
+        <v>7096886</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3368,18 +3384,19 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3390,10 +3407,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126936886</v>
+        <v>126936890</v>
       </c>
       <c r="B28" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3420,7 +3437,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3428,11 +3445,7 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3441,10 +3454,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>690607</v>
+        <v>690564</v>
       </c>
       <c r="R28" t="n">
-        <v>7097014</v>
+        <v>7096907</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3508,10 +3521,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126936890</v>
+        <v>126936886</v>
       </c>
       <c r="B29" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3538,7 +3551,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3546,7 +3559,11 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
@@ -3555,10 +3572,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>690564</v>
+        <v>690607</v>
       </c>
       <c r="R29" t="n">
-        <v>7096907</v>
+        <v>7097014</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3622,61 +3639,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126936889</v>
+        <v>126931565</v>
       </c>
       <c r="B30" t="n">
-        <v>98443</v>
+        <v>78777</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>690595</v>
+        <v>690620</v>
       </c>
       <c r="R30" t="n">
-        <v>7096886</v>
+        <v>7096859</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3717,19 +3718,18 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3740,10 +3740,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126936897</v>
+        <v>126927550</v>
       </c>
       <c r="B31" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3771,17 +3771,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>690544</v>
+        <v>690574</v>
       </c>
       <c r="R31" t="n">
-        <v>7096906</v>
+        <v>7096994</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3825,61 +3825,57 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126927550</v>
+        <v>126937621</v>
       </c>
       <c r="B32" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>690574</v>
+        <v>690635</v>
       </c>
       <c r="R32" t="n">
-        <v>7096994</v>
+        <v>7096944</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3914,6 +3910,11 @@
           <t>2025-07-26</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ca 40 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -3926,22 +3927,26 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>126936883</v>
       </c>
       <c r="B33" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4056,48 +4061,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126937621</v>
+        <v>126936897</v>
       </c>
       <c r="B34" t="n">
-        <v>98443</v>
+        <v>79018</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>690635</v>
+        <v>690544</v>
       </c>
       <c r="R34" t="n">
-        <v>7096944</v>
+        <v>7096906</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4127,11 +4132,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ca 40 bladrosetter</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4146,12 +4146,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4162,10 +4162,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126937620</v>
+        <v>126931567</v>
       </c>
       <c r="B35" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4190,24 +4190,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>690612</v>
+        <v>690686</v>
       </c>
       <c r="R35" t="n">
-        <v>7096930</v>
+        <v>7096928</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4237,11 +4245,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Cirka 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4257,12 +4260,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4276,7 +4279,7 @@
         <v>126936888</v>
       </c>
       <c r="B36" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4387,10 +4390,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126931567</v>
+        <v>126937620</v>
       </c>
       <c r="B37" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4415,32 +4418,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>690686</v>
+        <v>690612</v>
       </c>
       <c r="R37" t="n">
-        <v>7096928</v>
+        <v>7096930</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4470,6 +4465,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Cirka 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4485,12 +4485,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4501,10 +4501,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126936900</v>
+        <v>126926531</v>
       </c>
       <c r="B38" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4532,14 +4532,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>690663</v>
+        <v>690376</v>
       </c>
       <c r="R38" t="n">
-        <v>7096854</v>
+        <v>7097225</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4586,26 +4586,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126936910</v>
+        <v>126936900</v>
       </c>
       <c r="B39" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4637,10 +4633,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>690572</v>
+        <v>690663</v>
       </c>
       <c r="R39" t="n">
-        <v>7096932</v>
+        <v>7096854</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4703,10 +4699,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126926531</v>
+        <v>126936910</v>
       </c>
       <c r="B40" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4734,14 +4730,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>690376</v>
+        <v>690572</v>
       </c>
       <c r="R40" t="n">
-        <v>7097225</v>
+        <v>7096932</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4788,22 +4784,26 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
         <v>126936887</v>
       </c>
       <c r="B41" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>126926789</v>
       </c>
       <c r="B42" t="n">
-        <v>91346</v>
+        <v>91350</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>126936894</v>
       </c>
       <c r="B43" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5112,48 +5112,60 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126926859</v>
+        <v>126931570</v>
       </c>
       <c r="B44" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>690483</v>
+        <v>690658</v>
       </c>
       <c r="R44" t="n">
-        <v>7097114</v>
+        <v>7096895</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5191,75 +5203,68 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126931570</v>
+        <v>126936882</v>
       </c>
       <c r="B45" t="n">
-        <v>98443</v>
+        <v>78777</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>690658</v>
+        <v>690560</v>
       </c>
       <c r="R45" t="n">
-        <v>7096895</v>
+        <v>7096959</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5300,19 +5305,18 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5323,10 +5327,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126936882</v>
+        <v>126926859</v>
       </c>
       <c r="B46" t="n">
-        <v>78773</v>
+        <v>79018</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5334,37 +5338,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>690560</v>
+        <v>690483</v>
       </c>
       <c r="R46" t="n">
-        <v>7096959</v>
+        <v>7097114</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5408,26 +5412,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126937632</v>
+        <v>126928173</v>
       </c>
       <c r="B47" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5455,14 +5455,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>690454</v>
+        <v>690547</v>
       </c>
       <c r="R47" t="n">
-        <v>7097036</v>
+        <v>7096876</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5509,26 +5509,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126936911</v>
+        <v>126936877</v>
       </c>
       <c r="B48" t="n">
-        <v>79014</v>
+        <v>79636</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5536,21 +5532,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5560,10 +5556,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>690481</v>
+        <v>690378</v>
       </c>
       <c r="R48" t="n">
-        <v>7097028</v>
+        <v>7096984</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5626,10 +5622,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126937623</v>
+        <v>126936911</v>
       </c>
       <c r="B49" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5657,17 +5653,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>690707</v>
+        <v>690481</v>
       </c>
       <c r="R49" t="n">
-        <v>7096903</v>
+        <v>7097028</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5711,12 +5707,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5727,10 +5723,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126936877</v>
+        <v>126937623</v>
       </c>
       <c r="B50" t="n">
-        <v>79632</v>
+        <v>79018</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5738,37 +5734,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>690378</v>
+        <v>690707</v>
       </c>
       <c r="R50" t="n">
-        <v>7096984</v>
+        <v>7096903</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5812,12 +5808,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5828,10 +5824,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126928173</v>
+        <v>126937632</v>
       </c>
       <c r="B51" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5859,14 +5855,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>690547</v>
+        <v>690454</v>
       </c>
       <c r="R51" t="n">
-        <v>7096876</v>
+        <v>7097036</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5913,22 +5909,26 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
         <v>126936885</v>
       </c>
       <c r="B52" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6039,48 +6039,60 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126927000</v>
+        <v>126931571</v>
       </c>
       <c r="B53" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>690487</v>
+        <v>690644</v>
       </c>
       <c r="R53" t="n">
-        <v>7097101</v>
+        <v>7096948</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6118,28 +6130,33 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126928117</v>
+        <v>126927086</v>
       </c>
       <c r="B54" t="n">
-        <v>79014</v>
+        <v>80121</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6147,34 +6164,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>690540</v>
+        <v>690545</v>
       </c>
       <c r="R54" t="n">
-        <v>7096888</v>
+        <v>7097033</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6233,10 +6250,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126927086</v>
+        <v>126927000</v>
       </c>
       <c r="B55" t="n">
-        <v>80117</v>
+        <v>79018</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6244,21 +6261,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6268,10 +6285,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>690545</v>
+        <v>690487</v>
       </c>
       <c r="R55" t="n">
-        <v>7097033</v>
+        <v>7097101</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6333,7 +6350,7 @@
         <v>126936878</v>
       </c>
       <c r="B56" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6431,60 +6448,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126931571</v>
+        <v>126928117</v>
       </c>
       <c r="B57" t="n">
-        <v>98443</v>
+        <v>79018</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>690644</v>
+        <v>690540</v>
       </c>
       <c r="R57" t="n">
-        <v>7096948</v>
+        <v>7096888</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6522,33 +6527,28 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
         <v>126926624</v>
       </c>
       <c r="B58" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6642,10 +6642,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126926566</v>
+        <v>126927108</v>
       </c>
       <c r="B59" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6677,10 +6677,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>690362</v>
+        <v>690542</v>
       </c>
       <c r="R59" t="n">
-        <v>7097210</v>
+        <v>7097030</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6739,10 +6739,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126937630</v>
+        <v>126927426</v>
       </c>
       <c r="B60" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6770,14 +6770,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>690480</v>
+        <v>690560</v>
       </c>
       <c r="R60" t="n">
-        <v>7096994</v>
+        <v>7097019</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6824,26 +6824,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126927108</v>
+        <v>126937630</v>
       </c>
       <c r="B61" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6871,14 +6867,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>690542</v>
+        <v>690480</v>
       </c>
       <c r="R61" t="n">
-        <v>7097030</v>
+        <v>7096994</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6925,22 +6921,26 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126927426</v>
+        <v>126936881</v>
       </c>
       <c r="B62" t="n">
-        <v>79014</v>
+        <v>78777</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6948,37 +6948,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>690560</v>
+        <v>690617</v>
       </c>
       <c r="R62" t="n">
-        <v>7097019</v>
+        <v>7096851</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7022,22 +7022,26 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126936881</v>
+        <v>126926566</v>
       </c>
       <c r="B63" t="n">
-        <v>78773</v>
+        <v>79018</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7045,37 +7049,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>690617</v>
+        <v>690362</v>
       </c>
       <c r="R63" t="n">
-        <v>7096851</v>
+        <v>7097210</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7119,48 +7123,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126927409</v>
+        <v>126927067</v>
       </c>
       <c r="B64" t="n">
-        <v>98443</v>
+        <v>79018</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7170,13 +7170,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>690545</v>
+        <v>690536</v>
       </c>
       <c r="R64" t="n">
-        <v>7097003</v>
+        <v>7097045</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7232,10 +7232,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126936893</v>
+        <v>126927409</v>
       </c>
       <c r="B65" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7263,17 +7263,17 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>690658</v>
+        <v>690545</v>
       </c>
       <c r="R65" t="n">
-        <v>7096938</v>
+        <v>7097003</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7317,61 +7317,57 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126927067</v>
+        <v>126936893</v>
       </c>
       <c r="B66" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>690536</v>
+        <v>690658</v>
       </c>
       <c r="R66" t="n">
-        <v>7097045</v>
+        <v>7096938</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7418,22 +7414,26 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
         <v>126926457</v>
       </c>
       <c r="B67" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         <v>126931576</v>
       </c>
       <c r="B68" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>126926526</v>
       </c>
       <c r="B69" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>126936908</v>
       </c>
       <c r="B70" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>126927324</v>
       </c>
       <c r="B71" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7923,10 +7923,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126927191</v>
+        <v>126936896</v>
       </c>
       <c r="B72" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7954,17 +7954,17 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>690524</v>
+        <v>690482</v>
       </c>
       <c r="R72" t="n">
-        <v>7097009</v>
+        <v>7096931</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8008,54 +8008,70 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126936896</v>
+        <v>126936891</v>
       </c>
       <c r="B73" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>690482</v>
+        <v>690644</v>
       </c>
       <c r="R73" t="n">
         <v>7096931</v>
@@ -8099,6 +8115,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8124,7 +8141,7 @@
         <v>126936879</v>
       </c>
       <c r="B74" t="n">
-        <v>97327</v>
+        <v>97331</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8222,60 +8239,48 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126936891</v>
+        <v>126927191</v>
       </c>
       <c r="B75" t="n">
-        <v>98443</v>
+        <v>79018</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>690644</v>
+        <v>690524</v>
       </c>
       <c r="R75" t="n">
-        <v>7096931</v>
+        <v>7097009</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8313,33 +8318,28 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
         <v>126927943</v>
       </c>
       <c r="B76" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8433,10 +8433,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126937629</v>
+        <v>126927024</v>
       </c>
       <c r="B77" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8464,14 +8464,14 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>690504</v>
+        <v>690503</v>
       </c>
       <c r="R77" t="n">
-        <v>7096980</v>
+        <v>7097060</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8518,26 +8518,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126927024</v>
+        <v>126927395</v>
       </c>
       <c r="B78" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8569,10 +8565,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>690503</v>
+        <v>690542</v>
       </c>
       <c r="R78" t="n">
-        <v>7097060</v>
+        <v>7096989</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8631,10 +8627,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126927395</v>
+        <v>126937629</v>
       </c>
       <c r="B79" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8662,14 +8658,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>690542</v>
+        <v>690504</v>
       </c>
       <c r="R79" t="n">
-        <v>7096989</v>
+        <v>7096980</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8716,22 +8712,26 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126931564</v>
+        <v>126936909</v>
       </c>
       <c r="B80" t="n">
-        <v>79046</v>
+        <v>79018</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8739,34 +8739,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>690624</v>
+        <v>690590</v>
       </c>
       <c r="R80" t="n">
-        <v>7096879</v>
+        <v>7096893</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8813,12 +8813,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8829,10 +8829,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126936909</v>
+        <v>126937622</v>
       </c>
       <c r="B81" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8860,17 +8860,17 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>690590</v>
+        <v>690620</v>
       </c>
       <c r="R81" t="n">
-        <v>7096893</v>
+        <v>7096858</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8914,12 +8914,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -8930,10 +8930,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126937622</v>
+        <v>126927691</v>
       </c>
       <c r="B82" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8961,14 +8961,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>690620</v>
+        <v>690577</v>
       </c>
       <c r="R82" t="n">
-        <v>7096858</v>
+        <v>7096975</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9015,26 +9015,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126927691</v>
+        <v>126931564</v>
       </c>
       <c r="B83" t="n">
-        <v>79014</v>
+        <v>79050</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9042,37 +9038,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>690577</v>
+        <v>690624</v>
       </c>
       <c r="R83" t="n">
-        <v>7096975</v>
+        <v>7096879</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9116,44 +9112,48 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126926723</v>
+        <v>126927343</v>
       </c>
       <c r="B84" t="n">
-        <v>78773</v>
+        <v>98447</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9163,10 +9163,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>690433</v>
+        <v>690544</v>
       </c>
       <c r="R84" t="n">
-        <v>7097136</v>
+        <v>7097007</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9225,32 +9225,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126927343</v>
+        <v>126926723</v>
       </c>
       <c r="B85" t="n">
-        <v>98443</v>
+        <v>78777</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9260,10 +9260,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>690544</v>
+        <v>690433</v>
       </c>
       <c r="R85" t="n">
-        <v>7097007</v>
+        <v>7097136</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9322,10 +9322,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126936899</v>
+        <v>126927737</v>
       </c>
       <c r="B86" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9353,17 +9353,17 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>690607</v>
+        <v>690623</v>
       </c>
       <c r="R86" t="n">
-        <v>7097019</v>
+        <v>7096931</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9407,26 +9407,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126927737</v>
+        <v>126936899</v>
       </c>
       <c r="B87" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9454,17 +9450,17 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>690623</v>
+        <v>690607</v>
       </c>
       <c r="R87" t="n">
-        <v>7096931</v>
+        <v>7097019</v>
       </c>
       <c r="S87" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9508,22 +9504,26 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
         <v>126936901</v>
       </c>
       <c r="B88" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>126937616</v>
       </c>
       <c r="B89" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9722,48 +9722,48 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126936913</v>
+        <v>126926697</v>
       </c>
       <c r="B90" t="n">
-        <v>92616</v>
+        <v>79018</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>690466</v>
+        <v>690438</v>
       </c>
       <c r="R90" t="n">
-        <v>7096945</v>
+        <v>7097148</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9807,26 +9807,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
         <v>126936895</v>
       </c>
       <c r="B91" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9924,48 +9920,48 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126926697</v>
+        <v>126936913</v>
       </c>
       <c r="B92" t="n">
-        <v>79014</v>
+        <v>92620</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>690438</v>
+        <v>690466</v>
       </c>
       <c r="R92" t="n">
-        <v>7097148</v>
+        <v>7096945</v>
       </c>
       <c r="S92" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10009,22 +10005,26 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
         <v>126936892</v>
       </c>
       <c r="B93" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10135,10 +10135,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126936880</v>
+        <v>126936898</v>
       </c>
       <c r="B94" t="n">
-        <v>78773</v>
+        <v>79018</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10146,21 +10146,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10170,10 +10170,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>690619</v>
+        <v>690576</v>
       </c>
       <c r="R94" t="n">
-        <v>7097003</v>
+        <v>7096919</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10236,60 +10236,48 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126931572</v>
+        <v>126927128</v>
       </c>
       <c r="B95" t="n">
-        <v>98443</v>
+        <v>80121</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>690665</v>
+        <v>690517</v>
       </c>
       <c r="R95" t="n">
-        <v>7096920</v>
+        <v>7097014</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10327,55 +10315,50 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126937619</v>
+        <v>126937627</v>
       </c>
       <c r="B96" t="n">
-        <v>98443</v>
+        <v>79018</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10385,10 +10368,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>690621</v>
+        <v>690522</v>
       </c>
       <c r="R96" t="n">
-        <v>7096899</v>
+        <v>7096919</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -10451,10 +10434,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126931569</v>
+        <v>126936884</v>
       </c>
       <c r="B97" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10481,12 +10464,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -10498,14 +10481,14 @@
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>690550</v>
+        <v>690609</v>
       </c>
       <c r="R97" t="n">
-        <v>7097011</v>
+        <v>7096953</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10553,12 +10536,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10569,10 +10552,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126936884</v>
+        <v>126937619</v>
       </c>
       <c r="B98" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10597,36 +10580,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>690609</v>
+        <v>690621</v>
       </c>
       <c r="R98" t="n">
-        <v>7096953</v>
+        <v>7096899</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10664,19 +10631,18 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10687,45 +10653,61 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126936898</v>
+        <v>126931569</v>
       </c>
       <c r="B99" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>690576</v>
+        <v>690550</v>
       </c>
       <c r="R99" t="n">
-        <v>7096919</v>
+        <v>7097011</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10766,18 +10748,19 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10788,48 +10771,60 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126937627</v>
+        <v>126931572</v>
       </c>
       <c r="B100" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>690522</v>
+        <v>690665</v>
       </c>
       <c r="R100" t="n">
-        <v>7096919</v>
+        <v>7096920</v>
       </c>
       <c r="S100" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10867,18 +10862,19 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10889,10 +10885,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126927128</v>
+        <v>126936880</v>
       </c>
       <c r="B101" t="n">
-        <v>80117</v>
+        <v>78777</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10900,37 +10896,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>690517</v>
+        <v>690619</v>
       </c>
       <c r="R101" t="n">
-        <v>7097014</v>
+        <v>7097003</v>
       </c>
       <c r="S101" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10974,44 +10970,48 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY101" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126927292</v>
+        <v>126927465</v>
       </c>
       <c r="B102" t="n">
-        <v>98443</v>
+        <v>79018</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11021,10 +11021,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>690530</v>
+        <v>690596</v>
       </c>
       <c r="R102" t="n">
-        <v>7097014</v>
+        <v>7097023</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -11083,48 +11083,48 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126927465</v>
+        <v>126931577</v>
       </c>
       <c r="B103" t="n">
-        <v>79014</v>
+        <v>80056</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6457</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>690596</v>
+        <v>690656</v>
       </c>
       <c r="R103" t="n">
-        <v>7097023</v>
+        <v>7096927</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11168,22 +11168,26 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY103" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126931577</v>
+        <v>126927178</v>
       </c>
       <c r="B104" t="n">
-        <v>80052</v>
+        <v>80150</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11191,37 +11195,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6457</v>
+        <v>6462</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>690656</v>
+        <v>690520</v>
       </c>
       <c r="R104" t="n">
-        <v>7096927</v>
+        <v>7097024</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11265,48 +11269,44 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY104" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126927178</v>
+        <v>126927184</v>
       </c>
       <c r="B105" t="n">
-        <v>80146</v>
+        <v>80121</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11378,32 +11378,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126927184</v>
+        <v>126927139</v>
       </c>
       <c r="B106" t="n">
-        <v>80117</v>
+        <v>80150</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11413,10 +11413,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>690520</v>
+        <v>690515</v>
       </c>
       <c r="R106" t="n">
-        <v>7097024</v>
+        <v>7097011</v>
       </c>
       <c r="S106" t="n">
         <v>15</v>
@@ -11475,48 +11475,48 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126927139</v>
+        <v>126931566</v>
       </c>
       <c r="B107" t="n">
-        <v>80146</v>
+        <v>78776</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>690515</v>
+        <v>690621</v>
       </c>
       <c r="R107" t="n">
-        <v>7097011</v>
+        <v>7096855</v>
       </c>
       <c r="S107" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11560,60 +11560,64 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY107" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126931566</v>
+        <v>126927292</v>
       </c>
       <c r="B108" t="n">
-        <v>78772</v>
+        <v>98447</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>690621</v>
+        <v>690530</v>
       </c>
       <c r="R108" t="n">
-        <v>7096855</v>
+        <v>7097014</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11657,19 +11661,15 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY108" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30467-2025 artfynd.xlsx
+++ b/artfynd/A 30467-2025 artfynd.xlsx
@@ -1514,45 +1514,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126909288</v>
+        <v>126917545</v>
       </c>
       <c r="B10" t="n">
-        <v>78777</v>
+        <v>80025</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Rislidtjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>690438</v>
+        <v>690344</v>
       </c>
       <c r="R10" t="n">
-        <v>7097136</v>
+        <v>7097126</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,19 +1582,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1609,12 +1599,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1625,45 +1615,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126917545</v>
+        <v>126909288</v>
       </c>
       <c r="B11" t="n">
-        <v>80025</v>
+        <v>78777</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rislidtjärnarna, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>690344</v>
+        <v>690438</v>
       </c>
       <c r="R11" t="n">
-        <v>7097126</v>
+        <v>7097136</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,9 +1683,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1710,12 +1710,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -2598,48 +2598,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126927356</v>
+        <v>126936912</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>690516</v>
+        <v>690392</v>
       </c>
       <c r="R20" t="n">
-        <v>7096990</v>
+        <v>7097038</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2683,60 +2683,64 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126936912</v>
+        <v>126927356</v>
       </c>
       <c r="B21" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>690392</v>
+        <v>690516</v>
       </c>
       <c r="R21" t="n">
-        <v>7097038</v>
+        <v>7096990</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2780,19 +2784,15 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3091,7 +3091,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126927842</v>
+        <v>126937624</v>
       </c>
       <c r="B25" t="n">
         <v>79018</v>
@@ -3122,14 +3122,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>690605</v>
+        <v>690656</v>
       </c>
       <c r="R25" t="n">
-        <v>7096920</v>
+        <v>7096868</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3176,19 +3176,23 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126937624</v>
+        <v>126927842</v>
       </c>
       <c r="B26" t="n">
         <v>79018</v>
@@ -3219,14 +3223,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>690656</v>
+        <v>690605</v>
       </c>
       <c r="R26" t="n">
-        <v>7096868</v>
+        <v>7096920</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3273,77 +3277,57 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126936889</v>
+        <v>126931565</v>
       </c>
       <c r="B27" t="n">
-        <v>98447</v>
+        <v>78777</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>690595</v>
+        <v>690620</v>
       </c>
       <c r="R27" t="n">
-        <v>7096886</v>
+        <v>7096859</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3384,19 +3368,18 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3407,7 +3390,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126936890</v>
+        <v>126936889</v>
       </c>
       <c r="B28" t="n">
         <v>98447</v>
@@ -3437,7 +3420,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3445,7 +3428,11 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3454,10 +3441,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>690564</v>
+        <v>690595</v>
       </c>
       <c r="R28" t="n">
-        <v>7096907</v>
+        <v>7096886</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3521,7 +3508,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126936886</v>
+        <v>126936890</v>
       </c>
       <c r="B29" t="n">
         <v>98447</v>
@@ -3551,7 +3538,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3559,11 +3546,7 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
@@ -3572,10 +3555,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>690607</v>
+        <v>690564</v>
       </c>
       <c r="R29" t="n">
-        <v>7097014</v>
+        <v>7096907</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3639,45 +3622,61 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126931565</v>
+        <v>126936886</v>
       </c>
       <c r="B30" t="n">
-        <v>78777</v>
+        <v>98447</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>690620</v>
+        <v>690607</v>
       </c>
       <c r="R30" t="n">
-        <v>7096859</v>
+        <v>7097014</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3718,18 +3717,19 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3837,48 +3837,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126937621</v>
+        <v>126936897</v>
       </c>
       <c r="B32" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>690635</v>
+        <v>690544</v>
       </c>
       <c r="R32" t="n">
-        <v>7096944</v>
+        <v>7096906</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3908,11 +3908,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ca 40 bladrosetter</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3927,12 +3922,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3943,7 +3938,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126936883</v>
+        <v>126937621</v>
       </c>
       <c r="B33" t="n">
         <v>98447</v>
@@ -3971,36 +3966,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>690668</v>
+        <v>690635</v>
       </c>
       <c r="R33" t="n">
-        <v>7096918</v>
+        <v>7096944</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4032,25 +4011,29 @@
           <t>2025-07-26</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ca 40 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4061,45 +4044,61 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126936897</v>
+        <v>126936883</v>
       </c>
       <c r="B34" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>690544</v>
+        <v>690668</v>
       </c>
       <c r="R34" t="n">
-        <v>7096906</v>
+        <v>7096918</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4140,6 +4139,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -5424,10 +5424,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126928173</v>
+        <v>126936877</v>
       </c>
       <c r="B47" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5435,37 +5435,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>690547</v>
+        <v>690378</v>
       </c>
       <c r="R47" t="n">
-        <v>7096876</v>
+        <v>7096984</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5509,22 +5509,26 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126936877</v>
+        <v>126936911</v>
       </c>
       <c r="B48" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5532,21 +5536,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5556,10 +5560,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>690378</v>
+        <v>690481</v>
       </c>
       <c r="R48" t="n">
-        <v>7096984</v>
+        <v>7097028</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5622,7 +5626,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126936911</v>
+        <v>126928173</v>
       </c>
       <c r="B49" t="n">
         <v>79018</v>
@@ -5653,17 +5657,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>690481</v>
+        <v>690547</v>
       </c>
       <c r="R49" t="n">
-        <v>7097028</v>
+        <v>7096876</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5707,23 +5711,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126937623</v>
+        <v>126937632</v>
       </c>
       <c r="B50" t="n">
         <v>79018</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>690707</v>
+        <v>690454</v>
       </c>
       <c r="R50" t="n">
-        <v>7096903</v>
+        <v>7097036</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5824,7 +5824,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126937632</v>
+        <v>126937623</v>
       </c>
       <c r="B51" t="n">
         <v>79018</v>
@@ -5859,10 +5859,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>690454</v>
+        <v>690707</v>
       </c>
       <c r="R51" t="n">
-        <v>7097036</v>
+        <v>7096903</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6039,60 +6039,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126931571</v>
+        <v>126927000</v>
       </c>
       <c r="B53" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>690644</v>
+        <v>690487</v>
       </c>
       <c r="R53" t="n">
-        <v>7096948</v>
+        <v>7097101</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6130,33 +6118,28 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126927086</v>
+        <v>126928117</v>
       </c>
       <c r="B54" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6164,34 +6147,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>690545</v>
+        <v>690540</v>
       </c>
       <c r="R54" t="n">
-        <v>7097033</v>
+        <v>7096888</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6250,10 +6233,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126927000</v>
+        <v>126927086</v>
       </c>
       <c r="B55" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6261,21 +6244,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6285,10 +6268,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>690487</v>
+        <v>690545</v>
       </c>
       <c r="R55" t="n">
-        <v>7097101</v>
+        <v>7097033</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6448,48 +6431,60 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126928117</v>
+        <v>126931571</v>
       </c>
       <c r="B57" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>690540</v>
+        <v>690644</v>
       </c>
       <c r="R57" t="n">
-        <v>7096888</v>
+        <v>7096948</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6527,21 +6522,26 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6642,7 +6642,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126927108</v>
+        <v>126926566</v>
       </c>
       <c r="B59" t="n">
         <v>79018</v>
@@ -6677,10 +6677,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>690542</v>
+        <v>690362</v>
       </c>
       <c r="R59" t="n">
-        <v>7097030</v>
+        <v>7097210</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6739,7 +6739,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126927426</v>
+        <v>126937630</v>
       </c>
       <c r="B60" t="n">
         <v>79018</v>
@@ -6770,14 +6770,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>690560</v>
+        <v>690480</v>
       </c>
       <c r="R60" t="n">
-        <v>7097019</v>
+        <v>7096994</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6824,19 +6824,23 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126937630</v>
+        <v>126927108</v>
       </c>
       <c r="B61" t="n">
         <v>79018</v>
@@ -6867,14 +6871,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>690480</v>
+        <v>690542</v>
       </c>
       <c r="R61" t="n">
-        <v>7096994</v>
+        <v>7097030</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6921,26 +6925,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126936881</v>
+        <v>126927426</v>
       </c>
       <c r="B62" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6948,37 +6948,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>690617</v>
+        <v>690560</v>
       </c>
       <c r="R62" t="n">
-        <v>7096851</v>
+        <v>7097019</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7022,26 +7022,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126926566</v>
+        <v>126936881</v>
       </c>
       <c r="B63" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7049,37 +7045,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>690362</v>
+        <v>690617</v>
       </c>
       <c r="R63" t="n">
-        <v>7097210</v>
+        <v>7096851</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7123,15 +7119,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7232,32 +7232,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126927409</v>
+        <v>126926457</v>
       </c>
       <c r="B65" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7267,10 +7267,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>690545</v>
+        <v>690374</v>
       </c>
       <c r="R65" t="n">
-        <v>7097003</v>
+        <v>7097232</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7329,45 +7329,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126936893</v>
+        <v>126931576</v>
       </c>
       <c r="B66" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>690658</v>
+        <v>690565</v>
       </c>
       <c r="R66" t="n">
-        <v>7096938</v>
+        <v>7096992</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7414,12 +7414,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7430,32 +7430,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126926457</v>
+        <v>126927409</v>
       </c>
       <c r="B67" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7465,10 +7465,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>690374</v>
+        <v>690545</v>
       </c>
       <c r="R67" t="n">
-        <v>7097232</v>
+        <v>7097003</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7527,45 +7527,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126931576</v>
+        <v>126936893</v>
       </c>
       <c r="B68" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>690565</v>
+        <v>690658</v>
       </c>
       <c r="R68" t="n">
-        <v>7096992</v>
+        <v>7096938</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7612,12 +7612,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7923,7 +7923,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126936896</v>
+        <v>126927191</v>
       </c>
       <c r="B72" t="n">
         <v>79018</v>
@@ -7954,17 +7954,17 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>690482</v>
+        <v>690524</v>
       </c>
       <c r="R72" t="n">
-        <v>7096931</v>
+        <v>7097009</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8008,70 +8008,54 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126936891</v>
+        <v>126936896</v>
       </c>
       <c r="B73" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>690644</v>
+        <v>690482</v>
       </c>
       <c r="R73" t="n">
         <v>7096931</v>
@@ -8115,7 +8099,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8138,45 +8121,57 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126936879</v>
+        <v>126936891</v>
       </c>
       <c r="B74" t="n">
-        <v>97331</v>
+        <v>98447</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>690490</v>
+        <v>690644</v>
       </c>
       <c r="R74" t="n">
-        <v>7096937</v>
+        <v>7096931</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8217,6 +8212,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8239,48 +8235,48 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126927191</v>
+        <v>126936879</v>
       </c>
       <c r="B75" t="n">
-        <v>79018</v>
+        <v>97331</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>690524</v>
+        <v>690490</v>
       </c>
       <c r="R75" t="n">
-        <v>7097009</v>
+        <v>7096937</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8324,15 +8320,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8433,7 +8433,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126927024</v>
+        <v>126937629</v>
       </c>
       <c r="B77" t="n">
         <v>79018</v>
@@ -8464,14 +8464,14 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>690503</v>
+        <v>690504</v>
       </c>
       <c r="R77" t="n">
-        <v>7097060</v>
+        <v>7096980</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8518,19 +8518,23 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126927395</v>
+        <v>126927024</v>
       </c>
       <c r="B78" t="n">
         <v>79018</v>
@@ -8565,10 +8569,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>690542</v>
+        <v>690503</v>
       </c>
       <c r="R78" t="n">
-        <v>7096989</v>
+        <v>7097060</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8627,7 +8631,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126937629</v>
+        <v>126927395</v>
       </c>
       <c r="B79" t="n">
         <v>79018</v>
@@ -8658,14 +8662,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>690504</v>
+        <v>690542</v>
       </c>
       <c r="R79" t="n">
-        <v>7096980</v>
+        <v>7096989</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8712,26 +8716,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126936909</v>
+        <v>126931564</v>
       </c>
       <c r="B80" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8739,34 +8739,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>690590</v>
+        <v>690624</v>
       </c>
       <c r="R80" t="n">
-        <v>7096893</v>
+        <v>7096879</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8813,12 +8813,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -9027,10 +9027,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126931564</v>
+        <v>126936909</v>
       </c>
       <c r="B83" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9038,34 +9038,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>690624</v>
+        <v>690590</v>
       </c>
       <c r="R83" t="n">
-        <v>7096879</v>
+        <v>7096893</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9112,12 +9112,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9322,7 +9322,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126927737</v>
+        <v>126936899</v>
       </c>
       <c r="B86" t="n">
         <v>79018</v>
@@ -9353,17 +9353,17 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>690623</v>
+        <v>690607</v>
       </c>
       <c r="R86" t="n">
-        <v>7096931</v>
+        <v>7097019</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9407,19 +9407,23 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126936899</v>
+        <v>126927737</v>
       </c>
       <c r="B87" t="n">
         <v>79018</v>
@@ -9450,17 +9454,17 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>690607</v>
+        <v>690623</v>
       </c>
       <c r="R87" t="n">
-        <v>7097019</v>
+        <v>7096931</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9504,19 +9508,15 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9621,48 +9621,60 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126937616</v>
+        <v>126936892</v>
       </c>
       <c r="B89" t="n">
-        <v>79636</v>
+        <v>98447</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>690516</v>
+        <v>690619</v>
       </c>
       <c r="R89" t="n">
-        <v>7096946</v>
+        <v>7096955</v>
       </c>
       <c r="S89" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9700,18 +9712,19 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9722,48 +9735,48 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126926697</v>
+        <v>126936913</v>
       </c>
       <c r="B90" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>690438</v>
+        <v>690466</v>
       </c>
       <c r="R90" t="n">
-        <v>7097148</v>
+        <v>7096945</v>
       </c>
       <c r="S90" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9807,19 +9820,23 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126936895</v>
+        <v>126926697</v>
       </c>
       <c r="B91" t="n">
         <v>79018</v>
@@ -9850,17 +9867,17 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>690445</v>
+        <v>690438</v>
       </c>
       <c r="R91" t="n">
-        <v>7096945</v>
+        <v>7097148</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9904,64 +9921,60 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126936913</v>
+        <v>126937616</v>
       </c>
       <c r="B92" t="n">
-        <v>92620</v>
+        <v>79636</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>690466</v>
+        <v>690516</v>
       </c>
       <c r="R92" t="n">
-        <v>7096945</v>
+        <v>7096946</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10005,12 +10018,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10021,57 +10034,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126936892</v>
+        <v>126936895</v>
       </c>
       <c r="B93" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>690619</v>
+        <v>690445</v>
       </c>
       <c r="R93" t="n">
-        <v>7096955</v>
+        <v>7096945</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10112,7 +10113,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10135,45 +10135,61 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126936898</v>
+        <v>126936884</v>
       </c>
       <c r="B94" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>690576</v>
+        <v>690609</v>
       </c>
       <c r="R94" t="n">
-        <v>7096919</v>
+        <v>7096953</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10214,6 +10230,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10236,45 +10253,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126927128</v>
+        <v>126937619</v>
       </c>
       <c r="B95" t="n">
-        <v>80121</v>
+        <v>98447</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>690517</v>
+        <v>690621</v>
       </c>
       <c r="R95" t="n">
-        <v>7097014</v>
+        <v>7096899</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -10321,60 +10338,80 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126937627</v>
+        <v>126931569</v>
       </c>
       <c r="B96" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>690522</v>
+        <v>690550</v>
       </c>
       <c r="R96" t="n">
-        <v>7096919</v>
+        <v>7097011</v>
       </c>
       <c r="S96" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10412,18 +10449,19 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10434,7 +10472,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126936884</v>
+        <v>126931572</v>
       </c>
       <c r="B97" t="n">
         <v>98447</v>
@@ -10464,31 +10502,27 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>690609</v>
+        <v>690665</v>
       </c>
       <c r="R97" t="n">
-        <v>7096953</v>
+        <v>7096920</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10536,12 +10570,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10552,48 +10586,48 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126937619</v>
+        <v>126936880</v>
       </c>
       <c r="B98" t="n">
-        <v>98447</v>
+        <v>78777</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>690621</v>
+        <v>690619</v>
       </c>
       <c r="R98" t="n">
-        <v>7096899</v>
+        <v>7097003</v>
       </c>
       <c r="S98" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10637,12 +10671,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10653,61 +10687,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126931569</v>
+        <v>126936898</v>
       </c>
       <c r="B99" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>690550</v>
+        <v>690576</v>
       </c>
       <c r="R99" t="n">
-        <v>7097011</v>
+        <v>7096919</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10748,19 +10766,18 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10771,60 +10788,48 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126931572</v>
+        <v>126927128</v>
       </c>
       <c r="B100" t="n">
-        <v>98447</v>
+        <v>80121</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>690665</v>
+        <v>690517</v>
       </c>
       <c r="R100" t="n">
-        <v>7096920</v>
+        <v>7097014</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10862,33 +10867,28 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY100" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126936880</v>
+        <v>126937627</v>
       </c>
       <c r="B101" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10896,37 +10896,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>690619</v>
+        <v>690522</v>
       </c>
       <c r="R101" t="n">
-        <v>7097003</v>
+        <v>7096919</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10970,12 +10970,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -10986,32 +10986,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126927465</v>
+        <v>126927292</v>
       </c>
       <c r="B102" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11021,10 +11021,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>690596</v>
+        <v>690530</v>
       </c>
       <c r="R102" t="n">
-        <v>7097023</v>
+        <v>7097014</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -11083,48 +11083,48 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126931577</v>
+        <v>126927465</v>
       </c>
       <c r="B103" t="n">
-        <v>80056</v>
+        <v>79018</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>690656</v>
+        <v>690596</v>
       </c>
       <c r="R103" t="n">
-        <v>7096927</v>
+        <v>7097023</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11168,26 +11168,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY103" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126927178</v>
+        <v>126931577</v>
       </c>
       <c r="B104" t="n">
-        <v>80150</v>
+        <v>80056</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11195,37 +11191,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6462</v>
+        <v>6457</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>690520</v>
+        <v>690656</v>
       </c>
       <c r="R104" t="n">
-        <v>7097024</v>
+        <v>7096927</v>
       </c>
       <c r="S104" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11269,44 +11265,48 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY104" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126927184</v>
+        <v>126927178</v>
       </c>
       <c r="B105" t="n">
-        <v>80121</v>
+        <v>80150</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11378,32 +11378,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126927139</v>
+        <v>126927184</v>
       </c>
       <c r="B106" t="n">
-        <v>80150</v>
+        <v>80121</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11413,10 +11413,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>690515</v>
+        <v>690520</v>
       </c>
       <c r="R106" t="n">
-        <v>7097011</v>
+        <v>7097024</v>
       </c>
       <c r="S106" t="n">
         <v>15</v>
@@ -11475,48 +11475,48 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126931566</v>
+        <v>126927139</v>
       </c>
       <c r="B107" t="n">
-        <v>78776</v>
+        <v>80150</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>690621</v>
+        <v>690515</v>
       </c>
       <c r="R107" t="n">
-        <v>7096855</v>
+        <v>7097011</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11560,64 +11560,60 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY107" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126927292</v>
+        <v>126931566</v>
       </c>
       <c r="B108" t="n">
-        <v>98447</v>
+        <v>78776</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>690530</v>
+        <v>690621</v>
       </c>
       <c r="R108" t="n">
-        <v>7097014</v>
+        <v>7096855</v>
       </c>
       <c r="S108" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11661,15 +11657,19 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY108" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30467-2025 artfynd.xlsx
+++ b/artfynd/A 30467-2025 artfynd.xlsx
@@ -1409,49 +1409,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126919966</v>
+        <v>126909288</v>
       </c>
       <c r="B9" t="n">
-        <v>91341</v>
+        <v>78777</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1205</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rislidstjärnarna, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>690349</v>
+        <v>690438</v>
       </c>
       <c r="R9" t="n">
-        <v>7097128</v>
+        <v>7097136</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,9 +1477,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1498,12 +1504,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
+          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1514,10 +1520,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126917545</v>
+        <v>126919966</v>
       </c>
       <c r="B10" t="n">
-        <v>80025</v>
+        <v>91341</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1525,34 +1531,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>1205</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rislidtjärnarna, Ång</t>
+          <t>Rislidstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>690344</v>
+        <v>690349</v>
       </c>
       <c r="R10" t="n">
-        <v>7097126</v>
+        <v>7097128</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1599,12 +1609,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1615,45 +1625,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126909288</v>
+        <v>126917545</v>
       </c>
       <c r="B11" t="n">
-        <v>78777</v>
+        <v>80025</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Rislidtjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>690438</v>
+        <v>690344</v>
       </c>
       <c r="R11" t="n">
-        <v>7097136</v>
+        <v>7097126</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1683,19 +1693,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1710,12 +1710,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -2598,45 +2598,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126936912</v>
+        <v>126931573</v>
       </c>
       <c r="B20" t="n">
-        <v>92620</v>
+        <v>98447</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>690392</v>
+        <v>690578</v>
       </c>
       <c r="R20" t="n">
-        <v>7097038</v>
+        <v>7096991</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2683,12 +2683,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2699,10 +2699,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126927356</v>
+        <v>126926856</v>
       </c>
       <c r="B21" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2710,37 +2710,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>N Johannesbomyran, N Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>690516</v>
+        <v>690563</v>
       </c>
       <c r="R21" t="n">
-        <v>7096990</v>
+        <v>7096856</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2784,60 +2784,60 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126931573</v>
+        <v>126927356</v>
       </c>
       <c r="B22" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>690578</v>
+        <v>690516</v>
       </c>
       <c r="R22" t="n">
-        <v>7096991</v>
+        <v>7096990</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2881,61 +2881,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126926856</v>
+        <v>126936912</v>
       </c>
       <c r="B23" t="n">
-        <v>78777</v>
+        <v>92620</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>N Johannesbomyran, N Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>690563</v>
+        <v>690392</v>
       </c>
       <c r="R23" t="n">
-        <v>7096856</v>
+        <v>7097038</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2982,60 +2978,80 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126927661</v>
+        <v>126936889</v>
       </c>
       <c r="B24" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>690574</v>
+        <v>690595</v>
       </c>
       <c r="R24" t="n">
-        <v>7096978</v>
+        <v>7096886</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3073,66 +3089,83 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126937624</v>
+        <v>126936890</v>
       </c>
       <c r="B25" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>690656</v>
+        <v>690564</v>
       </c>
       <c r="R25" t="n">
-        <v>7096868</v>
+        <v>7096907</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3170,18 +3203,19 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3192,48 +3226,64 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126927842</v>
+        <v>126936886</v>
       </c>
       <c r="B26" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>690605</v>
+        <v>690607</v>
       </c>
       <c r="R26" t="n">
-        <v>7096920</v>
+        <v>7097014</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3271,28 +3321,33 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126931565</v>
+        <v>126927661</v>
       </c>
       <c r="B27" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3300,37 +3355,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>690620</v>
+        <v>690574</v>
       </c>
       <c r="R27" t="n">
-        <v>7096859</v>
+        <v>7096978</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3374,80 +3429,60 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126936889</v>
+        <v>126937624</v>
       </c>
       <c r="B28" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>690595</v>
+        <v>690656</v>
       </c>
       <c r="R28" t="n">
-        <v>7096886</v>
+        <v>7096868</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3485,19 +3520,18 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3508,60 +3542,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126936890</v>
+        <v>126927842</v>
       </c>
       <c r="B29" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>690564</v>
+        <v>690605</v>
       </c>
       <c r="R29" t="n">
-        <v>7096907</v>
+        <v>7096920</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3599,84 +3621,63 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126936886</v>
+        <v>126931565</v>
       </c>
       <c r="B30" t="n">
-        <v>98447</v>
+        <v>78777</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>690607</v>
+        <v>690620</v>
       </c>
       <c r="R30" t="n">
-        <v>7097014</v>
+        <v>7096859</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3717,19 +3718,18 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -5112,60 +5112,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126931570</v>
+        <v>126926859</v>
       </c>
       <c r="B44" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>690658</v>
+        <v>690483</v>
       </c>
       <c r="R44" t="n">
-        <v>7096895</v>
+        <v>7097114</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5203,68 +5191,75 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126936882</v>
+        <v>126931570</v>
       </c>
       <c r="B45" t="n">
-        <v>78777</v>
+        <v>98447</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>690560</v>
+        <v>690658</v>
       </c>
       <c r="R45" t="n">
-        <v>7096959</v>
+        <v>7096895</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5305,18 +5300,19 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5327,10 +5323,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126926859</v>
+        <v>126936882</v>
       </c>
       <c r="B46" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5338,37 +5334,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>690483</v>
+        <v>690560</v>
       </c>
       <c r="R46" t="n">
-        <v>7097114</v>
+        <v>7096959</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5412,15 +5408,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -10135,64 +10135,48 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126936884</v>
+        <v>126937627</v>
       </c>
       <c r="B94" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>690609</v>
+        <v>690522</v>
       </c>
       <c r="R94" t="n">
-        <v>7096953</v>
+        <v>7096919</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10230,19 +10214,18 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10253,48 +10236,48 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126937619</v>
+        <v>126936898</v>
       </c>
       <c r="B95" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>690621</v>
+        <v>690576</v>
       </c>
       <c r="R95" t="n">
-        <v>7096899</v>
+        <v>7096919</v>
       </c>
       <c r="S95" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10338,12 +10321,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10354,64 +10337,48 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126931569</v>
+        <v>126927128</v>
       </c>
       <c r="B96" t="n">
-        <v>98447</v>
+        <v>80121</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>690550</v>
+        <v>690517</v>
       </c>
       <c r="R96" t="n">
-        <v>7097011</v>
+        <v>7097014</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10449,30 +10416,25 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126931572</v>
+        <v>126936884</v>
       </c>
       <c r="B97" t="n">
         <v>98447</v>
@@ -10502,27 +10464,31 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>690665</v>
+        <v>690609</v>
       </c>
       <c r="R97" t="n">
-        <v>7096920</v>
+        <v>7096953</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10570,12 +10536,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10586,48 +10552,48 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126936880</v>
+        <v>126937619</v>
       </c>
       <c r="B98" t="n">
-        <v>78777</v>
+        <v>98447</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>690619</v>
+        <v>690621</v>
       </c>
       <c r="R98" t="n">
-        <v>7097003</v>
+        <v>7096899</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10671,12 +10637,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10687,45 +10653,61 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126936898</v>
+        <v>126931569</v>
       </c>
       <c r="B99" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>690576</v>
+        <v>690550</v>
       </c>
       <c r="R99" t="n">
-        <v>7096919</v>
+        <v>7097011</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10766,18 +10748,19 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10788,48 +10771,60 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126927128</v>
+        <v>126931572</v>
       </c>
       <c r="B100" t="n">
-        <v>80121</v>
+        <v>98447</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>690517</v>
+        <v>690665</v>
       </c>
       <c r="R100" t="n">
-        <v>7097014</v>
+        <v>7096920</v>
       </c>
       <c r="S100" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10867,28 +10862,33 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY100" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126937627</v>
+        <v>126936880</v>
       </c>
       <c r="B101" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10896,37 +10896,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>690522</v>
+        <v>690619</v>
       </c>
       <c r="R101" t="n">
-        <v>7096919</v>
+        <v>7097003</v>
       </c>
       <c r="S101" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10970,12 +10970,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">

--- a/artfynd/A 30467-2025 artfynd.xlsx
+++ b/artfynd/A 30467-2025 artfynd.xlsx
@@ -1409,45 +1409,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126909288</v>
+        <v>126919966</v>
       </c>
       <c r="B9" t="n">
-        <v>78777</v>
+        <v>91341</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>1205</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Rislidstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>690438</v>
+        <v>690349</v>
       </c>
       <c r="R9" t="n">
-        <v>7097136</v>
+        <v>7097128</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1477,19 +1481,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1504,12 +1498,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
+          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1520,10 +1514,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126919966</v>
+        <v>126917545</v>
       </c>
       <c r="B10" t="n">
-        <v>91341</v>
+        <v>80025</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1531,38 +1525,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1205</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rislidstjärnarna, Ång</t>
+          <t>Rislidtjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>690349</v>
+        <v>690344</v>
       </c>
       <c r="R10" t="n">
-        <v>7097128</v>
+        <v>7097126</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,12 +1599,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1625,45 +1615,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126917545</v>
+        <v>126909288</v>
       </c>
       <c r="B11" t="n">
-        <v>80025</v>
+        <v>78777</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rislidtjärnarna, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>690344</v>
+        <v>690438</v>
       </c>
       <c r="R11" t="n">
-        <v>7097126</v>
+        <v>7097136</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,9 +1683,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1710,12 +1710,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -2598,45 +2598,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126931573</v>
+        <v>126936912</v>
       </c>
       <c r="B20" t="n">
-        <v>98447</v>
+        <v>92620</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>690578</v>
+        <v>690392</v>
       </c>
       <c r="R20" t="n">
-        <v>7096991</v>
+        <v>7097038</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2683,12 +2683,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2699,10 +2699,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126926856</v>
+        <v>126927356</v>
       </c>
       <c r="B21" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2710,37 +2710,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>N Johannesbomyran, N Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>690563</v>
+        <v>690516</v>
       </c>
       <c r="R21" t="n">
-        <v>7096856</v>
+        <v>7096990</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2784,60 +2784,60 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126927356</v>
+        <v>126931573</v>
       </c>
       <c r="B22" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>690516</v>
+        <v>690578</v>
       </c>
       <c r="R22" t="n">
-        <v>7096990</v>
+        <v>7096991</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2881,57 +2881,61 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126936912</v>
+        <v>126926856</v>
       </c>
       <c r="B23" t="n">
-        <v>92620</v>
+        <v>78777</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>N Johannesbomyran, N Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>690392</v>
+        <v>690563</v>
       </c>
       <c r="R23" t="n">
-        <v>7097038</v>
+        <v>7096856</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2978,19 +2982,15 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -8728,48 +8728,48 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126931564</v>
+        <v>126927343</v>
       </c>
       <c r="B80" t="n">
-        <v>79050</v>
+        <v>98447</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>690624</v>
+        <v>690544</v>
       </c>
       <c r="R80" t="n">
-        <v>7096879</v>
+        <v>7097007</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8813,26 +8813,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126937622</v>
+        <v>126931564</v>
       </c>
       <c r="B81" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8840,37 +8836,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>690620</v>
+        <v>690624</v>
       </c>
       <c r="R81" t="n">
-        <v>7096858</v>
+        <v>7096879</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8914,12 +8910,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -8930,7 +8926,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126927691</v>
+        <v>126937622</v>
       </c>
       <c r="B82" t="n">
         <v>79018</v>
@@ -8961,14 +8957,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>690577</v>
+        <v>690620</v>
       </c>
       <c r="R82" t="n">
-        <v>7096975</v>
+        <v>7096858</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9015,19 +9011,23 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126936909</v>
+        <v>126927691</v>
       </c>
       <c r="B83" t="n">
         <v>79018</v>
@@ -9058,17 +9058,17 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>690590</v>
+        <v>690577</v>
       </c>
       <c r="R83" t="n">
-        <v>7096893</v>
+        <v>7096975</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9112,64 +9112,60 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126927343</v>
+        <v>126936909</v>
       </c>
       <c r="B84" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>690544</v>
+        <v>690590</v>
       </c>
       <c r="R84" t="n">
-        <v>7097007</v>
+        <v>7096893</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9213,15 +9209,19 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">

--- a/artfynd/A 30467-2025 artfynd.xlsx
+++ b/artfynd/A 30467-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>126909580</v>
       </c>
       <c r="B3" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1005,32 +1005,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126917563</v>
+        <v>126917550</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>80157</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>690509</v>
+        <v>690515</v>
       </c>
       <c r="R5" t="n">
-        <v>7097052</v>
+        <v>7097014</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,32 +1106,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126917550</v>
+        <v>126917563</v>
       </c>
       <c r="B6" t="n">
-        <v>80157</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>690515</v>
+        <v>690509</v>
       </c>
       <c r="R6" t="n">
-        <v>7097014</v>
+        <v>7097052</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1210,7 @@
         <v>126919976</v>
       </c>
       <c r="B7" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1726,10 +1726,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126909413</v>
+        <v>126909538</v>
       </c>
       <c r="B12" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>690516</v>
+        <v>690484</v>
       </c>
       <c r="R12" t="n">
-        <v>7097033</v>
+        <v>7097073</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126909538</v>
+        <v>126909413</v>
       </c>
       <c r="B13" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>690484</v>
+        <v>690516</v>
       </c>
       <c r="R13" t="n">
-        <v>7097073</v>
+        <v>7097033</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,7 +1959,7 @@
         <v>126918516</v>
       </c>
       <c r="B14" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2699,48 +2699,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126927356</v>
+        <v>126931573</v>
       </c>
       <c r="B21" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>690516</v>
+        <v>690578</v>
       </c>
       <c r="R21" t="n">
-        <v>7096990</v>
+        <v>7096991</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2784,57 +2784,61 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126931573</v>
+        <v>126926856</v>
       </c>
       <c r="B22" t="n">
-        <v>98447</v>
+        <v>78777</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>N Johannesbomyran, N Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>690578</v>
+        <v>690563</v>
       </c>
       <c r="R22" t="n">
-        <v>7096991</v>
+        <v>7096856</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2881,26 +2885,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126926856</v>
+        <v>126927356</v>
       </c>
       <c r="B23" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2908,37 +2908,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>N Johannesbomyran, N Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>690563</v>
+        <v>690516</v>
       </c>
       <c r="R23" t="n">
-        <v>7096856</v>
+        <v>7096990</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2982,76 +2982,60 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126936889</v>
+        <v>126937624</v>
       </c>
       <c r="B24" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>690595</v>
+        <v>690656</v>
       </c>
       <c r="R24" t="n">
-        <v>7096886</v>
+        <v>7096868</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3089,19 +3073,18 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3112,60 +3095,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126936890</v>
+        <v>126927842</v>
       </c>
       <c r="B25" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>690564</v>
+        <v>690605</v>
       </c>
       <c r="R25" t="n">
-        <v>7096907</v>
+        <v>7096920</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3203,87 +3174,66 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126936886</v>
+        <v>126927661</v>
       </c>
       <c r="B26" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>690607</v>
+        <v>690574</v>
       </c>
       <c r="R26" t="n">
-        <v>7097014</v>
+        <v>7096978</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3321,71 +3271,82 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126927661</v>
+        <v>126936886</v>
       </c>
       <c r="B27" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>690574</v>
+        <v>690607</v>
       </c>
       <c r="R27" t="n">
-        <v>7096978</v>
+        <v>7097014</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3423,66 +3384,87 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126937624</v>
+        <v>126936889</v>
       </c>
       <c r="B28" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>690656</v>
+        <v>690595</v>
       </c>
       <c r="R28" t="n">
-        <v>7096868</v>
+        <v>7096886</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3520,18 +3502,19 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3542,10 +3525,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126927842</v>
+        <v>126931565</v>
       </c>
       <c r="B29" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3553,37 +3536,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>690605</v>
+        <v>690620</v>
       </c>
       <c r="R29" t="n">
-        <v>7096920</v>
+        <v>7096859</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3627,57 +3610,73 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126931565</v>
+        <v>126936890</v>
       </c>
       <c r="B30" t="n">
-        <v>78777</v>
+        <v>98448</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>690620</v>
+        <v>690564</v>
       </c>
       <c r="R30" t="n">
-        <v>7096859</v>
+        <v>7096907</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3718,18 +3717,19 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3938,10 +3938,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126937621</v>
+        <v>126936883</v>
       </c>
       <c r="B33" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3966,20 +3966,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>690635</v>
+        <v>690668</v>
       </c>
       <c r="R33" t="n">
-        <v>7096944</v>
+        <v>7096918</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4011,29 +4027,25 @@
           <t>2025-07-26</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ca 40 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4044,10 +4056,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126936883</v>
+        <v>126937621</v>
       </c>
       <c r="B34" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4072,36 +4084,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>690668</v>
+        <v>690635</v>
       </c>
       <c r="R34" t="n">
-        <v>7096918</v>
+        <v>7096944</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4133,25 +4129,29 @@
           <t>2025-07-26</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ca 40 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4165,7 +4165,7 @@
         <v>126931567</v>
       </c>
       <c r="B35" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4276,10 +4276,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126936888</v>
+        <v>126937620</v>
       </c>
       <c r="B36" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4304,32 +4304,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>690639</v>
+        <v>690612</v>
       </c>
       <c r="R36" t="n">
-        <v>7096927</v>
+        <v>7096930</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4359,6 +4351,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Cirka 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4374,12 +4371,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4390,10 +4387,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126937620</v>
+        <v>126936888</v>
       </c>
       <c r="B37" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4418,24 +4415,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>690612</v>
+        <v>690639</v>
       </c>
       <c r="R37" t="n">
-        <v>7096930</v>
+        <v>7096927</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4465,11 +4470,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Cirka 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4485,12 +4485,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4803,7 +4803,7 @@
         <v>126936887</v>
       </c>
       <c r="B41" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>126936894</v>
       </c>
       <c r="B43" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>126931570</v>
       </c>
       <c r="B45" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5424,10 +5424,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126936877</v>
+        <v>126928173</v>
       </c>
       <c r="B47" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5435,37 +5435,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>690378</v>
+        <v>690547</v>
       </c>
       <c r="R47" t="n">
-        <v>7096984</v>
+        <v>7096876</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5509,23 +5509,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126936911</v>
+        <v>126937632</v>
       </c>
       <c r="B48" t="n">
         <v>79018</v>
@@ -5556,17 +5552,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>690481</v>
+        <v>690454</v>
       </c>
       <c r="R48" t="n">
-        <v>7097028</v>
+        <v>7097036</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5610,12 +5606,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5626,10 +5622,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126928173</v>
+        <v>126936877</v>
       </c>
       <c r="B49" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5637,37 +5633,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>690547</v>
+        <v>690378</v>
       </c>
       <c r="R49" t="n">
-        <v>7096876</v>
+        <v>7096984</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5711,19 +5707,23 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126937632</v>
+        <v>126936911</v>
       </c>
       <c r="B50" t="n">
         <v>79018</v>
@@ -5754,17 +5754,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>690454</v>
+        <v>690481</v>
       </c>
       <c r="R50" t="n">
-        <v>7097036</v>
+        <v>7097028</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5808,12 +5808,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5928,7 +5928,7 @@
         <v>126936885</v>
       </c>
       <c r="B52" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6039,10 +6039,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126927000</v>
+        <v>126927086</v>
       </c>
       <c r="B53" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6050,21 +6050,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6074,10 +6074,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>690487</v>
+        <v>690545</v>
       </c>
       <c r="R53" t="n">
-        <v>7097101</v>
+        <v>7097033</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6136,7 +6136,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126928117</v>
+        <v>126927000</v>
       </c>
       <c r="B54" t="n">
         <v>79018</v>
@@ -6167,14 +6167,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>690540</v>
+        <v>690487</v>
       </c>
       <c r="R54" t="n">
-        <v>7096888</v>
+        <v>7097101</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6233,10 +6233,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126927086</v>
+        <v>126936878</v>
       </c>
       <c r="B55" t="n">
-        <v>80121</v>
+        <v>79636</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6244,37 +6244,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>690545</v>
+        <v>690509</v>
       </c>
       <c r="R55" t="n">
-        <v>7097033</v>
+        <v>7096927</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6318,22 +6318,26 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126936878</v>
+        <v>126928117</v>
       </c>
       <c r="B56" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6341,37 +6345,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>690509</v>
+        <v>690540</v>
       </c>
       <c r="R56" t="n">
-        <v>7096927</v>
+        <v>7096888</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6415,26 +6419,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
         <v>126931571</v>
       </c>
       <c r="B57" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>126927409</v>
       </c>
       <c r="B67" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         <v>126936893</v>
       </c>
       <c r="B68" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8020,42 +8020,54 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126936896</v>
+        <v>126936891</v>
       </c>
       <c r="B73" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>690482</v>
+        <v>690644</v>
       </c>
       <c r="R73" t="n">
         <v>7096931</v>
@@ -8099,6 +8111,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8121,57 +8134,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126936891</v>
+        <v>126936879</v>
       </c>
       <c r="B74" t="n">
-        <v>98447</v>
+        <v>97331</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>690644</v>
+        <v>690490</v>
       </c>
       <c r="R74" t="n">
-        <v>7096931</v>
+        <v>7096937</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8212,7 +8213,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8235,32 +8235,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126936879</v>
+        <v>126936896</v>
       </c>
       <c r="B75" t="n">
-        <v>97331</v>
+        <v>79018</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8270,10 +8270,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>690490</v>
+        <v>690482</v>
       </c>
       <c r="R75" t="n">
-        <v>7096937</v>
+        <v>7096931</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8336,7 +8336,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126927943</v>
+        <v>126937629</v>
       </c>
       <c r="B76" t="n">
         <v>79018</v>
@@ -8367,14 +8367,14 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>690585</v>
+        <v>690504</v>
       </c>
       <c r="R76" t="n">
-        <v>7096888</v>
+        <v>7096980</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8421,19 +8421,23 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126937629</v>
+        <v>126927943</v>
       </c>
       <c r="B77" t="n">
         <v>79018</v>
@@ -8464,14 +8468,14 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>690504</v>
+        <v>690585</v>
       </c>
       <c r="R77" t="n">
-        <v>7096980</v>
+        <v>7096888</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8518,19 +8522,15 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8728,48 +8728,48 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126927343</v>
+        <v>126936909</v>
       </c>
       <c r="B80" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>690544</v>
+        <v>690590</v>
       </c>
       <c r="R80" t="n">
-        <v>7097007</v>
+        <v>7096893</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8813,22 +8813,26 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126931564</v>
+        <v>126927691</v>
       </c>
       <c r="B81" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8836,37 +8840,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>690624</v>
+        <v>690577</v>
       </c>
       <c r="R81" t="n">
-        <v>7096879</v>
+        <v>7096975</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8910,26 +8914,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126937622</v>
+        <v>126931564</v>
       </c>
       <c r="B82" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8937,37 +8937,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>690620</v>
+        <v>690624</v>
       </c>
       <c r="R82" t="n">
-        <v>7096858</v>
+        <v>7096879</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9011,12 +9011,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9027,7 +9027,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126927691</v>
+        <v>126937622</v>
       </c>
       <c r="B83" t="n">
         <v>79018</v>
@@ -9058,14 +9058,14 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>690577</v>
+        <v>690620</v>
       </c>
       <c r="R83" t="n">
-        <v>7096975</v>
+        <v>7096858</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9112,60 +9112,64 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126936909</v>
+        <v>126927343</v>
       </c>
       <c r="B84" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>690590</v>
+        <v>690544</v>
       </c>
       <c r="R84" t="n">
-        <v>7096893</v>
+        <v>7097007</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9209,19 +9213,15 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9423,7 +9423,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126927737</v>
+        <v>126936901</v>
       </c>
       <c r="B87" t="n">
         <v>79018</v>
@@ -9454,17 +9454,17 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
         <v>690623</v>
       </c>
       <c r="R87" t="n">
-        <v>7096931</v>
+        <v>7096862</v>
       </c>
       <c r="S87" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9508,19 +9508,23 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126936901</v>
+        <v>126927737</v>
       </c>
       <c r="B88" t="n">
         <v>79018</v>
@@ -9551,17 +9555,17 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
         <v>690623</v>
       </c>
       <c r="R88" t="n">
-        <v>7096862</v>
+        <v>7096931</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9605,73 +9609,57 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY88" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126936892</v>
+        <v>126936913</v>
       </c>
       <c r="B89" t="n">
-        <v>98447</v>
+        <v>92620</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>690619</v>
+        <v>690466</v>
       </c>
       <c r="R89" t="n">
-        <v>7096955</v>
+        <v>7096945</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9712,7 +9700,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9735,32 +9722,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126936913</v>
+        <v>126936895</v>
       </c>
       <c r="B90" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9770,7 +9757,7 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>690466</v>
+        <v>690445</v>
       </c>
       <c r="R90" t="n">
         <v>7096945</v>
@@ -9836,10 +9823,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126926697</v>
+        <v>126937616</v>
       </c>
       <c r="B91" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9847,34 +9834,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>690438</v>
+        <v>690516</v>
       </c>
       <c r="R91" t="n">
-        <v>7097148</v>
+        <v>7096946</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -9921,22 +9908,26 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126937616</v>
+        <v>126926697</v>
       </c>
       <c r="B92" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9944,34 +9935,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>690516</v>
+        <v>690438</v>
       </c>
       <c r="R92" t="n">
-        <v>7096946</v>
+        <v>7097148</v>
       </c>
       <c r="S92" t="n">
         <v>15</v>
@@ -10018,61 +10009,69 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126936895</v>
+        <v>126936892</v>
       </c>
       <c r="B93" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>690445</v>
+        <v>690619</v>
       </c>
       <c r="R93" t="n">
-        <v>7096945</v>
+        <v>7096955</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10113,6 +10112,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10135,7 +10135,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126937627</v>
+        <v>126936898</v>
       </c>
       <c r="B94" t="n">
         <v>79018</v>
@@ -10166,17 +10166,17 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>690522</v>
+        <v>690576</v>
       </c>
       <c r="R94" t="n">
         <v>7096919</v>
       </c>
       <c r="S94" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10220,12 +10220,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10236,45 +10236,57 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126936898</v>
+        <v>126931572</v>
       </c>
       <c r="B95" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>690576</v>
+        <v>690665</v>
       </c>
       <c r="R95" t="n">
-        <v>7096919</v>
+        <v>7096920</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10315,18 +10327,19 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10337,45 +10350,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126927128</v>
+        <v>126937619</v>
       </c>
       <c r="B96" t="n">
-        <v>80121</v>
+        <v>98448</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>690517</v>
+        <v>690621</v>
       </c>
       <c r="R96" t="n">
-        <v>7097014</v>
+        <v>7096899</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -10422,22 +10435,26 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126936884</v>
+        <v>126931569</v>
       </c>
       <c r="B97" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10464,12 +10481,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -10481,14 +10498,14 @@
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>690609</v>
+        <v>690550</v>
       </c>
       <c r="R97" t="n">
-        <v>7096953</v>
+        <v>7097011</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10536,12 +10553,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10552,10 +10569,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126937619</v>
+        <v>126936884</v>
       </c>
       <c r="B98" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10580,20 +10597,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>690621</v>
+        <v>690609</v>
       </c>
       <c r="R98" t="n">
-        <v>7096899</v>
+        <v>7096953</v>
       </c>
       <c r="S98" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10631,18 +10664,19 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10653,64 +10687,48 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126931569</v>
+        <v>126927128</v>
       </c>
       <c r="B99" t="n">
-        <v>98447</v>
+        <v>80121</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>690550</v>
+        <v>690517</v>
       </c>
       <c r="R99" t="n">
-        <v>7097011</v>
+        <v>7097014</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10748,80 +10766,63 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY99" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126931572</v>
+        <v>126936880</v>
       </c>
       <c r="B100" t="n">
-        <v>98447</v>
+        <v>78777</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>690665</v>
+        <v>690619</v>
       </c>
       <c r="R100" t="n">
-        <v>7096920</v>
+        <v>7097003</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10862,19 +10863,18 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10885,10 +10885,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126936880</v>
+        <v>126937627</v>
       </c>
       <c r="B101" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10896,37 +10896,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>690619</v>
+        <v>690522</v>
       </c>
       <c r="R101" t="n">
-        <v>7097003</v>
+        <v>7096919</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10970,12 +10970,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -10986,32 +10986,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126927292</v>
+        <v>126927178</v>
       </c>
       <c r="B102" t="n">
-        <v>98447</v>
+        <v>80150</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11021,10 +11021,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>690530</v>
+        <v>690520</v>
       </c>
       <c r="R102" t="n">
-        <v>7097014</v>
+        <v>7097024</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -11083,32 +11083,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126927465</v>
+        <v>126927139</v>
       </c>
       <c r="B103" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11118,10 +11118,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>690596</v>
+        <v>690515</v>
       </c>
       <c r="R103" t="n">
-        <v>7097023</v>
+        <v>7097011</v>
       </c>
       <c r="S103" t="n">
         <v>15</v>
@@ -11180,32 +11180,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126931577</v>
+        <v>126931566</v>
       </c>
       <c r="B104" t="n">
-        <v>80056</v>
+        <v>78776</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6457</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11215,10 +11215,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>690656</v>
+        <v>690621</v>
       </c>
       <c r="R104" t="n">
-        <v>7096927</v>
+        <v>7096855</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11281,32 +11281,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126927178</v>
+        <v>126927465</v>
       </c>
       <c r="B105" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11316,10 +11316,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>690520</v>
+        <v>690596</v>
       </c>
       <c r="R105" t="n">
-        <v>7097024</v>
+        <v>7097023</v>
       </c>
       <c r="S105" t="n">
         <v>15</v>
@@ -11378,48 +11378,48 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126927184</v>
+        <v>126931577</v>
       </c>
       <c r="B106" t="n">
-        <v>80121</v>
+        <v>80056</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6458</v>
+        <v>6457</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>690520</v>
+        <v>690656</v>
       </c>
       <c r="R106" t="n">
-        <v>7097024</v>
+        <v>7096927</v>
       </c>
       <c r="S106" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11463,44 +11463,48 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY106" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126927139</v>
+        <v>126927184</v>
       </c>
       <c r="B107" t="n">
-        <v>80150</v>
+        <v>80121</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11510,10 +11514,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>690515</v>
+        <v>690520</v>
       </c>
       <c r="R107" t="n">
-        <v>7097011</v>
+        <v>7097024</v>
       </c>
       <c r="S107" t="n">
         <v>15</v>
@@ -11572,48 +11576,48 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126931566</v>
+        <v>126927292</v>
       </c>
       <c r="B108" t="n">
-        <v>78776</v>
+        <v>98448</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>690621</v>
+        <v>690530</v>
       </c>
       <c r="R108" t="n">
-        <v>7096855</v>
+        <v>7097014</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11657,19 +11661,15 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY108" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30467-2025 artfynd.xlsx
+++ b/artfynd/A 30467-2025 artfynd.xlsx
@@ -675,45 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126919968</v>
+        <v>126909580</v>
       </c>
       <c r="B2" t="n">
-        <v>80025</v>
+        <v>98448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rislidstjärnarna, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>690349</v>
+        <v>690493</v>
       </c>
       <c r="R2" t="n">
-        <v>7097128</v>
+        <v>7097055</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,9 +747,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,12 +774,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
+          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -776,49 +790,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126909580</v>
+        <v>126919968</v>
       </c>
       <c r="B3" t="n">
-        <v>98448</v>
+        <v>80025</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Rislidstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>690493</v>
+        <v>690349</v>
       </c>
       <c r="R3" t="n">
-        <v>7097055</v>
+        <v>7097128</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,19 +858,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,12 +875,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
+          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1726,7 +1726,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126909538</v>
+        <v>126909413</v>
       </c>
       <c r="B12" t="n">
         <v>98448</v>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>690484</v>
+        <v>690516</v>
       </c>
       <c r="R12" t="n">
-        <v>7097073</v>
+        <v>7097033</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1841,7 +1841,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126909413</v>
+        <v>126909538</v>
       </c>
       <c r="B13" t="n">
         <v>98448</v>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>690516</v>
+        <v>690484</v>
       </c>
       <c r="R13" t="n">
-        <v>7097033</v>
+        <v>7097073</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2800,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126926856</v>
+        <v>126927356</v>
       </c>
       <c r="B22" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2811,37 +2811,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>N Johannesbomyran, N Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>690563</v>
+        <v>690516</v>
       </c>
       <c r="R22" t="n">
-        <v>7096856</v>
+        <v>7096990</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2885,22 +2885,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126927356</v>
+        <v>126926856</v>
       </c>
       <c r="B23" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2908,37 +2908,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>N Johannesbomyran, N Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>690516</v>
+        <v>690563</v>
       </c>
       <c r="R23" t="n">
-        <v>7096990</v>
+        <v>7096856</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2982,19 +2982,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126937624</v>
+        <v>126927661</v>
       </c>
       <c r="B24" t="n">
         <v>79018</v>
@@ -3025,14 +3025,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>690656</v>
+        <v>690574</v>
       </c>
       <c r="R24" t="n">
-        <v>7096868</v>
+        <v>7096978</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3079,64 +3079,76 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126927842</v>
+        <v>126936889</v>
       </c>
       <c r="B25" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>690605</v>
+        <v>690595</v>
       </c>
       <c r="R25" t="n">
-        <v>7096920</v>
+        <v>7096886</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3174,28 +3186,33 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126927661</v>
+        <v>126931565</v>
       </c>
       <c r="B26" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3203,37 +3220,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>690574</v>
+        <v>690620</v>
       </c>
       <c r="R26" t="n">
-        <v>7096978</v>
+        <v>7096859</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3277,76 +3294,64 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126936886</v>
+        <v>126937624</v>
       </c>
       <c r="B27" t="n">
-        <v>98448</v>
+        <v>79018</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>690607</v>
+        <v>690656</v>
       </c>
       <c r="R27" t="n">
-        <v>7097014</v>
+        <v>7096868</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3384,19 +3389,18 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3407,64 +3411,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126936889</v>
+        <v>126927842</v>
       </c>
       <c r="B28" t="n">
-        <v>98448</v>
+        <v>79018</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>690595</v>
+        <v>690605</v>
       </c>
       <c r="R28" t="n">
-        <v>7096886</v>
+        <v>7096920</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3502,68 +3490,79 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126931565</v>
+        <v>126936886</v>
       </c>
       <c r="B29" t="n">
-        <v>78777</v>
+        <v>98448</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>690620</v>
+        <v>690607</v>
       </c>
       <c r="R29" t="n">
-        <v>7096859</v>
+        <v>7097014</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3604,18 +3603,19 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3740,48 +3740,64 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126927550</v>
+        <v>126936883</v>
       </c>
       <c r="B31" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>690574</v>
+        <v>690668</v>
       </c>
       <c r="R31" t="n">
-        <v>7096994</v>
+        <v>7096918</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3819,66 +3835,71 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126936897</v>
+        <v>126937621</v>
       </c>
       <c r="B32" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>690544</v>
+        <v>690635</v>
       </c>
       <c r="R32" t="n">
-        <v>7096906</v>
+        <v>7096944</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3908,6 +3929,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ca 40 bladrosetter</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3922,12 +3948,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3938,64 +3964,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126936883</v>
+        <v>126927550</v>
       </c>
       <c r="B33" t="n">
-        <v>98448</v>
+        <v>79018</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>690668</v>
+        <v>690574</v>
       </c>
       <c r="R33" t="n">
-        <v>7096918</v>
+        <v>7096994</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4033,71 +4043,66 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126937621</v>
+        <v>126936897</v>
       </c>
       <c r="B34" t="n">
-        <v>98448</v>
+        <v>79018</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>690635</v>
+        <v>690544</v>
       </c>
       <c r="R34" t="n">
-        <v>7096944</v>
+        <v>7096906</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4127,11 +4132,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ca 40 bladrosetter</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4146,12 +4146,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4162,7 +4162,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126931567</v>
+        <v>126937620</v>
       </c>
       <c r="B35" t="n">
         <v>98448</v>
@@ -4190,32 +4190,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>690686</v>
+        <v>690612</v>
       </c>
       <c r="R35" t="n">
-        <v>7096928</v>
+        <v>7096930</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4245,6 +4237,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Cirka 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4260,12 +4257,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4276,7 +4273,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126937620</v>
+        <v>126936888</v>
       </c>
       <c r="B36" t="n">
         <v>98448</v>
@@ -4304,24 +4301,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>690612</v>
+        <v>690639</v>
       </c>
       <c r="R36" t="n">
-        <v>7096930</v>
+        <v>7096927</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4351,11 +4356,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Cirka 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4371,12 +4371,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4387,7 +4387,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126936888</v>
+        <v>126931567</v>
       </c>
       <c r="B37" t="n">
         <v>98448</v>
@@ -4417,12 +4417,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -4430,14 +4430,14 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>690639</v>
+        <v>690686</v>
       </c>
       <c r="R37" t="n">
-        <v>7096927</v>
+        <v>7096928</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4485,12 +4485,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -5424,48 +5424,60 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126928173</v>
+        <v>126936885</v>
       </c>
       <c r="B47" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>690547</v>
+        <v>690596</v>
       </c>
       <c r="R47" t="n">
-        <v>7096876</v>
+        <v>7097007</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5503,25 +5515,30 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126937632</v>
+        <v>126928173</v>
       </c>
       <c r="B48" t="n">
         <v>79018</v>
@@ -5552,14 +5569,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>690454</v>
+        <v>690547</v>
       </c>
       <c r="R48" t="n">
-        <v>7097036</v>
+        <v>7096876</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5606,26 +5623,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126936877</v>
+        <v>126937632</v>
       </c>
       <c r="B49" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5633,37 +5646,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>690378</v>
+        <v>690454</v>
       </c>
       <c r="R49" t="n">
-        <v>7096984</v>
+        <v>7097036</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5707,12 +5720,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5723,10 +5736,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126936911</v>
+        <v>126936877</v>
       </c>
       <c r="B50" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5734,21 +5747,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5758,10 +5771,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>690481</v>
+        <v>690378</v>
       </c>
       <c r="R50" t="n">
-        <v>7097028</v>
+        <v>7096984</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5824,7 +5837,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126937623</v>
+        <v>126936911</v>
       </c>
       <c r="B51" t="n">
         <v>79018</v>
@@ -5855,17 +5868,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>690707</v>
+        <v>690481</v>
       </c>
       <c r="R51" t="n">
-        <v>7096903</v>
+        <v>7097028</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5909,12 +5922,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5925,60 +5938,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126936885</v>
+        <v>126937623</v>
       </c>
       <c r="B52" t="n">
-        <v>98448</v>
+        <v>79018</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>690596</v>
+        <v>690707</v>
       </c>
       <c r="R52" t="n">
-        <v>7097007</v>
+        <v>7096903</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6016,19 +6017,18 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6039,10 +6039,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126927086</v>
+        <v>126927000</v>
       </c>
       <c r="B53" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6050,21 +6050,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6074,10 +6074,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>690545</v>
+        <v>690487</v>
       </c>
       <c r="R53" t="n">
-        <v>7097033</v>
+        <v>7097101</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6136,10 +6136,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126927000</v>
+        <v>126936878</v>
       </c>
       <c r="B54" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6147,37 +6147,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>690487</v>
+        <v>690509</v>
       </c>
       <c r="R54" t="n">
-        <v>7097101</v>
+        <v>7096927</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6221,57 +6221,73 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126936878</v>
+        <v>126931571</v>
       </c>
       <c r="B55" t="n">
-        <v>79636</v>
+        <v>98448</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>690509</v>
+        <v>690644</v>
       </c>
       <c r="R55" t="n">
-        <v>7096927</v>
+        <v>7096948</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6312,18 +6328,19 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6334,10 +6351,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126928117</v>
+        <v>126927086</v>
       </c>
       <c r="B56" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6345,34 +6362,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>690540</v>
+        <v>690545</v>
       </c>
       <c r="R56" t="n">
-        <v>7096888</v>
+        <v>7097033</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6431,60 +6448,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126931571</v>
+        <v>126928117</v>
       </c>
       <c r="B57" t="n">
-        <v>98448</v>
+        <v>79018</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>690644</v>
+        <v>690540</v>
       </c>
       <c r="R57" t="n">
-        <v>7096948</v>
+        <v>7096888</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6522,33 +6527,28 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126926624</v>
+        <v>126936881</v>
       </c>
       <c r="B58" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6556,37 +6556,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>690399</v>
+        <v>690617</v>
       </c>
       <c r="R58" t="n">
-        <v>7097170</v>
+        <v>7096851</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6630,19 +6630,23 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126926566</v>
+        <v>126926624</v>
       </c>
       <c r="B59" t="n">
         <v>79018</v>
@@ -6677,10 +6681,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>690362</v>
+        <v>690399</v>
       </c>
       <c r="R59" t="n">
-        <v>7097210</v>
+        <v>7097170</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6739,7 +6743,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126937630</v>
+        <v>126926566</v>
       </c>
       <c r="B60" t="n">
         <v>79018</v>
@@ -6770,14 +6774,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>690480</v>
+        <v>690362</v>
       </c>
       <c r="R60" t="n">
-        <v>7096994</v>
+        <v>7097210</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6824,23 +6828,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126927108</v>
+        <v>126937630</v>
       </c>
       <c r="B61" t="n">
         <v>79018</v>
@@ -6871,14 +6871,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>690542</v>
+        <v>690480</v>
       </c>
       <c r="R61" t="n">
-        <v>7097030</v>
+        <v>7096994</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6925,19 +6925,23 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126927426</v>
+        <v>126927108</v>
       </c>
       <c r="B62" t="n">
         <v>79018</v>
@@ -6972,10 +6976,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>690560</v>
+        <v>690542</v>
       </c>
       <c r="R62" t="n">
-        <v>7097019</v>
+        <v>7097030</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7034,10 +7038,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126936881</v>
+        <v>126927426</v>
       </c>
       <c r="B63" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7045,37 +7049,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>690617</v>
+        <v>690560</v>
       </c>
       <c r="R63" t="n">
-        <v>7096851</v>
+        <v>7097019</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7119,19 +7123,15 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8020,57 +8020,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126936891</v>
+        <v>126936879</v>
       </c>
       <c r="B73" t="n">
-        <v>98448</v>
+        <v>97331</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>690644</v>
+        <v>690490</v>
       </c>
       <c r="R73" t="n">
-        <v>7096931</v>
+        <v>7096937</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8111,7 +8099,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8134,32 +8121,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126936879</v>
+        <v>126936896</v>
       </c>
       <c r="B74" t="n">
-        <v>97331</v>
+        <v>79018</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8169,10 +8156,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>690490</v>
+        <v>690482</v>
       </c>
       <c r="R74" t="n">
-        <v>7096937</v>
+        <v>7096931</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8235,42 +8222,54 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126936896</v>
+        <v>126936891</v>
       </c>
       <c r="B75" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>690482</v>
+        <v>690644</v>
       </c>
       <c r="R75" t="n">
         <v>7096931</v>
@@ -8314,6 +8313,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -9621,48 +9621,48 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126936913</v>
+        <v>126937616</v>
       </c>
       <c r="B89" t="n">
-        <v>92620</v>
+        <v>79636</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>690466</v>
+        <v>690516</v>
       </c>
       <c r="R89" t="n">
-        <v>7096945</v>
+        <v>7096946</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9706,12 +9706,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9823,10 +9823,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126937616</v>
+        <v>126926697</v>
       </c>
       <c r="B91" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9834,34 +9834,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>690516</v>
+        <v>690438</v>
       </c>
       <c r="R91" t="n">
-        <v>7096946</v>
+        <v>7097148</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -9908,64 +9908,72 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126926697</v>
+        <v>126936892</v>
       </c>
       <c r="B92" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>690438</v>
+        <v>690619</v>
       </c>
       <c r="R92" t="n">
-        <v>7097148</v>
+        <v>7096955</v>
       </c>
       <c r="S92" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10003,75 +10011,68 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126936892</v>
+        <v>126936913</v>
       </c>
       <c r="B93" t="n">
-        <v>98448</v>
+        <v>92620</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>690619</v>
+        <v>690466</v>
       </c>
       <c r="R93" t="n">
-        <v>7096955</v>
+        <v>7096945</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10112,7 +10113,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10135,45 +10135,57 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126936898</v>
+        <v>126931572</v>
       </c>
       <c r="B94" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>690576</v>
+        <v>690665</v>
       </c>
       <c r="R94" t="n">
-        <v>7096919</v>
+        <v>7096920</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10214,18 +10226,19 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10236,7 +10249,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126931572</v>
+        <v>126937619</v>
       </c>
       <c r="B95" t="n">
         <v>98448</v>
@@ -10264,32 +10277,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>690665</v>
+        <v>690621</v>
       </c>
       <c r="R95" t="n">
-        <v>7096920</v>
+        <v>7096899</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10327,19 +10328,18 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10350,7 +10350,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126937619</v>
+        <v>126931569</v>
       </c>
       <c r="B96" t="n">
         <v>98448</v>
@@ -10378,20 +10378,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>690621</v>
+        <v>690550</v>
       </c>
       <c r="R96" t="n">
-        <v>7096899</v>
+        <v>7097011</v>
       </c>
       <c r="S96" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10429,18 +10445,19 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10451,7 +10468,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126931569</v>
+        <v>126936884</v>
       </c>
       <c r="B97" t="n">
         <v>98448</v>
@@ -10481,12 +10498,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -10498,14 +10515,14 @@
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>690550</v>
+        <v>690609</v>
       </c>
       <c r="R97" t="n">
-        <v>7097011</v>
+        <v>7096953</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10553,12 +10570,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10569,64 +10586,48 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126936884</v>
+        <v>126937627</v>
       </c>
       <c r="B98" t="n">
-        <v>98448</v>
+        <v>79018</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>690609</v>
+        <v>690522</v>
       </c>
       <c r="R98" t="n">
-        <v>7096953</v>
+        <v>7096919</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10664,19 +10665,18 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10784,10 +10784,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126936880</v>
+        <v>126936898</v>
       </c>
       <c r="B100" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10795,21 +10795,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10819,10 +10819,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>690619</v>
+        <v>690576</v>
       </c>
       <c r="R100" t="n">
-        <v>7097003</v>
+        <v>7096919</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10885,10 +10885,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126937627</v>
+        <v>126936880</v>
       </c>
       <c r="B101" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10896,37 +10896,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>690522</v>
+        <v>690619</v>
       </c>
       <c r="R101" t="n">
-        <v>7096919</v>
+        <v>7097003</v>
       </c>
       <c r="S101" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10970,12 +10970,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -10986,32 +10986,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126927178</v>
+        <v>126927465</v>
       </c>
       <c r="B102" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11021,10 +11021,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>690520</v>
+        <v>690596</v>
       </c>
       <c r="R102" t="n">
-        <v>7097024</v>
+        <v>7097023</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -11083,10 +11083,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126927139</v>
+        <v>126931577</v>
       </c>
       <c r="B103" t="n">
-        <v>80150</v>
+        <v>80056</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11094,37 +11094,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6462</v>
+        <v>6457</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>690515</v>
+        <v>690656</v>
       </c>
       <c r="R103" t="n">
-        <v>7097011</v>
+        <v>7096927</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11168,22 +11168,26 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY103" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126931566</v>
+        <v>126927184</v>
       </c>
       <c r="B104" t="n">
-        <v>78776</v>
+        <v>80121</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11191,37 +11195,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>690621</v>
+        <v>690520</v>
       </c>
       <c r="R104" t="n">
-        <v>7096855</v>
+        <v>7097024</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11265,48 +11269,44 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY104" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126927465</v>
+        <v>126927178</v>
       </c>
       <c r="B105" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11316,10 +11316,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>690596</v>
+        <v>690520</v>
       </c>
       <c r="R105" t="n">
-        <v>7097023</v>
+        <v>7097024</v>
       </c>
       <c r="S105" t="n">
         <v>15</v>
@@ -11378,10 +11378,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126931577</v>
+        <v>126927139</v>
       </c>
       <c r="B106" t="n">
-        <v>80056</v>
+        <v>80150</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11389,37 +11389,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6457</v>
+        <v>6462</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>690656</v>
+        <v>690515</v>
       </c>
       <c r="R106" t="n">
-        <v>7096927</v>
+        <v>7097011</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11463,26 +11463,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY106" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126927184</v>
+        <v>126931566</v>
       </c>
       <c r="B107" t="n">
-        <v>80121</v>
+        <v>78776</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11490,37 +11486,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>690520</v>
+        <v>690621</v>
       </c>
       <c r="R107" t="n">
-        <v>7097024</v>
+        <v>7096855</v>
       </c>
       <c r="S107" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11564,15 +11560,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY107" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">

--- a/artfynd/A 30467-2025 artfynd.xlsx
+++ b/artfynd/A 30467-2025 artfynd.xlsx
@@ -675,49 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126909580</v>
+        <v>126919968</v>
       </c>
       <c r="B2" t="n">
-        <v>98448</v>
+        <v>80027</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Rislidstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>690493</v>
+        <v>690349</v>
       </c>
       <c r="R2" t="n">
-        <v>7097055</v>
+        <v>7097128</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -747,19 +743,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
+          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -790,45 +776,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126919968</v>
+        <v>126909580</v>
       </c>
       <c r="B3" t="n">
-        <v>80025</v>
+        <v>98450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rislidstjärnarna, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>690349</v>
+        <v>690493</v>
       </c>
       <c r="R3" t="n">
-        <v>7097128</v>
+        <v>7097055</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,9 +848,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,12 +875,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
+          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -894,7 +894,7 @@
         <v>126917533</v>
       </c>
       <c r="B4" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>126917550</v>
       </c>
       <c r="B5" t="n">
-        <v>80157</v>
+        <v>80159</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>126917563</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>126919976</v>
       </c>
       <c r="B7" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>126917539</v>
       </c>
       <c r="B8" t="n">
-        <v>91341</v>
+        <v>91343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126919966</v>
+        <v>126917545</v>
       </c>
       <c r="B9" t="n">
-        <v>91341</v>
+        <v>80027</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1420,38 +1420,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1205</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rislidstjärnarna, Ång</t>
+          <t>Rislidtjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>690349</v>
+        <v>690344</v>
       </c>
       <c r="R9" t="n">
-        <v>7097128</v>
+        <v>7097126</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1498,12 +1494,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1514,45 +1510,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126917545</v>
+        <v>126909288</v>
       </c>
       <c r="B10" t="n">
-        <v>80025</v>
+        <v>78779</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rislidtjärnarna, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>690344</v>
+        <v>690438</v>
       </c>
       <c r="R10" t="n">
-        <v>7097126</v>
+        <v>7097136</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,9 +1578,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1599,12 +1605,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1615,45 +1621,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126909288</v>
+        <v>126919966</v>
       </c>
       <c r="B11" t="n">
-        <v>78777</v>
+        <v>91343</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>1205</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Rislidstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>690438</v>
+        <v>690349</v>
       </c>
       <c r="R11" t="n">
-        <v>7097136</v>
+        <v>7097128</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1683,19 +1693,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1710,12 +1710,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
+          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1729,7 +1729,7 @@
         <v>126909413</v>
       </c>
       <c r="B12" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>126909538</v>
       </c>
       <c r="B13" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>126918516</v>
       </c>
       <c r="B14" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>126917549</v>
       </c>
       <c r="B15" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>126918507</v>
       </c>
       <c r="B16" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>126917534</v>
       </c>
       <c r="B17" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>126909505</v>
       </c>
       <c r="B18" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>126927367</v>
       </c>
       <c r="B19" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>126936912</v>
       </c>
       <c r="B20" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2699,48 +2699,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126931573</v>
+        <v>126927356</v>
       </c>
       <c r="B21" t="n">
-        <v>98448</v>
+        <v>79020</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>690578</v>
+        <v>690516</v>
       </c>
       <c r="R21" t="n">
-        <v>7096991</v>
+        <v>7096990</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2784,64 +2784,60 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126927356</v>
+        <v>126931573</v>
       </c>
       <c r="B22" t="n">
-        <v>79018</v>
+        <v>98450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>690516</v>
+        <v>690578</v>
       </c>
       <c r="R22" t="n">
-        <v>7096990</v>
+        <v>7096991</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2885,22 +2881,26 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>126926856</v>
       </c>
       <c r="B23" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2994,10 +2994,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126927661</v>
+        <v>126931565</v>
       </c>
       <c r="B24" t="n">
-        <v>79018</v>
+        <v>78779</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3005,37 +3005,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>690574</v>
+        <v>690620</v>
       </c>
       <c r="R24" t="n">
-        <v>7096978</v>
+        <v>7096859</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3079,76 +3079,64 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126936889</v>
+        <v>126937624</v>
       </c>
       <c r="B25" t="n">
-        <v>98448</v>
+        <v>79020</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>690595</v>
+        <v>690656</v>
       </c>
       <c r="R25" t="n">
-        <v>7096886</v>
+        <v>7096868</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3186,19 +3174,18 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3209,45 +3196,61 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126931565</v>
+        <v>126936889</v>
       </c>
       <c r="B26" t="n">
-        <v>78777</v>
+        <v>98450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>690620</v>
+        <v>690595</v>
       </c>
       <c r="R26" t="n">
-        <v>7096859</v>
+        <v>7096886</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3288,18 +3291,19 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3310,48 +3314,60 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126937624</v>
+        <v>126936890</v>
       </c>
       <c r="B27" t="n">
-        <v>79018</v>
+        <v>98450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>690656</v>
+        <v>690564</v>
       </c>
       <c r="R27" t="n">
-        <v>7096868</v>
+        <v>7096907</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3389,18 +3405,19 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3411,48 +3428,64 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126927842</v>
+        <v>126936886</v>
       </c>
       <c r="B28" t="n">
-        <v>79018</v>
+        <v>98450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>690605</v>
+        <v>690607</v>
       </c>
       <c r="R28" t="n">
-        <v>7096920</v>
+        <v>7097014</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3490,82 +3523,71 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126936886</v>
+        <v>126927842</v>
       </c>
       <c r="B29" t="n">
-        <v>98448</v>
+        <v>79020</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>690607</v>
+        <v>690605</v>
       </c>
       <c r="R29" t="n">
-        <v>7097014</v>
+        <v>7096920</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3603,83 +3625,66 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126936890</v>
+        <v>126927661</v>
       </c>
       <c r="B30" t="n">
-        <v>98448</v>
+        <v>79020</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>690564</v>
+        <v>690574</v>
       </c>
       <c r="R30" t="n">
-        <v>7096907</v>
+        <v>7096978</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3717,33 +3722,28 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126936883</v>
+        <v>126937621</v>
       </c>
       <c r="B31" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3768,36 +3768,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>690668</v>
+        <v>690635</v>
       </c>
       <c r="R31" t="n">
-        <v>7096918</v>
+        <v>7096944</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3829,25 +3813,29 @@
           <t>2025-07-26</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ca 40 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3858,10 +3846,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126937621</v>
+        <v>126936883</v>
       </c>
       <c r="B32" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3886,20 +3874,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>690635</v>
+        <v>690668</v>
       </c>
       <c r="R32" t="n">
-        <v>7096944</v>
+        <v>7096918</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3931,29 +3935,25 @@
           <t>2025-07-26</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ca 40 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3967,7 +3967,7 @@
         <v>126927550</v>
       </c>
       <c r="B33" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>126936897</v>
       </c>
       <c r="B34" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4162,10 +4162,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126937620</v>
+        <v>126931567</v>
       </c>
       <c r="B35" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4190,24 +4190,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>690612</v>
+        <v>690686</v>
       </c>
       <c r="R35" t="n">
-        <v>7096930</v>
+        <v>7096928</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4237,11 +4245,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Cirka 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4257,12 +4260,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4276,7 +4279,7 @@
         <v>126936888</v>
       </c>
       <c r="B36" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4387,10 +4390,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126931567</v>
+        <v>126937620</v>
       </c>
       <c r="B37" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4415,32 +4418,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>690686</v>
+        <v>690612</v>
       </c>
       <c r="R37" t="n">
-        <v>7096928</v>
+        <v>7096930</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4470,6 +4465,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Cirka 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4485,12 +4485,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4504,7 +4504,7 @@
         <v>126926531</v>
       </c>
       <c r="B38" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4598,10 +4598,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126936900</v>
+        <v>126936910</v>
       </c>
       <c r="B39" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4633,10 +4633,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>690663</v>
+        <v>690572</v>
       </c>
       <c r="R39" t="n">
-        <v>7096854</v>
+        <v>7096932</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4699,10 +4699,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126936910</v>
+        <v>126936900</v>
       </c>
       <c r="B40" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4734,10 +4734,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>690572</v>
+        <v>690663</v>
       </c>
       <c r="R40" t="n">
-        <v>7096932</v>
+        <v>7096854</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4803,7 +4803,7 @@
         <v>126936887</v>
       </c>
       <c r="B41" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>126926789</v>
       </c>
       <c r="B42" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>126936894</v>
       </c>
       <c r="B43" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5112,10 +5112,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126926859</v>
+        <v>126936882</v>
       </c>
       <c r="B44" t="n">
-        <v>79018</v>
+        <v>78779</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5123,37 +5123,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>690483</v>
+        <v>690560</v>
       </c>
       <c r="R44" t="n">
-        <v>7097114</v>
+        <v>7096959</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5197,72 +5197,64 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126931570</v>
+        <v>126926859</v>
       </c>
       <c r="B45" t="n">
-        <v>98448</v>
+        <v>79020</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>690658</v>
+        <v>690483</v>
       </c>
       <c r="R45" t="n">
-        <v>7096895</v>
+        <v>7097114</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5300,68 +5292,75 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126936882</v>
+        <v>126931570</v>
       </c>
       <c r="B46" t="n">
-        <v>78777</v>
+        <v>98450</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>690560</v>
+        <v>690658</v>
       </c>
       <c r="R46" t="n">
-        <v>7096959</v>
+        <v>7096895</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5402,18 +5401,19 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5424,60 +5424,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126936885</v>
+        <v>126937632</v>
       </c>
       <c r="B47" t="n">
-        <v>98448</v>
+        <v>79020</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>690596</v>
+        <v>690454</v>
       </c>
       <c r="R47" t="n">
-        <v>7097007</v>
+        <v>7097036</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5515,19 +5503,18 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5538,10 +5525,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126928173</v>
+        <v>126937623</v>
       </c>
       <c r="B48" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5569,14 +5556,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>690547</v>
+        <v>690707</v>
       </c>
       <c r="R48" t="n">
-        <v>7096876</v>
+        <v>7096903</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5623,22 +5610,26 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126937632</v>
+        <v>126928173</v>
       </c>
       <c r="B49" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5666,14 +5657,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>690454</v>
+        <v>690547</v>
       </c>
       <c r="R49" t="n">
-        <v>7097036</v>
+        <v>7096876</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5720,26 +5711,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126936877</v>
+        <v>126936911</v>
       </c>
       <c r="B50" t="n">
-        <v>79636</v>
+        <v>79020</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5747,21 +5734,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5771,10 +5758,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>690378</v>
+        <v>690481</v>
       </c>
       <c r="R50" t="n">
-        <v>7096984</v>
+        <v>7097028</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5837,10 +5824,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126936911</v>
+        <v>126936877</v>
       </c>
       <c r="B51" t="n">
-        <v>79018</v>
+        <v>79638</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5848,21 +5835,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5872,10 +5859,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>690481</v>
+        <v>690378</v>
       </c>
       <c r="R51" t="n">
-        <v>7097028</v>
+        <v>7096984</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5938,48 +5925,60 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126937623</v>
+        <v>126936885</v>
       </c>
       <c r="B52" t="n">
-        <v>79018</v>
+        <v>98450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>690707</v>
+        <v>690596</v>
       </c>
       <c r="R52" t="n">
-        <v>7096903</v>
+        <v>7097007</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6017,18 +6016,19 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6039,10 +6039,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126927000</v>
+        <v>126927086</v>
       </c>
       <c r="B53" t="n">
-        <v>79018</v>
+        <v>80123</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6050,21 +6050,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6074,10 +6074,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>690487</v>
+        <v>690545</v>
       </c>
       <c r="R53" t="n">
-        <v>7097101</v>
+        <v>7097033</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6136,10 +6136,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126936878</v>
+        <v>126927000</v>
       </c>
       <c r="B54" t="n">
-        <v>79636</v>
+        <v>79020</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6147,37 +6147,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>690509</v>
+        <v>690487</v>
       </c>
       <c r="R54" t="n">
-        <v>7096927</v>
+        <v>7097101</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6221,73 +6221,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126931571</v>
+        <v>126936878</v>
       </c>
       <c r="B55" t="n">
-        <v>98448</v>
+        <v>79638</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>690644</v>
+        <v>690509</v>
       </c>
       <c r="R55" t="n">
-        <v>7096948</v>
+        <v>7096927</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6328,19 +6312,18 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6351,10 +6334,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126927086</v>
+        <v>126928117</v>
       </c>
       <c r="B56" t="n">
-        <v>80121</v>
+        <v>79020</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6362,34 +6345,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>690545</v>
+        <v>690540</v>
       </c>
       <c r="R56" t="n">
-        <v>7097033</v>
+        <v>7096888</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6448,48 +6431,60 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126928117</v>
+        <v>126931571</v>
       </c>
       <c r="B57" t="n">
-        <v>79018</v>
+        <v>98450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>690540</v>
+        <v>690644</v>
       </c>
       <c r="R57" t="n">
-        <v>7096888</v>
+        <v>7096948</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6527,28 +6522,33 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
         <v>126936881</v>
       </c>
       <c r="B58" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         <v>126926624</v>
       </c>
       <c r="B59" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>126926566</v>
       </c>
       <c r="B60" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>126937630</v>
       </c>
       <c r="B61" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>126927108</v>
       </c>
       <c r="B62" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>126927426</v>
       </c>
       <c r="B63" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7135,32 +7135,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126927067</v>
+        <v>126927409</v>
       </c>
       <c r="B64" t="n">
-        <v>79018</v>
+        <v>98450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7170,13 +7170,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>690536</v>
+        <v>690545</v>
       </c>
       <c r="R64" t="n">
-        <v>7097045</v>
+        <v>7097003</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7232,48 +7232,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126926457</v>
+        <v>126936893</v>
       </c>
       <c r="B65" t="n">
-        <v>79018</v>
+        <v>98450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>690374</v>
+        <v>690658</v>
       </c>
       <c r="R65" t="n">
-        <v>7097232</v>
+        <v>7096938</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7317,22 +7317,26 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
         <v>126931576</v>
       </c>
       <c r="B66" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7430,32 +7434,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126927409</v>
+        <v>126927067</v>
       </c>
       <c r="B67" t="n">
-        <v>98448</v>
+        <v>79020</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7465,13 +7469,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>690545</v>
+        <v>690536</v>
       </c>
       <c r="R67" t="n">
-        <v>7097003</v>
+        <v>7097045</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7527,48 +7531,48 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126936893</v>
+        <v>126926457</v>
       </c>
       <c r="B68" t="n">
-        <v>98448</v>
+        <v>79020</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>690658</v>
+        <v>690374</v>
       </c>
       <c r="R68" t="n">
-        <v>7096938</v>
+        <v>7097232</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7612,26 +7616,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
         <v>126926526</v>
       </c>
       <c r="B69" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7725,10 +7725,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126936908</v>
+        <v>126927324</v>
       </c>
       <c r="B70" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7756,17 +7756,17 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>690598</v>
+        <v>690542</v>
       </c>
       <c r="R70" t="n">
-        <v>7096855</v>
+        <v>7097025</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7810,26 +7810,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126927324</v>
+        <v>126936908</v>
       </c>
       <c r="B71" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7857,17 +7853,17 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>690542</v>
+        <v>690598</v>
       </c>
       <c r="R71" t="n">
-        <v>7097025</v>
+        <v>7096855</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7911,22 +7907,26 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126927191</v>
+        <v>126936896</v>
       </c>
       <c r="B72" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7954,17 +7954,17 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>690524</v>
+        <v>690482</v>
       </c>
       <c r="R72" t="n">
-        <v>7097009</v>
+        <v>7096931</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8008,60 +8008,64 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126936879</v>
+        <v>126927191</v>
       </c>
       <c r="B73" t="n">
-        <v>97331</v>
+        <v>79020</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>690490</v>
+        <v>690524</v>
       </c>
       <c r="R73" t="n">
-        <v>7096937</v>
+        <v>7097009</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8105,58 +8109,66 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126936896</v>
+        <v>126936891</v>
       </c>
       <c r="B74" t="n">
-        <v>79018</v>
+        <v>98450</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>690482</v>
+        <v>690644</v>
       </c>
       <c r="R74" t="n">
         <v>7096931</v>
@@ -8200,6 +8212,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8222,57 +8235,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126936891</v>
+        <v>126936879</v>
       </c>
       <c r="B75" t="n">
-        <v>98448</v>
+        <v>97333</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>690644</v>
+        <v>690490</v>
       </c>
       <c r="R75" t="n">
-        <v>7096931</v>
+        <v>7096937</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8313,7 +8314,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8339,7 +8339,7 @@
         <v>126937629</v>
       </c>
       <c r="B76" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8437,10 +8437,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126927943</v>
+        <v>126927024</v>
       </c>
       <c r="B77" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8468,14 +8468,14 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>690585</v>
+        <v>690503</v>
       </c>
       <c r="R77" t="n">
-        <v>7096888</v>
+        <v>7097060</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8534,10 +8534,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126927024</v>
+        <v>126927395</v>
       </c>
       <c r="B78" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8569,10 +8569,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>690503</v>
+        <v>690542</v>
       </c>
       <c r="R78" t="n">
-        <v>7097060</v>
+        <v>7096989</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8631,10 +8631,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126927395</v>
+        <v>126927943</v>
       </c>
       <c r="B79" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8662,14 +8662,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>690542</v>
+        <v>690585</v>
       </c>
       <c r="R79" t="n">
-        <v>7096989</v>
+        <v>7096888</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8728,10 +8728,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126936909</v>
+        <v>126926723</v>
       </c>
       <c r="B80" t="n">
-        <v>79018</v>
+        <v>78779</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8739,37 +8739,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>690590</v>
+        <v>690433</v>
       </c>
       <c r="R80" t="n">
-        <v>7096893</v>
+        <v>7097136</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8813,26 +8813,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126927691</v>
+        <v>126937622</v>
       </c>
       <c r="B81" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8860,14 +8856,14 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>690577</v>
+        <v>690620</v>
       </c>
       <c r="R81" t="n">
-        <v>7096975</v>
+        <v>7096858</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8914,22 +8910,26 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126931564</v>
+        <v>126927691</v>
       </c>
       <c r="B82" t="n">
-        <v>79050</v>
+        <v>79020</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8937,37 +8937,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>690624</v>
+        <v>690577</v>
       </c>
       <c r="R82" t="n">
-        <v>7096879</v>
+        <v>7096975</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9011,26 +9011,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126937622</v>
+        <v>126936909</v>
       </c>
       <c r="B83" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9058,17 +9054,17 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>690620</v>
+        <v>690590</v>
       </c>
       <c r="R83" t="n">
-        <v>7096858</v>
+        <v>7096893</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9112,12 +9108,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9128,48 +9124,48 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126927343</v>
+        <v>126931564</v>
       </c>
       <c r="B84" t="n">
-        <v>98448</v>
+        <v>79052</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>690544</v>
+        <v>690624</v>
       </c>
       <c r="R84" t="n">
-        <v>7097007</v>
+        <v>7096879</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9213,44 +9209,48 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126926723</v>
+        <v>126927343</v>
       </c>
       <c r="B85" t="n">
-        <v>78777</v>
+        <v>98450</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9260,10 +9260,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>690433</v>
+        <v>690544</v>
       </c>
       <c r="R85" t="n">
-        <v>7097136</v>
+        <v>7097007</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9325,7 +9325,7 @@
         <v>126936899</v>
       </c>
       <c r="B86" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>126936901</v>
       </c>
       <c r="B87" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9527,7 +9527,7 @@
         <v>126927737</v>
       </c>
       <c r="B88" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9621,10 +9621,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126937616</v>
+        <v>126926697</v>
       </c>
       <c r="B89" t="n">
-        <v>79636</v>
+        <v>79020</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9632,34 +9632,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>690516</v>
+        <v>690438</v>
       </c>
       <c r="R89" t="n">
-        <v>7096946</v>
+        <v>7097148</v>
       </c>
       <c r="S89" t="n">
         <v>15</v>
@@ -9706,48 +9706,44 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126936895</v>
+        <v>126936913</v>
       </c>
       <c r="B90" t="n">
-        <v>79018</v>
+        <v>92622</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9757,7 +9753,7 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>690445</v>
+        <v>690466</v>
       </c>
       <c r="R90" t="n">
         <v>7096945</v>
@@ -9823,10 +9819,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126926697</v>
+        <v>126937616</v>
       </c>
       <c r="B91" t="n">
-        <v>79018</v>
+        <v>79638</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9834,34 +9830,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>690438</v>
+        <v>690516</v>
       </c>
       <c r="R91" t="n">
-        <v>7097148</v>
+        <v>7096946</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -9908,69 +9904,61 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126936892</v>
+        <v>126936895</v>
       </c>
       <c r="B92" t="n">
-        <v>98448</v>
+        <v>79020</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>690619</v>
+        <v>690445</v>
       </c>
       <c r="R92" t="n">
-        <v>7096955</v>
+        <v>7096945</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10011,7 +9999,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10034,45 +10021,57 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126936913</v>
+        <v>126936892</v>
       </c>
       <c r="B93" t="n">
-        <v>92620</v>
+        <v>98450</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>690466</v>
+        <v>690619</v>
       </c>
       <c r="R93" t="n">
-        <v>7096945</v>
+        <v>7096955</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10113,6 +10112,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10135,60 +10135,48 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126931572</v>
+        <v>126937627</v>
       </c>
       <c r="B94" t="n">
-        <v>98448</v>
+        <v>79020</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>690665</v>
+        <v>690522</v>
       </c>
       <c r="R94" t="n">
-        <v>7096920</v>
+        <v>7096919</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10226,19 +10214,18 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10249,48 +10236,48 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126937619</v>
+        <v>126936880</v>
       </c>
       <c r="B95" t="n">
-        <v>98448</v>
+        <v>78779</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>690621</v>
+        <v>690619</v>
       </c>
       <c r="R95" t="n">
-        <v>7096899</v>
+        <v>7097003</v>
       </c>
       <c r="S95" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10334,12 +10321,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10350,64 +10337,48 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126931569</v>
+        <v>126927128</v>
       </c>
       <c r="B96" t="n">
-        <v>98448</v>
+        <v>80123</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>690550</v>
+        <v>690517</v>
       </c>
       <c r="R96" t="n">
-        <v>7097011</v>
+        <v>7097014</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10445,84 +10416,63 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126936884</v>
+        <v>126936898</v>
       </c>
       <c r="B97" t="n">
-        <v>98448</v>
+        <v>79020</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>690609</v>
+        <v>690576</v>
       </c>
       <c r="R97" t="n">
-        <v>7096953</v>
+        <v>7096919</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10563,7 +10513,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10586,48 +10535,64 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126937627</v>
+        <v>126936884</v>
       </c>
       <c r="B98" t="n">
-        <v>79018</v>
+        <v>98450</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>690522</v>
+        <v>690609</v>
       </c>
       <c r="R98" t="n">
-        <v>7096919</v>
+        <v>7096953</v>
       </c>
       <c r="S98" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10665,18 +10630,19 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10687,45 +10653,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126927128</v>
+        <v>126937619</v>
       </c>
       <c r="B99" t="n">
-        <v>80121</v>
+        <v>98450</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>690517</v>
+        <v>690621</v>
       </c>
       <c r="R99" t="n">
-        <v>7097014</v>
+        <v>7096899</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -10772,57 +10738,77 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY99" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126936898</v>
+        <v>126931569</v>
       </c>
       <c r="B100" t="n">
-        <v>79018</v>
+        <v>98450</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>690576</v>
+        <v>690550</v>
       </c>
       <c r="R100" t="n">
-        <v>7096919</v>
+        <v>7097011</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10863,18 +10849,19 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10885,45 +10872,57 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126936880</v>
+        <v>126931572</v>
       </c>
       <c r="B101" t="n">
-        <v>78777</v>
+        <v>98450</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>690619</v>
+        <v>690665</v>
       </c>
       <c r="R101" t="n">
-        <v>7097003</v>
+        <v>7096920</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10964,18 +10963,19 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -10989,7 +10989,7 @@
         <v>126927465</v>
       </c>
       <c r="B102" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11083,48 +11083,48 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126931577</v>
+        <v>126927292</v>
       </c>
       <c r="B103" t="n">
-        <v>80056</v>
+        <v>98450</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6457</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>690656</v>
+        <v>690530</v>
       </c>
       <c r="R103" t="n">
-        <v>7096927</v>
+        <v>7097014</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11168,48 +11168,44 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY103" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126927184</v>
+        <v>126927178</v>
       </c>
       <c r="B104" t="n">
-        <v>80121</v>
+        <v>80152</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11281,10 +11277,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126927178</v>
+        <v>126927139</v>
       </c>
       <c r="B105" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11316,10 +11312,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>690520</v>
+        <v>690515</v>
       </c>
       <c r="R105" t="n">
-        <v>7097024</v>
+        <v>7097011</v>
       </c>
       <c r="S105" t="n">
         <v>15</v>
@@ -11378,10 +11374,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126927139</v>
+        <v>126931577</v>
       </c>
       <c r="B106" t="n">
-        <v>80150</v>
+        <v>80058</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11389,37 +11385,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6462</v>
+        <v>6457</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>690515</v>
+        <v>690656</v>
       </c>
       <c r="R106" t="n">
-        <v>7097011</v>
+        <v>7096927</v>
       </c>
       <c r="S106" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11463,22 +11459,26 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY106" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126931566</v>
+        <v>126927184</v>
       </c>
       <c r="B107" t="n">
-        <v>78776</v>
+        <v>80123</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11486,37 +11486,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>690621</v>
+        <v>690520</v>
       </c>
       <c r="R107" t="n">
-        <v>7096855</v>
+        <v>7097024</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11560,64 +11560,60 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY107" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126927292</v>
+        <v>126931566</v>
       </c>
       <c r="B108" t="n">
-        <v>98448</v>
+        <v>78778</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>690530</v>
+        <v>690621</v>
       </c>
       <c r="R108" t="n">
-        <v>7097014</v>
+        <v>7096855</v>
       </c>
       <c r="S108" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11661,15 +11657,19 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY108" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30467-2025 artfynd.xlsx
+++ b/artfynd/A 30467-2025 artfynd.xlsx
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126917545</v>
+        <v>126919966</v>
       </c>
       <c r="B9" t="n">
-        <v>80027</v>
+        <v>91343</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1420,34 +1420,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>1205</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rislidtjärnarna, Ång</t>
+          <t>Rislidstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>690344</v>
+        <v>690349</v>
       </c>
       <c r="R9" t="n">
-        <v>7097126</v>
+        <v>7097128</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,12 +1498,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1510,45 +1514,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126909288</v>
+        <v>126917545</v>
       </c>
       <c r="B10" t="n">
-        <v>78779</v>
+        <v>80027</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Rislidtjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>690438</v>
+        <v>690344</v>
       </c>
       <c r="R10" t="n">
-        <v>7097136</v>
+        <v>7097126</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1578,19 +1582,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1605,12 +1599,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1621,49 +1615,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126919966</v>
+        <v>126909288</v>
       </c>
       <c r="B11" t="n">
-        <v>91343</v>
+        <v>78779</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1205</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rislidstjärnarna, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>690349</v>
+        <v>690438</v>
       </c>
       <c r="R11" t="n">
-        <v>7097128</v>
+        <v>7097136</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,9 +1683,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1710,12 +1710,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
+          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -2994,10 +2994,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126931565</v>
+        <v>126927842</v>
       </c>
       <c r="B24" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3005,37 +3005,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>690620</v>
+        <v>690605</v>
       </c>
       <c r="R24" t="n">
-        <v>7096859</v>
+        <v>7096920</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3079,23 +3079,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126937624</v>
+        <v>126927661</v>
       </c>
       <c r="B25" t="n">
         <v>79020</v>
@@ -3126,14 +3122,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>690656</v>
+        <v>690574</v>
       </c>
       <c r="R25" t="n">
-        <v>7096868</v>
+        <v>7096978</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3180,80 +3176,60 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126936889</v>
+        <v>126937624</v>
       </c>
       <c r="B26" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>690595</v>
+        <v>690656</v>
       </c>
       <c r="R26" t="n">
-        <v>7096886</v>
+        <v>7096868</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3291,19 +3267,18 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3314,7 +3289,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126936890</v>
+        <v>126936889</v>
       </c>
       <c r="B27" t="n">
         <v>98450</v>
@@ -3344,7 +3319,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3352,7 +3327,11 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
@@ -3361,10 +3340,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>690564</v>
+        <v>690595</v>
       </c>
       <c r="R27" t="n">
-        <v>7096907</v>
+        <v>7096886</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3546,10 +3525,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126927842</v>
+        <v>126931565</v>
       </c>
       <c r="B29" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3557,37 +3536,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>690605</v>
+        <v>690620</v>
       </c>
       <c r="R29" t="n">
-        <v>7096920</v>
+        <v>7096859</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3631,60 +3610,76 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126927661</v>
+        <v>126936890</v>
       </c>
       <c r="B30" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>690574</v>
+        <v>690564</v>
       </c>
       <c r="R30" t="n">
-        <v>7096978</v>
+        <v>7096907</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3722,66 +3717,71 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126937621</v>
+        <v>126936897</v>
       </c>
       <c r="B31" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>690635</v>
+        <v>690544</v>
       </c>
       <c r="R31" t="n">
-        <v>7096944</v>
+        <v>7096906</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3811,11 +3811,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ca 40 bladrosetter</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3830,12 +3825,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3846,7 +3841,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126936883</v>
+        <v>126937621</v>
       </c>
       <c r="B32" t="n">
         <v>98450</v>
@@ -3874,36 +3869,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>690668</v>
+        <v>690635</v>
       </c>
       <c r="R32" t="n">
-        <v>7096918</v>
+        <v>7096944</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3935,25 +3914,29 @@
           <t>2025-07-26</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ca 40 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4061,45 +4044,61 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126936897</v>
+        <v>126936883</v>
       </c>
       <c r="B34" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>690544</v>
+        <v>690668</v>
       </c>
       <c r="R34" t="n">
-        <v>7096906</v>
+        <v>7096918</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4140,6 +4139,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4276,7 +4276,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126936888</v>
+        <v>126937620</v>
       </c>
       <c r="B36" t="n">
         <v>98450</v>
@@ -4304,32 +4304,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>690639</v>
+        <v>690612</v>
       </c>
       <c r="R36" t="n">
-        <v>7096927</v>
+        <v>7096930</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4359,6 +4351,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Cirka 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4374,12 +4371,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4390,7 +4387,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126937620</v>
+        <v>126936888</v>
       </c>
       <c r="B37" t="n">
         <v>98450</v>
@@ -4418,24 +4415,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>690612</v>
+        <v>690639</v>
       </c>
       <c r="R37" t="n">
-        <v>7096930</v>
+        <v>7096927</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4465,11 +4470,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Cirka 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4485,12 +4485,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4914,48 +4914,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126926789</v>
+        <v>126936894</v>
       </c>
       <c r="B42" t="n">
-        <v>91352</v>
+        <v>98450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>690438</v>
+        <v>690497</v>
       </c>
       <c r="R42" t="n">
-        <v>7097141</v>
+        <v>7097017</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4999,60 +4999,64 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126936894</v>
+        <v>126926789</v>
       </c>
       <c r="B43" t="n">
-        <v>98450</v>
+        <v>91352</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>690497</v>
+        <v>690438</v>
       </c>
       <c r="R43" t="n">
-        <v>7097017</v>
+        <v>7097141</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5096,26 +5100,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126936882</v>
+        <v>126926859</v>
       </c>
       <c r="B44" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5123,37 +5123,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>690560</v>
+        <v>690483</v>
       </c>
       <c r="R44" t="n">
-        <v>7096959</v>
+        <v>7097114</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5197,64 +5197,72 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126926859</v>
+        <v>126931570</v>
       </c>
       <c r="B45" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>690483</v>
+        <v>690658</v>
       </c>
       <c r="R45" t="n">
-        <v>7097114</v>
+        <v>7096895</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5292,75 +5300,68 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126931570</v>
+        <v>126936882</v>
       </c>
       <c r="B46" t="n">
-        <v>98450</v>
+        <v>78779</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>690658</v>
+        <v>690560</v>
       </c>
       <c r="R46" t="n">
-        <v>7096895</v>
+        <v>7096959</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5401,19 +5402,18 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -6039,10 +6039,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126927086</v>
+        <v>126927000</v>
       </c>
       <c r="B53" t="n">
-        <v>80123</v>
+        <v>79020</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6050,21 +6050,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6074,10 +6074,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>690545</v>
+        <v>690487</v>
       </c>
       <c r="R53" t="n">
-        <v>7097033</v>
+        <v>7097101</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6136,10 +6136,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126927000</v>
+        <v>126927086</v>
       </c>
       <c r="B54" t="n">
-        <v>79020</v>
+        <v>80123</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6147,21 +6147,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6171,10 +6171,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>690487</v>
+        <v>690545</v>
       </c>
       <c r="R54" t="n">
-        <v>7097101</v>
+        <v>7097033</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6233,10 +6233,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126936878</v>
+        <v>126928117</v>
       </c>
       <c r="B55" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6244,37 +6244,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>690509</v>
+        <v>690540</v>
       </c>
       <c r="R55" t="n">
-        <v>7096927</v>
+        <v>7096888</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6318,26 +6318,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126928117</v>
+        <v>126936878</v>
       </c>
       <c r="B56" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6345,37 +6341,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>690540</v>
+        <v>690509</v>
       </c>
       <c r="R56" t="n">
-        <v>7096888</v>
+        <v>7096927</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6419,15 +6415,19 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6545,10 +6545,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126936881</v>
+        <v>126926624</v>
       </c>
       <c r="B58" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6556,37 +6556,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>690617</v>
+        <v>690399</v>
       </c>
       <c r="R58" t="n">
-        <v>7096851</v>
+        <v>7097170</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6630,23 +6630,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126926624</v>
+        <v>126937630</v>
       </c>
       <c r="B59" t="n">
         <v>79020</v>
@@ -6677,14 +6673,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>690399</v>
+        <v>690480</v>
       </c>
       <c r="R59" t="n">
-        <v>7097170</v>
+        <v>7096994</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6731,19 +6727,23 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126926566</v>
+        <v>126927108</v>
       </c>
       <c r="B60" t="n">
         <v>79020</v>
@@ -6778,10 +6778,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>690362</v>
+        <v>690542</v>
       </c>
       <c r="R60" t="n">
-        <v>7097210</v>
+        <v>7097030</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6840,7 +6840,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126937630</v>
+        <v>126927426</v>
       </c>
       <c r="B61" t="n">
         <v>79020</v>
@@ -6871,14 +6871,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>690480</v>
+        <v>690560</v>
       </c>
       <c r="R61" t="n">
-        <v>7096994</v>
+        <v>7097019</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6925,23 +6925,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126927108</v>
+        <v>126926566</v>
       </c>
       <c r="B62" t="n">
         <v>79020</v>
@@ -6976,10 +6972,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>690542</v>
+        <v>690362</v>
       </c>
       <c r="R62" t="n">
-        <v>7097030</v>
+        <v>7097210</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7038,10 +7034,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126927426</v>
+        <v>126936881</v>
       </c>
       <c r="B63" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7049,37 +7045,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>690560</v>
+        <v>690617</v>
       </c>
       <c r="R63" t="n">
-        <v>7097019</v>
+        <v>7096851</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7123,60 +7119,64 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126927409</v>
+        <v>126931576</v>
       </c>
       <c r="B64" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>690545</v>
+        <v>690565</v>
       </c>
       <c r="R64" t="n">
-        <v>7097003</v>
+        <v>7096992</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7220,57 +7220,61 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126936893</v>
+        <v>126927067</v>
       </c>
       <c r="B65" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>690658</v>
+        <v>690536</v>
       </c>
       <c r="R65" t="n">
-        <v>7096938</v>
+        <v>7097045</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7317,23 +7321,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126931576</v>
+        <v>126926457</v>
       </c>
       <c r="B66" t="n">
         <v>79020</v>
@@ -7364,17 +7364,17 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>690565</v>
+        <v>690374</v>
       </c>
       <c r="R66" t="n">
-        <v>7096992</v>
+        <v>7097232</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7418,61 +7418,57 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126927067</v>
+        <v>126936893</v>
       </c>
       <c r="B67" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>690536</v>
+        <v>690658</v>
       </c>
       <c r="R67" t="n">
-        <v>7097045</v>
+        <v>7096938</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7519,44 +7515,48 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126926457</v>
+        <v>126927409</v>
       </c>
       <c r="B68" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7566,10 +7566,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>690374</v>
+        <v>690545</v>
       </c>
       <c r="R68" t="n">
-        <v>7097232</v>
+        <v>7097003</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7923,42 +7923,54 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126936896</v>
+        <v>126936891</v>
       </c>
       <c r="B72" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>690482</v>
+        <v>690644</v>
       </c>
       <c r="R72" t="n">
         <v>7096931</v>
@@ -8002,6 +8014,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8024,7 +8037,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126927191</v>
+        <v>126936896</v>
       </c>
       <c r="B73" t="n">
         <v>79020</v>
@@ -8055,17 +8068,17 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>690524</v>
+        <v>690482</v>
       </c>
       <c r="R73" t="n">
-        <v>7097009</v>
+        <v>7096931</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8109,69 +8122,61 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126936891</v>
+        <v>126936879</v>
       </c>
       <c r="B74" t="n">
-        <v>98450</v>
+        <v>97333</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>690644</v>
+        <v>690490</v>
       </c>
       <c r="R74" t="n">
-        <v>7096931</v>
+        <v>7096937</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8212,7 +8217,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8235,48 +8239,48 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126936879</v>
+        <v>126927191</v>
       </c>
       <c r="B75" t="n">
-        <v>97333</v>
+        <v>79020</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>690490</v>
+        <v>690524</v>
       </c>
       <c r="R75" t="n">
-        <v>7096937</v>
+        <v>7097009</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8320,23 +8324,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126937629</v>
+        <v>126927943</v>
       </c>
       <c r="B76" t="n">
         <v>79020</v>
@@ -8367,14 +8367,14 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>690504</v>
+        <v>690585</v>
       </c>
       <c r="R76" t="n">
-        <v>7096980</v>
+        <v>7096888</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8421,23 +8421,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126927024</v>
+        <v>126937629</v>
       </c>
       <c r="B77" t="n">
         <v>79020</v>
@@ -8468,14 +8464,14 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>690503</v>
+        <v>690504</v>
       </c>
       <c r="R77" t="n">
-        <v>7097060</v>
+        <v>7096980</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8522,19 +8518,23 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126927395</v>
+        <v>126927024</v>
       </c>
       <c r="B78" t="n">
         <v>79020</v>
@@ -8569,10 +8569,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>690542</v>
+        <v>690503</v>
       </c>
       <c r="R78" t="n">
-        <v>7096989</v>
+        <v>7097060</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8631,7 +8631,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126927943</v>
+        <v>126927395</v>
       </c>
       <c r="B79" t="n">
         <v>79020</v>
@@ -8662,14 +8662,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>690585</v>
+        <v>690542</v>
       </c>
       <c r="R79" t="n">
-        <v>7096888</v>
+        <v>7096989</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8728,32 +8728,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126926723</v>
+        <v>126927343</v>
       </c>
       <c r="B80" t="n">
-        <v>78779</v>
+        <v>98450</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8763,10 +8763,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>690433</v>
+        <v>690544</v>
       </c>
       <c r="R80" t="n">
-        <v>7097136</v>
+        <v>7097007</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8825,10 +8825,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126937622</v>
+        <v>126931564</v>
       </c>
       <c r="B81" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8836,37 +8836,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>690620</v>
+        <v>690624</v>
       </c>
       <c r="R81" t="n">
-        <v>7096858</v>
+        <v>7096879</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8910,12 +8910,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -8926,7 +8926,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126927691</v>
+        <v>126937622</v>
       </c>
       <c r="B82" t="n">
         <v>79020</v>
@@ -8957,14 +8957,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>690577</v>
+        <v>690620</v>
       </c>
       <c r="R82" t="n">
-        <v>7096975</v>
+        <v>7096858</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9011,19 +9011,23 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126936909</v>
+        <v>126927691</v>
       </c>
       <c r="B83" t="n">
         <v>79020</v>
@@ -9054,17 +9058,17 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>690590</v>
+        <v>690577</v>
       </c>
       <c r="R83" t="n">
-        <v>7096893</v>
+        <v>7096975</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9108,26 +9112,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126931564</v>
+        <v>126936909</v>
       </c>
       <c r="B84" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9135,34 +9135,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>690624</v>
+        <v>690590</v>
       </c>
       <c r="R84" t="n">
-        <v>7096879</v>
+        <v>7096893</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9209,12 +9209,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9225,32 +9225,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126927343</v>
+        <v>126926723</v>
       </c>
       <c r="B85" t="n">
-        <v>98450</v>
+        <v>78779</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9260,10 +9260,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>690544</v>
+        <v>690433</v>
       </c>
       <c r="R85" t="n">
-        <v>7097007</v>
+        <v>7097136</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9322,7 +9322,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126936899</v>
+        <v>126927737</v>
       </c>
       <c r="B86" t="n">
         <v>79020</v>
@@ -9353,17 +9353,17 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>690607</v>
+        <v>690623</v>
       </c>
       <c r="R86" t="n">
-        <v>7097019</v>
+        <v>7096931</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9407,23 +9407,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126936901</v>
+        <v>126936899</v>
       </c>
       <c r="B87" t="n">
         <v>79020</v>
@@ -9458,10 +9454,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>690623</v>
+        <v>690607</v>
       </c>
       <c r="R87" t="n">
-        <v>7096862</v>
+        <v>7097019</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9524,7 +9520,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126927737</v>
+        <v>126936901</v>
       </c>
       <c r="B88" t="n">
         <v>79020</v>
@@ -9555,17 +9551,17 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
         <v>690623</v>
       </c>
       <c r="R88" t="n">
-        <v>7096931</v>
+        <v>7096862</v>
       </c>
       <c r="S88" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9609,60 +9605,64 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY88" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126926697</v>
+        <v>126936913</v>
       </c>
       <c r="B89" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>690438</v>
+        <v>690466</v>
       </c>
       <c r="R89" t="n">
-        <v>7097148</v>
+        <v>7096945</v>
       </c>
       <c r="S89" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9706,60 +9706,64 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126936913</v>
+        <v>126926697</v>
       </c>
       <c r="B90" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>690466</v>
+        <v>690438</v>
       </c>
       <c r="R90" t="n">
-        <v>7096945</v>
+        <v>7097148</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9803,26 +9807,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126937616</v>
+        <v>126936895</v>
       </c>
       <c r="B91" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9830,37 +9830,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>690516</v>
+        <v>690445</v>
       </c>
       <c r="R91" t="n">
-        <v>7096946</v>
+        <v>7096945</v>
       </c>
       <c r="S91" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9904,12 +9904,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -9920,10 +9920,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126936895</v>
+        <v>126937616</v>
       </c>
       <c r="B92" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9931,37 +9931,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>690445</v>
+        <v>690516</v>
       </c>
       <c r="R92" t="n">
-        <v>7096945</v>
+        <v>7096946</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10005,12 +10005,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10236,10 +10236,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126936880</v>
+        <v>126936898</v>
       </c>
       <c r="B95" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10247,21 +10247,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10271,10 +10271,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>690619</v>
+        <v>690576</v>
       </c>
       <c r="R95" t="n">
-        <v>7097003</v>
+        <v>7096919</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10434,48 +10434,48 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126936898</v>
+        <v>126937619</v>
       </c>
       <c r="B97" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>690576</v>
+        <v>690621</v>
       </c>
       <c r="R97" t="n">
-        <v>7096919</v>
+        <v>7096899</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10519,12 +10519,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10535,7 +10535,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126936884</v>
+        <v>126931569</v>
       </c>
       <c r="B98" t="n">
         <v>98450</v>
@@ -10565,12 +10565,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -10582,14 +10582,14 @@
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>690609</v>
+        <v>690550</v>
       </c>
       <c r="R98" t="n">
-        <v>7096953</v>
+        <v>7097011</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10637,12 +10637,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10653,7 +10653,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126937619</v>
+        <v>126936884</v>
       </c>
       <c r="B99" t="n">
         <v>98450</v>
@@ -10681,20 +10681,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>690621</v>
+        <v>690609</v>
       </c>
       <c r="R99" t="n">
-        <v>7096899</v>
+        <v>7096953</v>
       </c>
       <c r="S99" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10732,18 +10748,19 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10754,7 +10771,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126931569</v>
+        <v>126931572</v>
       </c>
       <c r="B100" t="n">
         <v>98450</v>
@@ -10784,7 +10801,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -10792,11 +10809,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
@@ -10805,10 +10818,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>690550</v>
+        <v>690665</v>
       </c>
       <c r="R100" t="n">
-        <v>7097011</v>
+        <v>7096920</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10872,57 +10885,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126931572</v>
+        <v>126936880</v>
       </c>
       <c r="B101" t="n">
-        <v>98450</v>
+        <v>78779</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>690665</v>
+        <v>690619</v>
       </c>
       <c r="R101" t="n">
-        <v>7096920</v>
+        <v>7097003</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10963,19 +10964,18 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -10986,10 +10986,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126927465</v>
+        <v>126931566</v>
       </c>
       <c r="B102" t="n">
-        <v>79020</v>
+        <v>78778</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10997,37 +10997,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>690596</v>
+        <v>690621</v>
       </c>
       <c r="R102" t="n">
-        <v>7097023</v>
+        <v>7096855</v>
       </c>
       <c r="S102" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11071,44 +11071,48 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY102" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126927292</v>
+        <v>126927465</v>
       </c>
       <c r="B103" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11118,10 +11122,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>690530</v>
+        <v>690596</v>
       </c>
       <c r="R103" t="n">
-        <v>7097014</v>
+        <v>7097023</v>
       </c>
       <c r="S103" t="n">
         <v>15</v>
@@ -11180,10 +11184,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126927178</v>
+        <v>126931577</v>
       </c>
       <c r="B104" t="n">
-        <v>80152</v>
+        <v>80058</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11191,37 +11195,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6462</v>
+        <v>6457</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>690520</v>
+        <v>690656</v>
       </c>
       <c r="R104" t="n">
-        <v>7097024</v>
+        <v>7096927</v>
       </c>
       <c r="S104" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11265,44 +11269,48 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY104" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126927139</v>
+        <v>126927184</v>
       </c>
       <c r="B105" t="n">
-        <v>80152</v>
+        <v>80123</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11312,10 +11320,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>690515</v>
+        <v>690520</v>
       </c>
       <c r="R105" t="n">
-        <v>7097011</v>
+        <v>7097024</v>
       </c>
       <c r="S105" t="n">
         <v>15</v>
@@ -11374,10 +11382,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126931577</v>
+        <v>126927178</v>
       </c>
       <c r="B106" t="n">
-        <v>80058</v>
+        <v>80152</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11385,37 +11393,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6457</v>
+        <v>6462</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>690656</v>
+        <v>690520</v>
       </c>
       <c r="R106" t="n">
-        <v>7096927</v>
+        <v>7097024</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11459,48 +11467,44 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY106" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126927184</v>
+        <v>126927139</v>
       </c>
       <c r="B107" t="n">
-        <v>80123</v>
+        <v>80152</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11510,10 +11514,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>690520</v>
+        <v>690515</v>
       </c>
       <c r="R107" t="n">
-        <v>7097024</v>
+        <v>7097011</v>
       </c>
       <c r="S107" t="n">
         <v>15</v>
@@ -11572,48 +11576,48 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126931566</v>
+        <v>126927292</v>
       </c>
       <c r="B108" t="n">
-        <v>78778</v>
+        <v>98450</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>690621</v>
+        <v>690530</v>
       </c>
       <c r="R108" t="n">
-        <v>7096855</v>
+        <v>7097014</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11657,19 +11661,15 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY108" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30467-2025 artfynd.xlsx
+++ b/artfynd/A 30467-2025 artfynd.xlsx
@@ -2598,45 +2598,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126936912</v>
+        <v>126931573</v>
       </c>
       <c r="B20" t="n">
-        <v>92622</v>
+        <v>98450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>690392</v>
+        <v>690578</v>
       </c>
       <c r="R20" t="n">
-        <v>7097038</v>
+        <v>7096991</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2683,12 +2683,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2699,10 +2699,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126927356</v>
+        <v>126926856</v>
       </c>
       <c r="B21" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2710,37 +2710,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>N Johannesbomyran, N Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>690516</v>
+        <v>690563</v>
       </c>
       <c r="R21" t="n">
-        <v>7096990</v>
+        <v>7096856</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2784,57 +2784,57 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126931573</v>
+        <v>126936912</v>
       </c>
       <c r="B22" t="n">
-        <v>98450</v>
+        <v>92622</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>690578</v>
+        <v>690392</v>
       </c>
       <c r="R22" t="n">
-        <v>7096991</v>
+        <v>7097038</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2881,12 +2881,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2897,10 +2897,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126926856</v>
+        <v>126927356</v>
       </c>
       <c r="B23" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2908,37 +2908,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>N Johannesbomyran, N Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>690563</v>
+        <v>690516</v>
       </c>
       <c r="R23" t="n">
-        <v>7096856</v>
+        <v>7096990</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2982,12 +2982,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3188,48 +3188,60 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126937624</v>
+        <v>126936890</v>
       </c>
       <c r="B26" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>690656</v>
+        <v>690564</v>
       </c>
       <c r="R26" t="n">
-        <v>7096868</v>
+        <v>7096907</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3267,18 +3279,19 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3626,60 +3639,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126936890</v>
+        <v>126937624</v>
       </c>
       <c r="B30" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>690564</v>
+        <v>690656</v>
       </c>
       <c r="R30" t="n">
-        <v>7096907</v>
+        <v>7096868</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3717,19 +3718,18 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -4162,7 +4162,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126931567</v>
+        <v>126936888</v>
       </c>
       <c r="B35" t="n">
         <v>98450</v>
@@ -4192,12 +4192,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -4205,14 +4205,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>690686</v>
+        <v>690639</v>
       </c>
       <c r="R35" t="n">
-        <v>7096928</v>
+        <v>7096927</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4260,12 +4260,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4276,7 +4276,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126937620</v>
+        <v>126931567</v>
       </c>
       <c r="B36" t="n">
         <v>98450</v>
@@ -4304,24 +4304,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>690612</v>
+        <v>690686</v>
       </c>
       <c r="R36" t="n">
-        <v>7096930</v>
+        <v>7096928</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4351,11 +4359,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Cirka 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4371,12 +4374,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4387,7 +4390,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126936888</v>
+        <v>126937620</v>
       </c>
       <c r="B37" t="n">
         <v>98450</v>
@@ -4415,32 +4418,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>690639</v>
+        <v>690612</v>
       </c>
       <c r="R37" t="n">
-        <v>7096927</v>
+        <v>7096930</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4470,6 +4465,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Cirka 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4485,12 +4485,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -6039,48 +6039,60 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126927000</v>
+        <v>126931571</v>
       </c>
       <c r="B53" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>690487</v>
+        <v>690644</v>
       </c>
       <c r="R53" t="n">
-        <v>7097101</v>
+        <v>7096948</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6118,28 +6130,33 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126927086</v>
+        <v>126927000</v>
       </c>
       <c r="B54" t="n">
-        <v>80123</v>
+        <v>79020</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6147,21 +6164,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6171,10 +6188,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>690545</v>
+        <v>690487</v>
       </c>
       <c r="R54" t="n">
-        <v>7097033</v>
+        <v>7097101</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6233,10 +6250,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126928117</v>
+        <v>126927086</v>
       </c>
       <c r="B55" t="n">
-        <v>79020</v>
+        <v>80123</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6244,34 +6261,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>690540</v>
+        <v>690545</v>
       </c>
       <c r="R55" t="n">
-        <v>7096888</v>
+        <v>7097033</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6330,10 +6347,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126936878</v>
+        <v>126928117</v>
       </c>
       <c r="B56" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6341,37 +6358,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>690509</v>
+        <v>690540</v>
       </c>
       <c r="R56" t="n">
-        <v>7096927</v>
+        <v>7096888</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6415,73 +6432,57 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126931571</v>
+        <v>126936878</v>
       </c>
       <c r="B57" t="n">
-        <v>98450</v>
+        <v>79638</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>690644</v>
+        <v>690509</v>
       </c>
       <c r="R57" t="n">
-        <v>7096948</v>
+        <v>7096927</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6522,19 +6523,18 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6545,10 +6545,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126926624</v>
+        <v>126936881</v>
       </c>
       <c r="B58" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6556,37 +6556,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>690399</v>
+        <v>690617</v>
       </c>
       <c r="R58" t="n">
-        <v>7097170</v>
+        <v>7096851</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6630,19 +6630,23 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126937630</v>
+        <v>126926624</v>
       </c>
       <c r="B59" t="n">
         <v>79020</v>
@@ -6673,14 +6677,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>690480</v>
+        <v>690399</v>
       </c>
       <c r="R59" t="n">
-        <v>7096994</v>
+        <v>7097170</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6727,23 +6731,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126927108</v>
+        <v>126937630</v>
       </c>
       <c r="B60" t="n">
         <v>79020</v>
@@ -6774,14 +6774,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>690542</v>
+        <v>690480</v>
       </c>
       <c r="R60" t="n">
-        <v>7097030</v>
+        <v>7096994</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6828,19 +6828,23 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126927426</v>
+        <v>126927108</v>
       </c>
       <c r="B61" t="n">
         <v>79020</v>
@@ -6875,10 +6879,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>690560</v>
+        <v>690542</v>
       </c>
       <c r="R61" t="n">
-        <v>7097019</v>
+        <v>7097030</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6937,7 +6941,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126926566</v>
+        <v>126927426</v>
       </c>
       <c r="B62" t="n">
         <v>79020</v>
@@ -6972,10 +6976,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>690362</v>
+        <v>690560</v>
       </c>
       <c r="R62" t="n">
-        <v>7097210</v>
+        <v>7097019</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7034,10 +7038,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126936881</v>
+        <v>126926566</v>
       </c>
       <c r="B63" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7045,37 +7049,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>690617</v>
+        <v>690362</v>
       </c>
       <c r="R63" t="n">
-        <v>7096851</v>
+        <v>7097210</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7119,19 +7123,15 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8336,7 +8336,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126927943</v>
+        <v>126937629</v>
       </c>
       <c r="B76" t="n">
         <v>79020</v>
@@ -8367,14 +8367,14 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>690585</v>
+        <v>690504</v>
       </c>
       <c r="R76" t="n">
-        <v>7096888</v>
+        <v>7096980</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8421,19 +8421,23 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126937629</v>
+        <v>126927024</v>
       </c>
       <c r="B77" t="n">
         <v>79020</v>
@@ -8464,14 +8468,14 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>690504</v>
+        <v>690503</v>
       </c>
       <c r="R77" t="n">
-        <v>7096980</v>
+        <v>7097060</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8518,23 +8522,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126927024</v>
+        <v>126927395</v>
       </c>
       <c r="B78" t="n">
         <v>79020</v>
@@ -8569,10 +8569,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>690503</v>
+        <v>690542</v>
       </c>
       <c r="R78" t="n">
-        <v>7097060</v>
+        <v>7096989</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8631,7 +8631,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126927395</v>
+        <v>126927943</v>
       </c>
       <c r="B79" t="n">
         <v>79020</v>
@@ -8662,14 +8662,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>690542</v>
+        <v>690585</v>
       </c>
       <c r="R79" t="n">
-        <v>7096989</v>
+        <v>7096888</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -9322,7 +9322,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126927737</v>
+        <v>126936899</v>
       </c>
       <c r="B86" t="n">
         <v>79020</v>
@@ -9353,17 +9353,17 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>690623</v>
+        <v>690607</v>
       </c>
       <c r="R86" t="n">
-        <v>7096931</v>
+        <v>7097019</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9407,19 +9407,23 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126936899</v>
+        <v>126936901</v>
       </c>
       <c r="B87" t="n">
         <v>79020</v>
@@ -9454,10 +9458,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>690607</v>
+        <v>690623</v>
       </c>
       <c r="R87" t="n">
-        <v>7097019</v>
+        <v>7096862</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9520,7 +9524,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126936901</v>
+        <v>126927737</v>
       </c>
       <c r="B88" t="n">
         <v>79020</v>
@@ -9551,17 +9555,17 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
         <v>690623</v>
       </c>
       <c r="R88" t="n">
-        <v>7096862</v>
+        <v>7096931</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9605,61 +9609,69 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY88" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126936913</v>
+        <v>126936892</v>
       </c>
       <c r="B89" t="n">
-        <v>92622</v>
+        <v>98450</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>690466</v>
+        <v>690619</v>
       </c>
       <c r="R89" t="n">
-        <v>7096945</v>
+        <v>7096955</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9700,6 +9712,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9722,48 +9735,48 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126926697</v>
+        <v>126936913</v>
       </c>
       <c r="B90" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>690438</v>
+        <v>690466</v>
       </c>
       <c r="R90" t="n">
-        <v>7097148</v>
+        <v>7096945</v>
       </c>
       <c r="S90" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9807,19 +9820,23 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126936895</v>
+        <v>126926697</v>
       </c>
       <c r="B91" t="n">
         <v>79020</v>
@@ -9850,17 +9867,17 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>690445</v>
+        <v>690438</v>
       </c>
       <c r="R91" t="n">
-        <v>7096945</v>
+        <v>7097148</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9904,26 +9921,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126937616</v>
+        <v>126936895</v>
       </c>
       <c r="B92" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9931,37 +9944,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>690516</v>
+        <v>690445</v>
       </c>
       <c r="R92" t="n">
-        <v>7096946</v>
+        <v>7096945</v>
       </c>
       <c r="S92" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10005,12 +10018,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10021,60 +10034,48 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126936892</v>
+        <v>126937616</v>
       </c>
       <c r="B93" t="n">
-        <v>98450</v>
+        <v>79638</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>690619</v>
+        <v>690516</v>
       </c>
       <c r="R93" t="n">
-        <v>7096955</v>
+        <v>7096946</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10112,19 +10113,18 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10434,7 +10434,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126937619</v>
+        <v>126936884</v>
       </c>
       <c r="B97" t="n">
         <v>98450</v>
@@ -10462,20 +10462,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>690621</v>
+        <v>690609</v>
       </c>
       <c r="R97" t="n">
-        <v>7096899</v>
+        <v>7096953</v>
       </c>
       <c r="S97" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10513,18 +10529,19 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10535,7 +10552,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126931569</v>
+        <v>126931572</v>
       </c>
       <c r="B98" t="n">
         <v>98450</v>
@@ -10565,7 +10582,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -10573,11 +10590,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
@@ -10586,10 +10599,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>690550</v>
+        <v>690665</v>
       </c>
       <c r="R98" t="n">
-        <v>7097011</v>
+        <v>7096920</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10653,7 +10666,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126936884</v>
+        <v>126937619</v>
       </c>
       <c r="B99" t="n">
         <v>98450</v>
@@ -10681,36 +10694,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>690609</v>
+        <v>690621</v>
       </c>
       <c r="R99" t="n">
-        <v>7096953</v>
+        <v>7096899</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10748,19 +10745,18 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10771,7 +10767,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126931572</v>
+        <v>126931569</v>
       </c>
       <c r="B100" t="n">
         <v>98450</v>
@@ -10801,7 +10797,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -10809,7 +10805,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
@@ -10818,10 +10818,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>690665</v>
+        <v>690550</v>
       </c>
       <c r="R100" t="n">
-        <v>7096920</v>
+        <v>7097011</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10986,48 +10986,48 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126931566</v>
+        <v>126927292</v>
       </c>
       <c r="B102" t="n">
-        <v>78778</v>
+        <v>98450</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>690621</v>
+        <v>690530</v>
       </c>
       <c r="R102" t="n">
-        <v>7096855</v>
+        <v>7097014</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11071,26 +11071,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY102" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126927465</v>
+        <v>126931566</v>
       </c>
       <c r="B103" t="n">
-        <v>79020</v>
+        <v>78778</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11098,37 +11094,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>690596</v>
+        <v>690621</v>
       </c>
       <c r="R103" t="n">
-        <v>7097023</v>
+        <v>7096855</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11172,60 +11168,64 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY103" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126931577</v>
+        <v>126927465</v>
       </c>
       <c r="B104" t="n">
-        <v>80058</v>
+        <v>79020</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>690656</v>
+        <v>690596</v>
       </c>
       <c r="R104" t="n">
-        <v>7096927</v>
+        <v>7097023</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11269,64 +11269,60 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY104" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126927184</v>
+        <v>126931577</v>
       </c>
       <c r="B105" t="n">
-        <v>80123</v>
+        <v>80058</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>6457</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>690520</v>
+        <v>690656</v>
       </c>
       <c r="R105" t="n">
-        <v>7097024</v>
+        <v>7096927</v>
       </c>
       <c r="S105" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11370,44 +11366,48 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY105" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126927178</v>
+        <v>126927184</v>
       </c>
       <c r="B106" t="n">
-        <v>80152</v>
+        <v>80123</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11479,7 +11479,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126927139</v>
+        <v>126927178</v>
       </c>
       <c r="B107" t="n">
         <v>80152</v>
@@ -11514,10 +11514,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>690515</v>
+        <v>690520</v>
       </c>
       <c r="R107" t="n">
-        <v>7097011</v>
+        <v>7097024</v>
       </c>
       <c r="S107" t="n">
         <v>15</v>
@@ -11576,32 +11576,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126927292</v>
+        <v>126927139</v>
       </c>
       <c r="B108" t="n">
-        <v>98450</v>
+        <v>80152</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11611,10 +11611,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>690530</v>
+        <v>690515</v>
       </c>
       <c r="R108" t="n">
-        <v>7097014</v>
+        <v>7097011</v>
       </c>
       <c r="S108" t="n">
         <v>15</v>

--- a/artfynd/A 30467-2025 artfynd.xlsx
+++ b/artfynd/A 30467-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY108"/>
+  <dimension ref="A1:AY109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11671,6 +11671,103 @@
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>126927712</v>
+      </c>
+      <c r="B109" t="n">
+        <v>79070</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>690586</v>
+      </c>
+      <c r="R109" t="n">
+        <v>7096958</v>
+      </c>
+      <c r="S109" t="n">
+        <v>15</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30467-2025 artfynd.xlsx
+++ b/artfynd/A 30467-2025 artfynd.xlsx
@@ -11676,7 +11676,7 @@
         <v>126927712</v>
       </c>
       <c r="B109" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>

--- a/artfynd/A 30467-2025 artfynd.xlsx
+++ b/artfynd/A 30467-2025 artfynd.xlsx
@@ -11676,7 +11676,7 @@
         <v>126927712</v>
       </c>
       <c r="B109" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>

--- a/artfynd/A 30467-2025 artfynd.xlsx
+++ b/artfynd/A 30467-2025 artfynd.xlsx
@@ -11676,7 +11676,7 @@
         <v>126927712</v>
       </c>
       <c r="B109" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>

--- a/artfynd/A 30467-2025 artfynd.xlsx
+++ b/artfynd/A 30467-2025 artfynd.xlsx
@@ -11676,7 +11676,7 @@
         <v>126927712</v>
       </c>
       <c r="B109" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>

--- a/artfynd/A 30467-2025 artfynd.xlsx
+++ b/artfynd/A 30467-2025 artfynd.xlsx
@@ -11676,7 +11676,7 @@
         <v>126927712</v>
       </c>
       <c r="B109" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>

--- a/artfynd/A 30467-2025 artfynd.xlsx
+++ b/artfynd/A 30467-2025 artfynd.xlsx
@@ -11676,7 +11676,7 @@
         <v>126927712</v>
       </c>
       <c r="B109" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>

--- a/artfynd/A 30467-2025 artfynd.xlsx
+++ b/artfynd/A 30467-2025 artfynd.xlsx
@@ -11676,7 +11676,7 @@
         <v>126927712</v>
       </c>
       <c r="B109" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>

--- a/artfynd/A 30467-2025 artfynd.xlsx
+++ b/artfynd/A 30467-2025 artfynd.xlsx
@@ -675,45 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126919968</v>
+        <v>126909580</v>
       </c>
       <c r="B2" t="n">
-        <v>80027</v>
+        <v>98436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rislidstjärnarna, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>690349</v>
+        <v>690493</v>
       </c>
       <c r="R2" t="n">
-        <v>7097128</v>
+        <v>7097055</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,9 +747,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,12 +774,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
+          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -776,49 +790,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126909580</v>
+        <v>126919968</v>
       </c>
       <c r="B3" t="n">
-        <v>98450</v>
+        <v>80018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Rislidstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>690493</v>
+        <v>690349</v>
       </c>
       <c r="R3" t="n">
-        <v>7097055</v>
+        <v>7097128</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,19 +858,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,12 +875,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
+          <t>Emil Lindgren, Hedda Bring, Lotta Ihse, Eleonor Johansson, Fredrik Wilde, Nicklas Gustavsson, Isac Enetjärn, Malin Löfgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -894,7 +894,7 @@
         <v>126917533</v>
       </c>
       <c r="B4" t="n">
-        <v>57663</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,32 +1005,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126917550</v>
+        <v>126917563</v>
       </c>
       <c r="B5" t="n">
-        <v>80159</v>
+        <v>79011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>690515</v>
+        <v>690509</v>
       </c>
       <c r="R5" t="n">
-        <v>7097014</v>
+        <v>7097052</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,32 +1106,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126917563</v>
+        <v>126917550</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>80150</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>690509</v>
+        <v>690515</v>
       </c>
       <c r="R6" t="n">
-        <v>7097052</v>
+        <v>7097014</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1210,7 @@
         <v>126919976</v>
       </c>
       <c r="B7" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
+          <t>Emil Lindgren, Hedda Bring, Lotta Ihse, Eleonor Johansson, Fredrik Wilde, Nicklas Gustavsson, Isac Enetjärn, Malin Löfgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1311,7 +1311,7 @@
         <v>126917539</v>
       </c>
       <c r="B8" t="n">
-        <v>91343</v>
+        <v>91330</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>126919966</v>
       </c>
       <c r="B9" t="n">
-        <v>91343</v>
+        <v>91330</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
+          <t>Emil Lindgren, Hedda Bring, Lotta Ihse, Eleonor Johansson, Fredrik Wilde, Nicklas Gustavsson, Isac Enetjärn, Malin Löfgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1517,7 +1517,7 @@
         <v>126917545</v>
       </c>
       <c r="B10" t="n">
-        <v>80027</v>
+        <v>80018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>126909288</v>
       </c>
       <c r="B11" t="n">
-        <v>78779</v>
+        <v>78770</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>126909413</v>
       </c>
       <c r="B12" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>126909538</v>
       </c>
       <c r="B13" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>126918516</v>
       </c>
       <c r="B14" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>126917549</v>
       </c>
       <c r="B15" t="n">
-        <v>80123</v>
+        <v>80114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>126918507</v>
       </c>
       <c r="B16" t="n">
-        <v>80123</v>
+        <v>80114</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>126917534</v>
       </c>
       <c r="B17" t="n">
-        <v>57663</v>
+        <v>57657</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>126909505</v>
       </c>
       <c r="B18" t="n">
-        <v>80152</v>
+        <v>80143</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>126927367</v>
       </c>
       <c r="B19" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2598,45 +2598,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126931573</v>
+        <v>126936912</v>
       </c>
       <c r="B20" t="n">
-        <v>98450</v>
+        <v>92609</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>690578</v>
+        <v>690392</v>
       </c>
       <c r="R20" t="n">
-        <v>7096991</v>
+        <v>7097038</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2683,12 +2683,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2699,10 +2699,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126926856</v>
+        <v>126927356</v>
       </c>
       <c r="B21" t="n">
-        <v>78779</v>
+        <v>79011</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2710,37 +2710,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>N Johannesbomyran, N Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>690563</v>
+        <v>690516</v>
       </c>
       <c r="R21" t="n">
-        <v>7096856</v>
+        <v>7096990</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2784,57 +2784,57 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126936912</v>
+        <v>126931573</v>
       </c>
       <c r="B22" t="n">
-        <v>92622</v>
+        <v>98436</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>690392</v>
+        <v>690578</v>
       </c>
       <c r="R22" t="n">
-        <v>7097038</v>
+        <v>7096991</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2881,12 +2881,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2897,10 +2897,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126927356</v>
+        <v>126926856</v>
       </c>
       <c r="B23" t="n">
-        <v>79020</v>
+        <v>78770</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2908,37 +2908,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>N Johannesbomyran, N Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>690516</v>
+        <v>690563</v>
       </c>
       <c r="R23" t="n">
-        <v>7096990</v>
+        <v>7096856</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2982,22 +2982,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126927842</v>
+        <v>126927661</v>
       </c>
       <c r="B24" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,10 +3029,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>690605</v>
+        <v>690574</v>
       </c>
       <c r="R24" t="n">
-        <v>7096920</v>
+        <v>7096978</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3091,10 +3091,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126927661</v>
+        <v>126937624</v>
       </c>
       <c r="B25" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3122,14 +3122,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>690574</v>
+        <v>690656</v>
       </c>
       <c r="R25" t="n">
-        <v>7096978</v>
+        <v>7096868</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3176,72 +3176,64 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126936890</v>
+        <v>126927842</v>
       </c>
       <c r="B26" t="n">
-        <v>98450</v>
+        <v>79011</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>690564</v>
+        <v>690605</v>
       </c>
       <c r="R26" t="n">
-        <v>7096907</v>
+        <v>7096920</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3279,33 +3271,28 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126936889</v>
+        <v>126936886</v>
       </c>
       <c r="B27" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3332,7 +3319,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3353,10 +3340,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>690595</v>
+        <v>690607</v>
       </c>
       <c r="R27" t="n">
-        <v>7096886</v>
+        <v>7097014</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,10 +3407,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126936886</v>
+        <v>126936889</v>
       </c>
       <c r="B28" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3450,7 +3437,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3471,10 +3458,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>690607</v>
+        <v>690595</v>
       </c>
       <c r="R28" t="n">
-        <v>7097014</v>
+        <v>7096886</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3538,45 +3525,57 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126931565</v>
+        <v>126936890</v>
       </c>
       <c r="B29" t="n">
-        <v>78779</v>
+        <v>98436</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>690620</v>
+        <v>690564</v>
       </c>
       <c r="R29" t="n">
-        <v>7096859</v>
+        <v>7096907</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3617,18 +3616,19 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3639,10 +3639,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126937624</v>
+        <v>126931565</v>
       </c>
       <c r="B30" t="n">
-        <v>79020</v>
+        <v>78770</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3650,37 +3650,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>690656</v>
+        <v>690620</v>
       </c>
       <c r="R30" t="n">
-        <v>7096868</v>
+        <v>7096859</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3724,12 +3724,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3740,10 +3740,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126936897</v>
+        <v>126927550</v>
       </c>
       <c r="B31" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3771,17 +3771,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>690544</v>
+        <v>690574</v>
       </c>
       <c r="R31" t="n">
-        <v>7096906</v>
+        <v>7096994</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3825,64 +3825,60 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126937621</v>
+        <v>126936897</v>
       </c>
       <c r="B32" t="n">
-        <v>98450</v>
+        <v>79011</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>690635</v>
+        <v>690544</v>
       </c>
       <c r="R32" t="n">
-        <v>7096944</v>
+        <v>7096906</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3912,11 +3908,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ca 40 bladrosetter</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3931,12 +3922,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3947,45 +3938,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126927550</v>
+        <v>126937621</v>
       </c>
       <c r="B33" t="n">
-        <v>79020</v>
+        <v>98436</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>690574</v>
+        <v>690635</v>
       </c>
       <c r="R33" t="n">
-        <v>7096994</v>
+        <v>7096944</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4020,6 +4011,11 @@
           <t>2025-07-26</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ca 40 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4032,22 +4028,26 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
         <v>126936883</v>
       </c>
       <c r="B34" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>126936888</v>
       </c>
       <c r="B35" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>126931567</v>
       </c>
       <c r="B36" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>126937620</v>
       </c>
       <c r="B37" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>126926531</v>
       </c>
       <c r="B38" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4598,10 +4598,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126936910</v>
+        <v>126936900</v>
       </c>
       <c r="B39" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4633,10 +4633,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>690572</v>
+        <v>690663</v>
       </c>
       <c r="R39" t="n">
-        <v>7096932</v>
+        <v>7096854</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4699,10 +4699,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126936900</v>
+        <v>126936910</v>
       </c>
       <c r="B40" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4734,10 +4734,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>690663</v>
+        <v>690572</v>
       </c>
       <c r="R40" t="n">
-        <v>7096854</v>
+        <v>7096932</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4803,7 +4803,7 @@
         <v>126936887</v>
       </c>
       <c r="B41" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4914,48 +4914,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126936894</v>
+        <v>126926789</v>
       </c>
       <c r="B42" t="n">
-        <v>98450</v>
+        <v>91339</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>690497</v>
+        <v>690438</v>
       </c>
       <c r="R42" t="n">
-        <v>7097017</v>
+        <v>7097141</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4999,64 +4999,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126926789</v>
+        <v>126936894</v>
       </c>
       <c r="B43" t="n">
-        <v>91352</v>
+        <v>98436</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>690438</v>
+        <v>690497</v>
       </c>
       <c r="R43" t="n">
-        <v>7097141</v>
+        <v>7097017</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5100,22 +5096,26 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
         <v>126926859</v>
       </c>
       <c r="B44" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>126931570</v>
       </c>
       <c r="B45" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
         <v>126936882</v>
       </c>
       <c r="B46" t="n">
-        <v>78779</v>
+        <v>78770</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5424,10 +5424,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126937632</v>
+        <v>126928173</v>
       </c>
       <c r="B47" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5455,14 +5455,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>690454</v>
+        <v>690547</v>
       </c>
       <c r="R47" t="n">
-        <v>7097036</v>
+        <v>7096876</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5509,26 +5509,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126937623</v>
+        <v>126937632</v>
       </c>
       <c r="B48" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5560,10 +5556,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>690707</v>
+        <v>690454</v>
       </c>
       <c r="R48" t="n">
-        <v>7096903</v>
+        <v>7097036</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5626,10 +5622,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126928173</v>
+        <v>126936911</v>
       </c>
       <c r="B49" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5657,17 +5653,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>690547</v>
+        <v>690481</v>
       </c>
       <c r="R49" t="n">
-        <v>7096876</v>
+        <v>7097028</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5711,22 +5707,26 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126936911</v>
+        <v>126937623</v>
       </c>
       <c r="B50" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5754,17 +5754,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>690481</v>
+        <v>690707</v>
       </c>
       <c r="R50" t="n">
-        <v>7097028</v>
+        <v>7096903</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5808,12 +5808,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5827,7 +5827,7 @@
         <v>126936877</v>
       </c>
       <c r="B51" t="n">
-        <v>79638</v>
+        <v>79629</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>126936885</v>
       </c>
       <c r="B52" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6039,60 +6039,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126931571</v>
+        <v>126927000</v>
       </c>
       <c r="B53" t="n">
-        <v>98450</v>
+        <v>79011</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>690644</v>
+        <v>690487</v>
       </c>
       <c r="R53" t="n">
-        <v>7096948</v>
+        <v>7097101</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6130,33 +6118,28 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126927000</v>
+        <v>126928117</v>
       </c>
       <c r="B54" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6184,14 +6167,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>690487</v>
+        <v>690540</v>
       </c>
       <c r="R54" t="n">
-        <v>7097101</v>
+        <v>7096888</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6253,7 +6236,7 @@
         <v>126927086</v>
       </c>
       <c r="B55" t="n">
-        <v>80123</v>
+        <v>80114</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6347,10 +6330,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126928117</v>
+        <v>126936878</v>
       </c>
       <c r="B56" t="n">
-        <v>79020</v>
+        <v>79629</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6358,37 +6341,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>690540</v>
+        <v>690509</v>
       </c>
       <c r="R56" t="n">
-        <v>7096888</v>
+        <v>7096927</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6432,57 +6415,73 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126936878</v>
+        <v>126931571</v>
       </c>
       <c r="B57" t="n">
-        <v>79638</v>
+        <v>98436</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>690509</v>
+        <v>690644</v>
       </c>
       <c r="R57" t="n">
-        <v>7096927</v>
+        <v>7096948</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6523,18 +6522,19 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6545,10 +6545,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126936881</v>
+        <v>126926624</v>
       </c>
       <c r="B58" t="n">
-        <v>78779</v>
+        <v>79011</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6556,37 +6556,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>690617</v>
+        <v>690399</v>
       </c>
       <c r="R58" t="n">
-        <v>7096851</v>
+        <v>7097170</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6630,26 +6630,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126926624</v>
+        <v>126926566</v>
       </c>
       <c r="B59" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6681,10 +6677,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>690399</v>
+        <v>690362</v>
       </c>
       <c r="R59" t="n">
-        <v>7097170</v>
+        <v>7097210</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6746,7 +6742,7 @@
         <v>126937630</v>
       </c>
       <c r="B60" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6847,7 +6843,7 @@
         <v>126927108</v>
       </c>
       <c r="B61" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6944,7 +6940,7 @@
         <v>126927426</v>
       </c>
       <c r="B62" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7038,10 +7034,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126926566</v>
+        <v>126936881</v>
       </c>
       <c r="B63" t="n">
-        <v>79020</v>
+        <v>78770</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7049,37 +7045,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>690362</v>
+        <v>690617</v>
       </c>
       <c r="R63" t="n">
-        <v>7097210</v>
+        <v>7096851</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7123,22 +7119,26 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126931576</v>
+        <v>126927067</v>
       </c>
       <c r="B64" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7166,14 +7166,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>690565</v>
+        <v>690536</v>
       </c>
       <c r="R64" t="n">
-        <v>7096992</v>
+        <v>7097045</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7220,26 +7220,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126927067</v>
+        <v>126926457</v>
       </c>
       <c r="B65" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7271,13 +7267,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>690536</v>
+        <v>690374</v>
       </c>
       <c r="R65" t="n">
-        <v>7097045</v>
+        <v>7097232</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7333,10 +7329,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126926457</v>
+        <v>126931576</v>
       </c>
       <c r="B66" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7364,17 +7360,17 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>690374</v>
+        <v>690565</v>
       </c>
       <c r="R66" t="n">
-        <v>7097232</v>
+        <v>7096992</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7418,22 +7414,26 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
         <v>126936893</v>
       </c>
       <c r="B67" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>126927409</v>
       </c>
       <c r="B68" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>126926526</v>
       </c>
       <c r="B69" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7725,10 +7725,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126927324</v>
+        <v>126936908</v>
       </c>
       <c r="B70" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7756,17 +7756,17 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>690542</v>
+        <v>690598</v>
       </c>
       <c r="R70" t="n">
-        <v>7097025</v>
+        <v>7096855</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7810,22 +7810,26 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126936908</v>
+        <v>126927324</v>
       </c>
       <c r="B71" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7853,17 +7857,17 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>690598</v>
+        <v>690542</v>
       </c>
       <c r="R71" t="n">
-        <v>7096855</v>
+        <v>7097025</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7907,26 +7911,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
         <v>126936891</v>
       </c>
       <c r="B72" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8037,32 +8037,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126936896</v>
+        <v>126936879</v>
       </c>
       <c r="B73" t="n">
-        <v>79020</v>
+        <v>97320</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8072,10 +8072,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>690482</v>
+        <v>690490</v>
       </c>
       <c r="R73" t="n">
-        <v>7096931</v>
+        <v>7096937</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8138,48 +8138,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126936879</v>
+        <v>126927191</v>
       </c>
       <c r="B74" t="n">
-        <v>97333</v>
+        <v>79011</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>690490</v>
+        <v>690524</v>
       </c>
       <c r="R74" t="n">
-        <v>7096937</v>
+        <v>7097009</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8223,26 +8223,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126927191</v>
+        <v>126936896</v>
       </c>
       <c r="B75" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8270,17 +8266,17 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>690524</v>
+        <v>690482</v>
       </c>
       <c r="R75" t="n">
-        <v>7097009</v>
+        <v>7096931</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8324,22 +8320,26 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126937629</v>
+        <v>126927943</v>
       </c>
       <c r="B76" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8367,14 +8367,14 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>690504</v>
+        <v>690585</v>
       </c>
       <c r="R76" t="n">
-        <v>7096980</v>
+        <v>7096888</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8421,26 +8421,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126927024</v>
+        <v>126937629</v>
       </c>
       <c r="B77" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8468,14 +8464,14 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>690503</v>
+        <v>690504</v>
       </c>
       <c r="R77" t="n">
-        <v>7097060</v>
+        <v>7096980</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8522,22 +8518,26 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126927395</v>
+        <v>126927024</v>
       </c>
       <c r="B78" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8569,10 +8569,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>690542</v>
+        <v>690503</v>
       </c>
       <c r="R78" t="n">
-        <v>7096989</v>
+        <v>7097060</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8631,10 +8631,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126927943</v>
+        <v>126927395</v>
       </c>
       <c r="B79" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8662,14 +8662,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>690585</v>
+        <v>690542</v>
       </c>
       <c r="R79" t="n">
-        <v>7096888</v>
+        <v>7096989</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8728,48 +8728,48 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126927343</v>
+        <v>126936909</v>
       </c>
       <c r="B80" t="n">
-        <v>98450</v>
+        <v>79011</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>690544</v>
+        <v>690590</v>
       </c>
       <c r="R80" t="n">
-        <v>7097007</v>
+        <v>7096893</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8813,22 +8813,26 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126931564</v>
+        <v>126937622</v>
       </c>
       <c r="B81" t="n">
-        <v>79052</v>
+        <v>79011</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8836,37 +8840,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>690624</v>
+        <v>690620</v>
       </c>
       <c r="R81" t="n">
-        <v>7096879</v>
+        <v>7096858</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8910,12 +8914,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -8926,10 +8930,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126937622</v>
+        <v>126927691</v>
       </c>
       <c r="B82" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8957,14 +8961,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>690620</v>
+        <v>690577</v>
       </c>
       <c r="R82" t="n">
-        <v>7096858</v>
+        <v>7096975</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9011,26 +9015,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126927691</v>
+        <v>126926723</v>
       </c>
       <c r="B83" t="n">
-        <v>79020</v>
+        <v>78770</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9038,21 +9038,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9062,10 +9062,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>690577</v>
+        <v>690433</v>
       </c>
       <c r="R83" t="n">
-        <v>7096975</v>
+        <v>7097136</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9124,10 +9124,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126936909</v>
+        <v>126931564</v>
       </c>
       <c r="B84" t="n">
-        <v>79020</v>
+        <v>79043</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9135,34 +9135,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>690590</v>
+        <v>690624</v>
       </c>
       <c r="R84" t="n">
-        <v>7096893</v>
+        <v>7096879</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9209,12 +9209,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9225,32 +9225,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126926723</v>
+        <v>126927343</v>
       </c>
       <c r="B85" t="n">
-        <v>78779</v>
+        <v>98436</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9260,10 +9260,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>690433</v>
+        <v>690544</v>
       </c>
       <c r="R85" t="n">
-        <v>7097136</v>
+        <v>7097007</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9325,7 +9325,7 @@
         <v>126936899</v>
       </c>
       <c r="B86" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9423,10 +9423,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126936901</v>
+        <v>126927737</v>
       </c>
       <c r="B87" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9454,17 +9454,17 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
         <v>690623</v>
       </c>
       <c r="R87" t="n">
-        <v>7096862</v>
+        <v>7096931</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9508,26 +9508,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126927737</v>
+        <v>126936901</v>
       </c>
       <c r="B88" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9555,17 +9551,17 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
         <v>690623</v>
       </c>
       <c r="R88" t="n">
-        <v>7096931</v>
+        <v>7096862</v>
       </c>
       <c r="S88" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9609,69 +9605,61 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY88" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126936892</v>
+        <v>126936913</v>
       </c>
       <c r="B89" t="n">
-        <v>98450</v>
+        <v>92609</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>690619</v>
+        <v>690466</v>
       </c>
       <c r="R89" t="n">
-        <v>7096955</v>
+        <v>7096945</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9712,7 +9700,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9735,32 +9722,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126936913</v>
+        <v>126936895</v>
       </c>
       <c r="B90" t="n">
-        <v>92622</v>
+        <v>79011</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9770,7 +9757,7 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>690466</v>
+        <v>690445</v>
       </c>
       <c r="R90" t="n">
         <v>7096945</v>
@@ -9839,7 +9826,7 @@
         <v>126926697</v>
       </c>
       <c r="B91" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9933,10 +9920,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126936895</v>
+        <v>126937616</v>
       </c>
       <c r="B92" t="n">
-        <v>79020</v>
+        <v>79629</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9944,37 +9931,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>690445</v>
+        <v>690516</v>
       </c>
       <c r="R92" t="n">
-        <v>7096945</v>
+        <v>7096946</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10018,12 +10005,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10034,48 +10021,60 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126937616</v>
+        <v>126936892</v>
       </c>
       <c r="B93" t="n">
-        <v>79638</v>
+        <v>98436</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>690516</v>
+        <v>690619</v>
       </c>
       <c r="R93" t="n">
-        <v>7096946</v>
+        <v>7096955</v>
       </c>
       <c r="S93" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10113,18 +10112,19 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10135,48 +10135,60 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126937627</v>
+        <v>126931572</v>
       </c>
       <c r="B94" t="n">
-        <v>79020</v>
+        <v>98436</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>690522</v>
+        <v>690665</v>
       </c>
       <c r="R94" t="n">
-        <v>7096919</v>
+        <v>7096920</v>
       </c>
       <c r="S94" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10214,18 +10226,19 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10236,45 +10249,61 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126936898</v>
+        <v>126936884</v>
       </c>
       <c r="B95" t="n">
-        <v>79020</v>
+        <v>98436</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>690576</v>
+        <v>690609</v>
       </c>
       <c r="R95" t="n">
-        <v>7096919</v>
+        <v>7096953</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10315,6 +10344,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10337,45 +10367,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126927128</v>
+        <v>126937619</v>
       </c>
       <c r="B96" t="n">
-        <v>80123</v>
+        <v>98436</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>690517</v>
+        <v>690621</v>
       </c>
       <c r="R96" t="n">
-        <v>7097014</v>
+        <v>7096899</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -10422,22 +10452,26 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126936884</v>
+        <v>126931569</v>
       </c>
       <c r="B97" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10464,12 +10498,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -10481,14 +10515,14 @@
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>690609</v>
+        <v>690550</v>
       </c>
       <c r="R97" t="n">
-        <v>7096953</v>
+        <v>7097011</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10536,12 +10570,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10552,57 +10586,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126931572</v>
+        <v>126936880</v>
       </c>
       <c r="B98" t="n">
-        <v>98450</v>
+        <v>78770</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>690665</v>
+        <v>690619</v>
       </c>
       <c r="R98" t="n">
-        <v>7096920</v>
+        <v>7097003</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10643,19 +10665,18 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10666,48 +10687,48 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126937619</v>
+        <v>126936898</v>
       </c>
       <c r="B99" t="n">
-        <v>98450</v>
+        <v>79011</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>690621</v>
+        <v>690576</v>
       </c>
       <c r="R99" t="n">
-        <v>7096899</v>
+        <v>7096919</v>
       </c>
       <c r="S99" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10751,12 +10772,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10767,64 +10788,48 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126931569</v>
+        <v>126937627</v>
       </c>
       <c r="B100" t="n">
-        <v>98450</v>
+        <v>79011</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>690550</v>
+        <v>690522</v>
       </c>
       <c r="R100" t="n">
-        <v>7097011</v>
+        <v>7096919</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10862,19 +10867,18 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10885,10 +10889,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126936880</v>
+        <v>126927128</v>
       </c>
       <c r="B101" t="n">
-        <v>78779</v>
+        <v>80114</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10896,37 +10900,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>690619</v>
+        <v>690517</v>
       </c>
       <c r="R101" t="n">
-        <v>7097003</v>
+        <v>7097014</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10970,48 +10974,44 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY101" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126927292</v>
+        <v>126927465</v>
       </c>
       <c r="B102" t="n">
-        <v>98450</v>
+        <v>79011</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11021,10 +11021,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>690530</v>
+        <v>690596</v>
       </c>
       <c r="R102" t="n">
-        <v>7097014</v>
+        <v>7097023</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -11086,7 +11086,7 @@
         <v>126931566</v>
       </c>
       <c r="B103" t="n">
-        <v>78778</v>
+        <v>78769</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11184,48 +11184,48 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126927465</v>
+        <v>126931577</v>
       </c>
       <c r="B104" t="n">
-        <v>79020</v>
+        <v>80049</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6457</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>690596</v>
+        <v>690656</v>
       </c>
       <c r="R104" t="n">
-        <v>7097023</v>
+        <v>7096927</v>
       </c>
       <c r="S104" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11269,22 +11269,26 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY104" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126931577</v>
+        <v>126927178</v>
       </c>
       <c r="B105" t="n">
-        <v>80058</v>
+        <v>80143</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11292,37 +11296,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6457</v>
+        <v>6462</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>690656</v>
+        <v>690520</v>
       </c>
       <c r="R105" t="n">
-        <v>7096927</v>
+        <v>7097024</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11366,26 +11370,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY105" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
         <v>126927184</v>
       </c>
       <c r="B106" t="n">
-        <v>80123</v>
+        <v>80114</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11479,10 +11479,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126927178</v>
+        <v>126927139</v>
       </c>
       <c r="B107" t="n">
-        <v>80152</v>
+        <v>80143</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11514,10 +11514,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>690520</v>
+        <v>690515</v>
       </c>
       <c r="R107" t="n">
-        <v>7097024</v>
+        <v>7097011</v>
       </c>
       <c r="S107" t="n">
         <v>15</v>
@@ -11576,32 +11576,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126927139</v>
+        <v>126927292</v>
       </c>
       <c r="B108" t="n">
-        <v>80152</v>
+        <v>98436</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11611,10 +11611,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>690515</v>
+        <v>690530</v>
       </c>
       <c r="R108" t="n">
-        <v>7097011</v>
+        <v>7097014</v>
       </c>
       <c r="S108" t="n">
         <v>15</v>

--- a/artfynd/A 30467-2025 artfynd.xlsx
+++ b/artfynd/A 30467-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY109"/>
+  <dimension ref="A1:AY116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126919968</v>
+        <v>126931564</v>
       </c>
       <c r="B2" t="n">
-        <v>80027</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rislidstjärnarna, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>690349</v>
+        <v>690624</v>
       </c>
       <c r="R2" t="n">
-        <v>7097128</v>
+        <v>7096879</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -776,49 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126909580</v>
+        <v>126917539</v>
       </c>
       <c r="B3" t="n">
-        <v>98450</v>
+        <v>91920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1205</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Rislidtjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>690493</v>
+        <v>690508</v>
       </c>
       <c r="R3" t="n">
-        <v>7097055</v>
+        <v>7097037</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,19 +844,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,12 +861,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -891,53 +877,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126917533</v>
+        <v>126919966</v>
       </c>
       <c r="B4" t="n">
-        <v>57663</v>
+        <v>91920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rislidtjärnarna, Ång</t>
+          <t>Rislidstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>690514</v>
+        <v>690349</v>
       </c>
       <c r="R4" t="n">
-        <v>7097039</v>
+        <v>7097128</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,16 +954,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Bohål i asp, storlek stämmer med tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
@@ -989,12 +966,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1005,45 +982,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126917550</v>
+        <v>126936912</v>
       </c>
       <c r="B5" t="n">
-        <v>80159</v>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rislidtjärnarna, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>690515</v>
+        <v>690392</v>
       </c>
       <c r="R5" t="n">
-        <v>7097014</v>
+        <v>7097038</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,12 +1047,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1090,12 +1067,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1106,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126917563</v>
+        <v>126936913</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1117,34 +1094,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rislidtjärnarna, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>690509</v>
+        <v>690466</v>
       </c>
       <c r="R6" t="n">
-        <v>7097052</v>
+        <v>7096945</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1171,12 +1148,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1191,12 +1168,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1207,48 +1184,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126919976</v>
+        <v>126926789</v>
       </c>
       <c r="B7" t="n">
-        <v>98450</v>
+        <v>91930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rislidstjärnarna, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>690349</v>
+        <v>690438</v>
       </c>
       <c r="R7" t="n">
-        <v>7097128</v>
+        <v>7097141</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1272,12 +1249,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,48 +1269,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126917539</v>
+        <v>126917563</v>
       </c>
       <c r="B8" t="n">
-        <v>91343</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1343,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>690508</v>
+        <v>690509</v>
       </c>
       <c r="R8" t="n">
-        <v>7097037</v>
+        <v>7097052</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,52 +1382,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126919966</v>
+        <v>126926415</v>
       </c>
       <c r="B9" t="n">
-        <v>91343</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rislidstjärnarna, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>690349</v>
+        <v>690329</v>
       </c>
       <c r="R9" t="n">
-        <v>7097128</v>
+        <v>7097272</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1478,12 +1447,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1498,64 +1467,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126917545</v>
+        <v>126926441</v>
       </c>
       <c r="B10" t="n">
-        <v>80027</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rislidtjärnarna, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>690344</v>
+        <v>690327</v>
       </c>
       <c r="R10" t="n">
-        <v>7097126</v>
+        <v>7097277</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1579,12 +1544,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1599,48 +1564,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126909288</v>
+        <v>126926457</v>
       </c>
       <c r="B11" t="n">
-        <v>78779</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1650,13 +1611,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>690438</v>
+        <v>690374</v>
       </c>
       <c r="R11" t="n">
-        <v>7097136</v>
+        <v>7097232</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1680,22 +1641,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>15:11</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:11</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1710,26 +1661,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126909413</v>
+        <v>126926526</v>
       </c>
       <c r="B12" t="n">
-        <v>98450</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1737,38 +1684,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>N Johannesbomyran, N Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>690516</v>
+        <v>690490</v>
       </c>
       <c r="R12" t="n">
-        <v>7097033</v>
+        <v>7096997</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1795,22 +1738,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>15:20</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>15:20</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1825,26 +1758,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126909538</v>
+        <v>126926531</v>
       </c>
       <c r="B13" t="n">
-        <v>98450</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,38 +1781,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>690484</v>
+        <v>690376</v>
       </c>
       <c r="R13" t="n">
-        <v>7097073</v>
+        <v>7097225</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1910,22 +1835,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:27</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:27</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1940,26 +1855,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126918516</v>
+        <v>126926566</v>
       </c>
       <c r="B14" t="n">
-        <v>98450</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1967,49 +1878,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>N Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>690488</v>
+        <v>690362</v>
       </c>
       <c r="R14" t="n">
-        <v>7097027</v>
+        <v>7097210</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2033,12 +1932,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2047,71 +1946,66 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126917549</v>
+        <v>126926624</v>
       </c>
       <c r="B15" t="n">
-        <v>80123</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rislidtjärnarna, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>690509</v>
+        <v>690399</v>
       </c>
       <c r="R15" t="n">
-        <v>7097031</v>
+        <v>7097170</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2135,12 +2029,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2155,67 +2049,60 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126918507</v>
+        <v>126926697</v>
       </c>
       <c r="B16" t="n">
-        <v>80123</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>N Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>690488</v>
+        <v>690438</v>
       </c>
       <c r="R16" t="n">
-        <v>7097027</v>
+        <v>7097148</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2239,12 +2126,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2253,79 +2140,66 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126917534</v>
+        <v>126926859</v>
       </c>
       <c r="B17" t="n">
-        <v>57663</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Rislidtjärnarna, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>690506</v>
+        <v>690483</v>
       </c>
       <c r="R17" t="n">
-        <v>7097037</v>
+        <v>7097114</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2349,24 +2223,19 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Bohål i asp, storlek stämmer med tretåig hackspett.</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="b">
         <v>0</v>
@@ -2374,64 +2243,60 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126909505</v>
+        <v>126927000</v>
       </c>
       <c r="B18" t="n">
-        <v>80152</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>690538</v>
+        <v>690487</v>
       </c>
       <c r="R18" t="n">
-        <v>7096999</v>
+        <v>7097101</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2455,22 +2320,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:25</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:25</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2485,30 +2340,26 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126927367</v>
+        <v>126927024</v>
       </c>
       <c r="B19" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2536,10 +2387,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>690520</v>
+        <v>690503</v>
       </c>
       <c r="R19" t="n">
-        <v>7096988</v>
+        <v>7097060</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2598,10 +2449,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126931573</v>
+        <v>126927067</v>
       </c>
       <c r="B20" t="n">
-        <v>98450</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2609,34 +2460,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>690578</v>
+        <v>690536</v>
       </c>
       <c r="R20" t="n">
-        <v>7096991</v>
+        <v>7097045</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2683,64 +2534,60 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126926856</v>
+        <v>126927108</v>
       </c>
       <c r="B21" t="n">
-        <v>78779</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>N Johannesbomyran, N Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>690563</v>
+        <v>690542</v>
       </c>
       <c r="R21" t="n">
-        <v>7096856</v>
+        <v>7097030</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2784,60 +2631,60 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126936912</v>
+        <v>126927191</v>
       </c>
       <c r="B22" t="n">
-        <v>92622</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>690392</v>
+        <v>690524</v>
       </c>
       <c r="R22" t="n">
-        <v>7097038</v>
+        <v>7097009</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2881,30 +2728,26 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126927356</v>
+        <v>126927324</v>
       </c>
       <c r="B23" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2932,10 +2775,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>690516</v>
+        <v>690542</v>
       </c>
       <c r="R23" t="n">
-        <v>7096990</v>
+        <v>7097025</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2994,14 +2837,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126927842</v>
+        <v>126927356</v>
       </c>
       <c r="B24" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3029,10 +2872,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>690605</v>
+        <v>690516</v>
       </c>
       <c r="R24" t="n">
-        <v>7096920</v>
+        <v>7096990</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3091,14 +2934,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126927661</v>
+        <v>126927367</v>
       </c>
       <c r="B25" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3126,10 +2969,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>690574</v>
+        <v>690520</v>
       </c>
       <c r="R25" t="n">
-        <v>7096978</v>
+        <v>7096988</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3188,10 +3031,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126936890</v>
+        <v>126927395</v>
       </c>
       <c r="B26" t="n">
-        <v>98450</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3199,49 +3042,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>690564</v>
+        <v>690542</v>
       </c>
       <c r="R26" t="n">
-        <v>7096907</v>
+        <v>7096989</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3279,33 +3110,28 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126936889</v>
+        <v>126927426</v>
       </c>
       <c r="B27" t="n">
-        <v>98450</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3313,53 +3139,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>690595</v>
+        <v>690560</v>
       </c>
       <c r="R27" t="n">
-        <v>7096886</v>
+        <v>7097019</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3397,33 +3207,28 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126936886</v>
+        <v>126927465</v>
       </c>
       <c r="B28" t="n">
-        <v>98450</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3431,53 +3236,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>690607</v>
+        <v>690596</v>
       </c>
       <c r="R28" t="n">
-        <v>7097014</v>
+        <v>7097023</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3515,71 +3304,66 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126931565</v>
+        <v>126927550</v>
       </c>
       <c r="B29" t="n">
-        <v>78779</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>690620</v>
+        <v>690574</v>
       </c>
       <c r="R29" t="n">
-        <v>7096859</v>
+        <v>7096994</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3623,30 +3407,26 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126937624</v>
+        <v>126927661</v>
       </c>
       <c r="B30" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3670,14 +3450,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>690656</v>
+        <v>690574</v>
       </c>
       <c r="R30" t="n">
-        <v>7096868</v>
+        <v>7096978</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3724,30 +3504,26 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126936897</v>
+        <v>126927691</v>
       </c>
       <c r="B31" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3771,17 +3547,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>690544</v>
+        <v>690577</v>
       </c>
       <c r="R31" t="n">
-        <v>7096906</v>
+        <v>7096975</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3825,26 +3601,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126937621</v>
+        <v>126927712</v>
       </c>
       <c r="B32" t="n">
-        <v>98450</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3852,34 +3624,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>690635</v>
+        <v>690586</v>
       </c>
       <c r="R32" t="n">
-        <v>7096944</v>
+        <v>7096958</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3914,11 +3686,6 @@
           <t>2025-07-26</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ca 40 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -3931,30 +3698,26 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126927550</v>
+        <v>126927737</v>
       </c>
       <c r="B33" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -3982,10 +3745,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>690574</v>
+        <v>690623</v>
       </c>
       <c r="R33" t="n">
-        <v>7096994</v>
+        <v>7096931</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4044,10 +3807,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126936883</v>
+        <v>126927842</v>
       </c>
       <c r="B34" t="n">
-        <v>98450</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4055,53 +3818,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>690668</v>
+        <v>690605</v>
       </c>
       <c r="R34" t="n">
-        <v>7096918</v>
+        <v>7096920</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4139,33 +3886,28 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126936888</v>
+        <v>126927943</v>
       </c>
       <c r="B35" t="n">
-        <v>98450</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4173,49 +3915,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>690639</v>
+        <v>690585</v>
       </c>
       <c r="R35" t="n">
-        <v>7096927</v>
+        <v>7096888</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4253,33 +3983,28 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126931567</v>
+        <v>126928117</v>
       </c>
       <c r="B36" t="n">
-        <v>98450</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4287,49 +4012,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>690686</v>
+        <v>690540</v>
       </c>
       <c r="R36" t="n">
-        <v>7096928</v>
+        <v>7096888</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4367,33 +4080,28 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126937620</v>
+        <v>126928173</v>
       </c>
       <c r="B37" t="n">
-        <v>98450</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4401,38 +4109,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>690612</v>
+        <v>690547</v>
       </c>
       <c r="R37" t="n">
-        <v>7096930</v>
+        <v>7096876</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4467,48 +4171,38 @@
           <t>2025-07-26</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Cirka 30 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126926531</v>
+        <v>126931576</v>
       </c>
       <c r="B38" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4532,14 +4226,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>690376</v>
+        <v>690565</v>
       </c>
       <c r="R38" t="n">
-        <v>7097225</v>
+        <v>7096992</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4586,26 +4280,30 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126936910</v>
+        <v>126936895</v>
       </c>
       <c r="B39" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4633,10 +4331,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>690572</v>
+        <v>690445</v>
       </c>
       <c r="R39" t="n">
-        <v>7096932</v>
+        <v>7096945</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4699,14 +4397,14 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126936900</v>
+        <v>126936896</v>
       </c>
       <c r="B40" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -4734,10 +4432,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>690663</v>
+        <v>690482</v>
       </c>
       <c r="R40" t="n">
-        <v>7096854</v>
+        <v>7096931</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4800,10 +4498,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126936887</v>
+        <v>126936897</v>
       </c>
       <c r="B41" t="n">
-        <v>98450</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4811,46 +4509,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>690632</v>
+        <v>690544</v>
       </c>
       <c r="R41" t="n">
-        <v>7096922</v>
+        <v>7096906</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4891,7 +4577,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4914,10 +4599,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126936894</v>
+        <v>126936898</v>
       </c>
       <c r="B42" t="n">
-        <v>98450</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4925,21 +4610,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4949,10 +4634,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>690497</v>
+        <v>690576</v>
       </c>
       <c r="R42" t="n">
-        <v>7097017</v>
+        <v>7096919</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5015,48 +4700,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126926789</v>
+        <v>126936899</v>
       </c>
       <c r="B43" t="n">
-        <v>91352</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>690438</v>
+        <v>690607</v>
       </c>
       <c r="R43" t="n">
-        <v>7097141</v>
+        <v>7097019</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5100,26 +4785,30 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126926859</v>
+        <v>126936900</v>
       </c>
       <c r="B44" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -5143,17 +4832,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>690483</v>
+        <v>690663</v>
       </c>
       <c r="R44" t="n">
-        <v>7097114</v>
+        <v>7096854</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5197,22 +4886,26 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126931570</v>
+        <v>126936901</v>
       </c>
       <c r="B45" t="n">
-        <v>98450</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5220,46 +4913,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>690658</v>
+        <v>690623</v>
       </c>
       <c r="R45" t="n">
-        <v>7096895</v>
+        <v>7096862</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5300,19 +4981,18 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5323,32 +5003,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126936882</v>
+        <v>126936906</v>
       </c>
       <c r="B46" t="n">
-        <v>78779</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5358,10 +5038,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>690560</v>
+        <v>690572</v>
       </c>
       <c r="R46" t="n">
-        <v>7096959</v>
+        <v>7096836</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5424,14 +5104,14 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126937632</v>
+        <v>126936907</v>
       </c>
       <c r="B47" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -5455,17 +5135,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>690454</v>
+        <v>690584</v>
       </c>
       <c r="R47" t="n">
-        <v>7097036</v>
+        <v>7096832</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5509,12 +5189,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5525,14 +5205,14 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126937623</v>
+        <v>126936908</v>
       </c>
       <c r="B48" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -5556,17 +5236,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>690707</v>
+        <v>690598</v>
       </c>
       <c r="R48" t="n">
-        <v>7096903</v>
+        <v>7096855</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5610,12 +5290,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5626,14 +5306,14 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126928173</v>
+        <v>126936909</v>
       </c>
       <c r="B49" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -5657,17 +5337,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>690547</v>
+        <v>690590</v>
       </c>
       <c r="R49" t="n">
-        <v>7096876</v>
+        <v>7096893</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5711,26 +5391,30 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126936911</v>
+        <v>126936910</v>
       </c>
       <c r="B50" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -5758,10 +5442,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>690481</v>
+        <v>690572</v>
       </c>
       <c r="R50" t="n">
-        <v>7097028</v>
+        <v>7096932</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5824,32 +5508,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126936877</v>
+        <v>126936911</v>
       </c>
       <c r="B51" t="n">
-        <v>79638</v>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5859,10 +5543,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>690378</v>
+        <v>690481</v>
       </c>
       <c r="R51" t="n">
-        <v>7096984</v>
+        <v>7097028</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5925,10 +5609,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126936885</v>
+        <v>126937622</v>
       </c>
       <c r="B52" t="n">
-        <v>98450</v>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5936,49 +5620,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>690596</v>
+        <v>690620</v>
       </c>
       <c r="R52" t="n">
-        <v>7097007</v>
+        <v>7096858</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6016,19 +5688,18 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6039,10 +5710,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126931571</v>
+        <v>126937623</v>
       </c>
       <c r="B53" t="n">
-        <v>98450</v>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6050,49 +5721,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>690644</v>
+        <v>690707</v>
       </c>
       <c r="R53" t="n">
-        <v>7096948</v>
+        <v>7096903</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6130,19 +5789,18 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6153,14 +5811,14 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126927000</v>
+        <v>126937624</v>
       </c>
       <c r="B54" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -6184,14 +5842,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>690487</v>
+        <v>690656</v>
       </c>
       <c r="R54" t="n">
-        <v>7097101</v>
+        <v>7096868</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6238,57 +5896,61 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126927086</v>
+        <v>126937626</v>
       </c>
       <c r="B55" t="n">
-        <v>80123</v>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>690545</v>
+        <v>690537</v>
       </c>
       <c r="R55" t="n">
-        <v>7097033</v>
+        <v>7096865</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6335,26 +5997,30 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126928117</v>
+        <v>126937627</v>
       </c>
       <c r="B56" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -6378,14 +6044,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>690540</v>
+        <v>690522</v>
       </c>
       <c r="R56" t="n">
-        <v>7096888</v>
+        <v>7096919</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6432,60 +6098,64 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126936878</v>
+        <v>126937629</v>
       </c>
       <c r="B57" t="n">
-        <v>79638</v>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>690509</v>
+        <v>690504</v>
       </c>
       <c r="R57" t="n">
-        <v>7096927</v>
+        <v>7096980</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6529,12 +6199,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6545,48 +6215,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126936881</v>
+        <v>126937630</v>
       </c>
       <c r="B58" t="n">
-        <v>78779</v>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>690617</v>
+        <v>690480</v>
       </c>
       <c r="R58" t="n">
-        <v>7096851</v>
+        <v>7096994</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6630,12 +6300,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6646,14 +6316,14 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126926624</v>
+        <v>126937632</v>
       </c>
       <c r="B59" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -6677,14 +6347,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>690399</v>
+        <v>690454</v>
       </c>
       <c r="R59" t="n">
-        <v>7097170</v>
+        <v>7097036</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6731,22 +6401,26 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126937630</v>
+        <v>126931566</v>
       </c>
       <c r="B60" t="n">
-        <v>79020</v>
+        <v>79084</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6754,37 +6428,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>690480</v>
+        <v>690621</v>
       </c>
       <c r="R60" t="n">
-        <v>7096994</v>
+        <v>7096855</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6828,12 +6502,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6844,10 +6518,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126927108</v>
+        <v>126937618</v>
       </c>
       <c r="B61" t="n">
-        <v>79020</v>
+        <v>79084</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6855,34 +6529,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>690542</v>
+        <v>690602</v>
       </c>
       <c r="R61" t="n">
-        <v>7097030</v>
+        <v>7096811</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6929,22 +6603,26 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126927426</v>
+        <v>126936877</v>
       </c>
       <c r="B62" t="n">
-        <v>79020</v>
+        <v>79946</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6952,37 +6630,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>690560</v>
+        <v>690378</v>
       </c>
       <c r="R62" t="n">
-        <v>7097019</v>
+        <v>7096984</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7026,22 +6704,26 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126926566</v>
+        <v>126936878</v>
       </c>
       <c r="B63" t="n">
-        <v>79020</v>
+        <v>79946</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7049,37 +6731,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>690362</v>
+        <v>690509</v>
       </c>
       <c r="R63" t="n">
-        <v>7097210</v>
+        <v>7096927</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7123,22 +6805,26 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126931576</v>
+        <v>126937616</v>
       </c>
       <c r="B64" t="n">
-        <v>79020</v>
+        <v>79946</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7146,37 +6832,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>690565</v>
+        <v>690516</v>
       </c>
       <c r="R64" t="n">
-        <v>7096992</v>
+        <v>7096946</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7220,12 +6906,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7236,45 +6922,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126927067</v>
+        <v>126917545</v>
       </c>
       <c r="B65" t="n">
-        <v>79020</v>
+        <v>80336</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Rislidtjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>690536</v>
+        <v>690344</v>
       </c>
       <c r="R65" t="n">
-        <v>7097045</v>
+        <v>7097126</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7301,12 +6987,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7321,60 +7007,64 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126926457</v>
+        <v>126919968</v>
       </c>
       <c r="B66" t="n">
-        <v>79020</v>
+        <v>80336</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Rislidstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>690374</v>
+        <v>690349</v>
       </c>
       <c r="R66" t="n">
-        <v>7097232</v>
+        <v>7097128</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7398,12 +7088,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7418,57 +7108,61 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
+          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126936893</v>
+        <v>126931577</v>
       </c>
       <c r="B67" t="n">
-        <v>98450</v>
+        <v>80367</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6457</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>690658</v>
+        <v>690656</v>
       </c>
       <c r="R67" t="n">
-        <v>7096938</v>
+        <v>7096927</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7515,12 +7209,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7531,48 +7225,48 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126927409</v>
+        <v>126917549</v>
       </c>
       <c r="B68" t="n">
-        <v>98450</v>
+        <v>80432</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Rislidtjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>690545</v>
+        <v>690509</v>
       </c>
       <c r="R68" t="n">
-        <v>7097003</v>
+        <v>7097031</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7596,12 +7290,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7616,22 +7310,26 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126926526</v>
+        <v>126918507</v>
       </c>
       <c r="B69" t="n">
-        <v>79020</v>
+        <v>80432</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7639,34 +7337,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>N Johannesbomyran, N Johannesbomyran, Ång</t>
+          <t>N Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>690490</v>
+        <v>690488</v>
       </c>
       <c r="R69" t="n">
-        <v>7096997</v>
+        <v>7097027</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7693,12 +7394,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7707,6 +7408,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7721,14 +7423,18 @@
           <t>Fredrik Wilde</t>
         </is>
       </c>
-      <c r="AY69" t="inlineStr"/>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126927324</v>
+        <v>126927086</v>
       </c>
       <c r="B70" t="n">
-        <v>79020</v>
+        <v>80432</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7736,21 +7442,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7760,10 +7466,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>690542</v>
+        <v>690545</v>
       </c>
       <c r="R70" t="n">
-        <v>7097025</v>
+        <v>7097033</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7822,10 +7528,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126936908</v>
+        <v>126927128</v>
       </c>
       <c r="B71" t="n">
-        <v>79020</v>
+        <v>80432</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7833,37 +7539,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>690598</v>
+        <v>690517</v>
       </c>
       <c r="R71" t="n">
-        <v>7096855</v>
+        <v>7097014</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7907,76 +7613,60 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126936891</v>
+        <v>126927184</v>
       </c>
       <c r="B72" t="n">
-        <v>98450</v>
+        <v>80432</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>690644</v>
+        <v>690520</v>
       </c>
       <c r="R72" t="n">
-        <v>7096931</v>
+        <v>7097024</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8014,68 +7704,63 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126936896</v>
+        <v>126909505</v>
       </c>
       <c r="B73" t="n">
-        <v>79020</v>
+        <v>80461</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>690482</v>
+        <v>690538</v>
       </c>
       <c r="R73" t="n">
-        <v>7096931</v>
+        <v>7096999</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8102,12 +7787,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8122,12 +7817,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8138,10 +7833,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126936879</v>
+        <v>126927139</v>
       </c>
       <c r="B74" t="n">
-        <v>97333</v>
+        <v>80461</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8149,37 +7844,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>690490</v>
+        <v>690515</v>
       </c>
       <c r="R74" t="n">
-        <v>7096937</v>
+        <v>7097011</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8223,48 +7918,44 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126927191</v>
+        <v>126927178</v>
       </c>
       <c r="B75" t="n">
-        <v>79020</v>
+        <v>80461</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8274,10 +7965,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>690524</v>
+        <v>690520</v>
       </c>
       <c r="R75" t="n">
-        <v>7097009</v>
+        <v>7097024</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8336,27 +8027,27 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126937629</v>
+        <v>126926946</v>
       </c>
       <c r="B76" t="n">
-        <v>79020</v>
+        <v>80467</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -8367,14 +8058,14 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>690504</v>
+        <v>690510</v>
       </c>
       <c r="R76" t="n">
-        <v>7096980</v>
+        <v>7097095</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8421,64 +8112,60 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126927024</v>
+        <v>126917550</v>
       </c>
       <c r="B77" t="n">
-        <v>79020</v>
+        <v>80468</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Rislidtjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>690503</v>
+        <v>690515</v>
       </c>
       <c r="R77" t="n">
-        <v>7097060</v>
+        <v>7097014</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8502,12 +8189,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8522,22 +8209,26 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126927395</v>
+        <v>126917533</v>
       </c>
       <c r="B78" t="n">
-        <v>79020</v>
+        <v>57953</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8545,37 +8236,45 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Rislidtjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>690542</v>
+        <v>690514</v>
       </c>
       <c r="R78" t="n">
-        <v>7096989</v>
+        <v>7097039</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8599,19 +8298,24 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Bohål i asp, storlek stämmer med tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG78" t="b">
         <v>0</v>
@@ -8619,22 +8323,26 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126927943</v>
+        <v>126917534</v>
       </c>
       <c r="B79" t="n">
-        <v>79020</v>
+        <v>57953</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8642,37 +8350,45 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Johannesbomyran, Ång</t>
+          <t>Rislidtjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>690585</v>
+        <v>690506</v>
       </c>
       <c r="R79" t="n">
-        <v>7096888</v>
+        <v>7097037</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8696,19 +8412,24 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Bohål i asp, storlek stämmer med tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG79" t="b">
         <v>0</v>
@@ -8716,22 +8437,26 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126927343</v>
+        <v>126909413</v>
       </c>
       <c r="B80" t="n">
-        <v>98450</v>
+        <v>99118</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8756,20 +8481,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>690544</v>
+        <v>690516</v>
       </c>
       <c r="R80" t="n">
-        <v>7097007</v>
+        <v>7097033</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8793,12 +8522,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8813,57 +8552,65 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr"/>
+          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126931564</v>
+        <v>126909538</v>
       </c>
       <c r="B81" t="n">
-        <v>79052</v>
+        <v>99118</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>690624</v>
+        <v>690484</v>
       </c>
       <c r="R81" t="n">
-        <v>7096879</v>
+        <v>7097073</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8890,12 +8637,22 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8910,12 +8667,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -8926,48 +8683,52 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126937622</v>
+        <v>126909580</v>
       </c>
       <c r="B82" t="n">
-        <v>79020</v>
+        <v>99118</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesbomyran, Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>690620</v>
+        <v>690493</v>
       </c>
       <c r="R82" t="n">
-        <v>7096858</v>
+        <v>7097055</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8991,12 +8752,22 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9011,12 +8782,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9027,48 +8798,60 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126927691</v>
+        <v>126918516</v>
       </c>
       <c r="B83" t="n">
-        <v>79020</v>
+        <v>99118</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>N Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>690577</v>
+        <v>690488</v>
       </c>
       <c r="R83" t="n">
-        <v>7096975</v>
+        <v>7097027</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9092,12 +8875,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9106,63 +8889,68 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr"/>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126936909</v>
+        <v>126919976</v>
       </c>
       <c r="B84" t="n">
-        <v>79020</v>
+        <v>99118</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Rislidstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>690590</v>
+        <v>690349</v>
       </c>
       <c r="R84" t="n">
-        <v>7096893</v>
+        <v>7097128</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9189,12 +8977,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9209,12 +8997,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9225,32 +9013,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126926723</v>
+        <v>126927292</v>
       </c>
       <c r="B85" t="n">
-        <v>78779</v>
+        <v>99118</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9260,10 +9048,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>690433</v>
+        <v>690530</v>
       </c>
       <c r="R85" t="n">
-        <v>7097136</v>
+        <v>7097014</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9322,48 +9110,48 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126936899</v>
+        <v>126927343</v>
       </c>
       <c r="B86" t="n">
-        <v>79020</v>
+        <v>99118</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>690607</v>
+        <v>690544</v>
       </c>
       <c r="R86" t="n">
-        <v>7097019</v>
+        <v>7097007</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9407,64 +9195,60 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126936901</v>
+        <v>126927409</v>
       </c>
       <c r="B87" t="n">
-        <v>79020</v>
+        <v>99118</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>690623</v>
+        <v>690545</v>
       </c>
       <c r="R87" t="n">
-        <v>7096862</v>
+        <v>7097003</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9508,64 +9292,72 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126927737</v>
+        <v>126931567</v>
       </c>
       <c r="B88" t="n">
-        <v>79020</v>
+        <v>99118</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>690623</v>
+        <v>690686</v>
       </c>
       <c r="R88" t="n">
-        <v>7096931</v>
+        <v>7096928</v>
       </c>
       <c r="S88" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9603,28 +9395,33 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY88" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126936892</v>
+        <v>126931569</v>
       </c>
       <c r="B89" t="n">
-        <v>98450</v>
+        <v>99118</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9651,27 +9448,31 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>690619</v>
+        <v>690550</v>
       </c>
       <c r="R89" t="n">
-        <v>7096955</v>
+        <v>7097011</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9719,12 +9520,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9735,45 +9536,57 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126936913</v>
+        <v>126931570</v>
       </c>
       <c r="B90" t="n">
-        <v>92622</v>
+        <v>99118</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>690466</v>
+        <v>690658</v>
       </c>
       <c r="R90" t="n">
-        <v>7096945</v>
+        <v>7096895</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9814,18 +9627,19 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9836,48 +9650,60 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126926697</v>
+        <v>126931571</v>
       </c>
       <c r="B91" t="n">
-        <v>79020</v>
+        <v>99118</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>690438</v>
+        <v>690644</v>
       </c>
       <c r="R91" t="n">
-        <v>7097148</v>
+        <v>7096948</v>
       </c>
       <c r="S91" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9915,63 +9741,80 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126936895</v>
+        <v>126931572</v>
       </c>
       <c r="B92" t="n">
-        <v>79020</v>
+        <v>99118</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Johannesomyran, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>690445</v>
+        <v>690665</v>
       </c>
       <c r="R92" t="n">
-        <v>7096945</v>
+        <v>7096920</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10012,18 +9855,19 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10034,48 +9878,48 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126937616</v>
+        <v>126931573</v>
       </c>
       <c r="B93" t="n">
-        <v>79638</v>
+        <v>99118</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesbomyran, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>690516</v>
+        <v>690578</v>
       </c>
       <c r="R93" t="n">
-        <v>7096946</v>
+        <v>7096991</v>
       </c>
       <c r="S93" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10119,12 +9963,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10135,48 +9979,64 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126937627</v>
+        <v>126936883</v>
       </c>
       <c r="B94" t="n">
-        <v>79020</v>
+        <v>99118</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>690522</v>
+        <v>690668</v>
       </c>
       <c r="R94" t="n">
-        <v>7096919</v>
+        <v>7096918</v>
       </c>
       <c r="S94" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10214,18 +10074,19 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10236,45 +10097,61 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126936898</v>
+        <v>126936884</v>
       </c>
       <c r="B95" t="n">
-        <v>79020</v>
+        <v>99118</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>690576</v>
+        <v>690609</v>
       </c>
       <c r="R95" t="n">
-        <v>7096919</v>
+        <v>7096953</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10315,6 +10192,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10337,48 +10215,60 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126927128</v>
+        <v>126936885</v>
       </c>
       <c r="B96" t="n">
-        <v>80123</v>
+        <v>99118</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>690517</v>
+        <v>690596</v>
       </c>
       <c r="R96" t="n">
-        <v>7097014</v>
+        <v>7097007</v>
       </c>
       <c r="S96" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10416,28 +10306,33 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126936884</v>
+        <v>126936886</v>
       </c>
       <c r="B97" t="n">
-        <v>98450</v>
+        <v>99118</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10464,7 +10359,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -10485,10 +10380,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>690609</v>
+        <v>690607</v>
       </c>
       <c r="R97" t="n">
-        <v>7096953</v>
+        <v>7097014</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10552,10 +10447,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126931572</v>
+        <v>126936887</v>
       </c>
       <c r="B98" t="n">
-        <v>98450</v>
+        <v>99118</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10582,12 +10477,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -10595,14 +10490,14 @@
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>690665</v>
+        <v>690632</v>
       </c>
       <c r="R98" t="n">
-        <v>7096920</v>
+        <v>7096922</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10650,12 +10545,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10666,10 +10561,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126937619</v>
+        <v>126936888</v>
       </c>
       <c r="B99" t="n">
-        <v>98450</v>
+        <v>99118</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10694,20 +10589,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Lillberget, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>690621</v>
+        <v>690639</v>
       </c>
       <c r="R99" t="n">
-        <v>7096899</v>
+        <v>7096927</v>
       </c>
       <c r="S99" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10745,18 +10652,19 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10767,10 +10675,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126931569</v>
+        <v>126936889</v>
       </c>
       <c r="B100" t="n">
-        <v>98450</v>
+        <v>99118</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10797,12 +10705,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -10814,14 +10722,14 @@
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>690550</v>
+        <v>690595</v>
       </c>
       <c r="R100" t="n">
-        <v>7097011</v>
+        <v>7096886</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10869,12 +10777,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10885,45 +10793,57 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126936880</v>
+        <v>126936890</v>
       </c>
       <c r="B101" t="n">
-        <v>78779</v>
+        <v>99118</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>690619</v>
+        <v>690564</v>
       </c>
       <c r="R101" t="n">
-        <v>7097003</v>
+        <v>7096907</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10964,6 +10884,7 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -10986,10 +10907,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126927292</v>
+        <v>126936891</v>
       </c>
       <c r="B102" t="n">
-        <v>98450</v>
+        <v>99118</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11014,20 +10935,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>690530</v>
+        <v>690644</v>
       </c>
       <c r="R102" t="n">
-        <v>7097014</v>
+        <v>7096931</v>
       </c>
       <c r="S102" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11065,63 +10998,80 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY102" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126931566</v>
+        <v>126936892</v>
       </c>
       <c r="B103" t="n">
-        <v>78778</v>
+        <v>99118</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>690621</v>
+        <v>690619</v>
       </c>
       <c r="R103" t="n">
-        <v>7096855</v>
+        <v>7096955</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11162,18 +11112,19 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -11184,48 +11135,48 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126927465</v>
+        <v>126936893</v>
       </c>
       <c r="B104" t="n">
-        <v>79020</v>
+        <v>99118</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>690596</v>
+        <v>690658</v>
       </c>
       <c r="R104" t="n">
-        <v>7097023</v>
+        <v>7096938</v>
       </c>
       <c r="S104" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11269,57 +11220,61 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY104" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126931577</v>
+        <v>126936894</v>
       </c>
       <c r="B105" t="n">
-        <v>80058</v>
+        <v>99118</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6457</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Johannesbomyran, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>690656</v>
+        <v>690497</v>
       </c>
       <c r="R105" t="n">
-        <v>7096927</v>
+        <v>7097017</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11366,12 +11321,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -11382,45 +11337,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126927184</v>
+        <v>126937619</v>
       </c>
       <c r="B106" t="n">
-        <v>80123</v>
+        <v>99118</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>690520</v>
+        <v>690621</v>
       </c>
       <c r="R106" t="n">
-        <v>7097024</v>
+        <v>7096899</v>
       </c>
       <c r="S106" t="n">
         <v>15</v>
@@ -11467,57 +11422,65 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY106" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126927178</v>
+        <v>126937620</v>
       </c>
       <c r="B107" t="n">
-        <v>80152</v>
+        <v>99118</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>690520</v>
+        <v>690612</v>
       </c>
       <c r="R107" t="n">
-        <v>7097024</v>
+        <v>7096930</v>
       </c>
       <c r="S107" t="n">
         <v>15</v>
@@ -11552,69 +11515,79 @@
           <t>2025-07-26</t>
         </is>
       </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Cirka 30 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY107" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126927139</v>
+        <v>126937621</v>
       </c>
       <c r="B108" t="n">
-        <v>80152</v>
+        <v>99118</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>690515</v>
+        <v>690635</v>
       </c>
       <c r="R108" t="n">
-        <v>7097011</v>
+        <v>7096944</v>
       </c>
       <c r="S108" t="n">
         <v>15</v>
@@ -11649,6 +11622,11 @@
           <t>2025-07-26</t>
         </is>
       </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Ca 40 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
@@ -11661,60 +11639,64 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY108" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126927712</v>
+        <v>126936879</v>
       </c>
       <c r="B109" t="n">
-        <v>79089</v>
+        <v>97989</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+          <t>Johannesomyran, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>690586</v>
+        <v>690490</v>
       </c>
       <c r="R109" t="n">
-        <v>7096958</v>
+        <v>7096937</v>
       </c>
       <c r="S109" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11758,15 +11740,728 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>126909288</v>
+      </c>
+      <c r="B110" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>690438</v>
+      </c>
+      <c r="R110" t="n">
+        <v>7097136</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Eleonor Johansson</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>126926723</v>
+      </c>
+      <c r="B111" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Nyfönnemyrtjärnen, Nyfönnemyrtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>690433</v>
+      </c>
+      <c r="R111" t="n">
+        <v>7097136</v>
+      </c>
+      <c r="S111" t="n">
+        <v>15</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
           <t>Anders Heggestad</t>
         </is>
       </c>
-      <c r="AX109" t="inlineStr">
+      <c r="AX111" t="inlineStr">
         <is>
           <t>Anders Heggestad</t>
         </is>
       </c>
-      <c r="AY109" t="inlineStr"/>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>126926856</v>
+      </c>
+      <c r="B112" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>N Johannesbomyran, N Johannesbomyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>690563</v>
+      </c>
+      <c r="R112" t="n">
+        <v>7096856</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>126931565</v>
+      </c>
+      <c r="B113" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Johannesbomyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>690620</v>
+      </c>
+      <c r="R113" t="n">
+        <v>7096859</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>126936880</v>
+      </c>
+      <c r="B114" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Johannesomyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>690619</v>
+      </c>
+      <c r="R114" t="n">
+        <v>7097003</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>126936881</v>
+      </c>
+      <c r="B115" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Johannesomyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>690617</v>
+      </c>
+      <c r="R115" t="n">
+        <v>7096851</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>126936882</v>
+      </c>
+      <c r="B116" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Johannesomyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>690560</v>
+      </c>
+      <c r="R116" t="n">
+        <v>7096959</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30467-2025 artfynd.xlsx
+++ b/artfynd/A 30467-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY116"/>
+  <dimension ref="A1:AZ116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126931564</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917539</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,6 +994,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126919966</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126936912</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1181,6 +1206,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126936913</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126926789</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917563</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1476,6 +1516,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126926415</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1573,6 +1618,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126926441</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1670,6 +1720,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126926457</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1767,6 +1822,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126926526</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1864,6 +1924,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126926531</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1961,6 +2026,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126926566</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2058,6 +2128,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126926624</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2155,6 +2230,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126926697</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2252,6 +2332,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126926859</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2349,6 +2434,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126927000</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2446,6 +2536,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126927024</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2543,6 +2638,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126927067</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2640,6 +2740,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126927108</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2737,6 +2842,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126927191</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2834,6 +2944,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126927324</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2931,6 +3046,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126927356</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3028,6 +3148,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126927367</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3125,6 +3250,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126927395</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3222,6 +3352,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126927426</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3319,6 +3454,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126927465</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3416,6 +3556,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126927550</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3513,6 +3658,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126927661</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3610,6 +3760,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126927691</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3707,6 +3862,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126927712</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3804,6 +3964,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126927737</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3901,6 +4066,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126927842</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3998,6 +4168,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126927943</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4095,6 +4270,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126928117</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4192,6 +4372,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126928173</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4293,6 +4478,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126931576</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4394,6 +4584,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126936895</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4495,6 +4690,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126936896</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4596,6 +4796,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126936897</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4697,6 +4902,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126936898</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4798,6 +5008,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126936899</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4899,6 +5114,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126936900</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5000,6 +5220,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126936901</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5101,6 +5326,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126936906</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5202,6 +5432,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126936907</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5303,6 +5538,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126936908</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5404,6 +5644,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126936909</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5505,6 +5750,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126936910</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5606,6 +5856,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126936911</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5707,6 +5962,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126937622</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5808,6 +6068,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126937623</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5909,6 +6174,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126937624</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6010,6 +6280,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126937626</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6111,6 +6386,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126937627</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6212,6 +6492,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126937629</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6313,6 +6598,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126937630</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6414,6 +6704,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126937632</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6515,6 +6810,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126931566</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6616,6 +6916,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126937618</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6717,6 +7022,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126936877</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6818,6 +7128,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126936878</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6919,6 +7234,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126937616</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7020,6 +7340,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917545</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7121,6 +7446,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126919968</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7222,6 +7552,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126931577</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7321,6 +7656,11 @@
       <c r="AY68" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917549</t>
         </is>
       </c>
     </row>
@@ -7428,6 +7768,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918507</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7525,6 +7870,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126927086</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7622,6 +7972,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126927128</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7719,6 +8074,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126927184</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7830,6 +8190,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126909505</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7927,6 +8292,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126927139</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8024,6 +8394,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126927178</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8121,6 +8496,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126926946</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8222,6 +8602,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917550</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8336,6 +8721,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917533</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8450,6 +8840,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917534</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8565,6 +8960,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126909413</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8680,6 +9080,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126909538</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8795,6 +9200,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126909580</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8909,6 +9319,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918516</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9010,6 +9425,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126919976</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9107,6 +9527,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126927292</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9204,6 +9629,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126927343</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9301,6 +9731,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126927409</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9415,6 +9850,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126931567</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9533,6 +9973,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126931569</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9647,6 +10092,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126931570</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9761,6 +10211,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126931571</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9875,6 +10330,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126931572</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9976,6 +10436,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126931573</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10094,6 +10559,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126936883</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10212,6 +10682,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126936884</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10326,6 +10801,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126936885</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10444,6 +10924,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126936886</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10558,6 +11043,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126936887</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10672,6 +11162,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126936888</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10790,6 +11285,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126936889</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10904,6 +11404,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126936890</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11018,6 +11523,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126936891</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11132,6 +11642,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126936892</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11233,6 +11748,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126936893</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11334,6 +11854,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126936894</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11433,6 +11958,11 @@
       <c r="AY106" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126937619</t>
         </is>
       </c>
     </row>
@@ -11546,6 +12076,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126937620</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11652,6 +12187,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126937621</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11753,6 +12293,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126936879</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11864,6 +12409,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126909288</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11961,6 +12511,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126926723</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12058,6 +12613,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126926856</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12159,6 +12719,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126931565</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12260,6 +12825,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126936880</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12361,6 +12931,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126936881</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12462,8 +13037,130 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126936882</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>